--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="444">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 01.02.2025 11:35:10</t>
+    <t>Период: на 14.10.2025 15:55:17</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,15 +62,30 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
@@ -80,6 +95,15 @@
     <t>Какао-порошок 100г/40 УБ</t>
   </si>
   <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 100г /40шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт</t>
+  </si>
+  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -89,13 +113,19 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
-    <t>Ванільний цукор УБ 40г /45шт</t>
+    <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт</t>
+    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
   </si>
   <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
@@ -104,45 +134,69 @@
     <t>ПРИПРАВИ</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
+    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
+    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Часник гранульований сушений УБ 15г /42шт</t>
   </si>
   <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /</t>
+  </si>
+  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -167,7 +221,10 @@
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
-    <t>Перець духм"яний УБ 20г /22шт</t>
+    <t>Перець духмяний УБ 15г /30шт</t>
+  </si>
+  <si>
+    <t>Перець духмяний УБ 20г /22шт</t>
   </si>
   <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
@@ -176,12 +233,12 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
@@ -194,46 +251,49 @@
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт ДС</t>
-  </si>
-  <si>
-    <t>БАТОН ROSHEN з начинкою 43г/180</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г/180 шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон мол-шок карамель 40г/180/30</t>
-  </si>
-  <si>
-    <t>Батон мол-шок крем-брюле 43г/180/30</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
@@ -248,6 +308,9 @@
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Празький ВКФ 300г /9шт</t>
+  </si>
+  <si>
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -269,12 +332,18 @@
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
     <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
+  </si>
+  <si>
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -290,18 +359,18 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -329,12 +398,21 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Wafers какао ККФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
@@ -350,9 +428,6 @@
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт IL /</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -365,9 +440,6 @@
     <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -398,6 +470,15 @@
     <t>Mintex+ зі смаком м'яти ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -407,6 +488,9 @@
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -422,40 +506,88 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
@@ -464,6 +596,12 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -473,21 +611,18 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -500,6 +635,9 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -512,6 +650,9 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -530,19 +671,28 @@
     <t>Шалена бджілка ВКФ 200г /12шт</t>
   </si>
   <si>
+    <t>Шалена бджілка РЦ 200г /12шт</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
     <t>Beri РЦ 1кг /8пак /</t>
   </si>
   <si>
+    <t>Coconut КрКФ 1кг /7пак</t>
+  </si>
+  <si>
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>CoffeeLike ВКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>CoffeeLike КрКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Fudgenta ВКФ 0.785кг /9пак</t>
+    <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
@@ -551,6 +701,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
@@ -560,7 +713,7 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт</t>
+    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
   </si>
   <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
@@ -581,6 +734,9 @@
     <t>Mintex+ Lemon зі смаком лимону та ментолу ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Peppinezzz РЦ 0.9кг /6пак</t>
+  </si>
+  <si>
     <t>Roshen Butter-Milk КрКФ 1кг /8шт</t>
   </si>
   <si>
@@ -608,10 +764,7 @@
     <t>Карамелькино КрКФ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Молочна крапля ВКФ 1кг /7пак</t>
-  </si>
-  <si>
-    <t>Молочна крапля КрКФ 1кг /7пак /</t>
+    <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
     <t>Рачки ВКФ 1кг /7пак /</t>
@@ -644,9 +797,6 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт ДС</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -671,10 +821,10 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Київ вечірній ККФ 176г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній ККФ 352г /7шт</t>
+    <t>Київ вечірній ВКФ 176г /7шт</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
   </si>
   <si>
     <t>Стріла Подільска 200г/10</t>
@@ -683,12 +833,42 @@
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
+    <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
     <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
+    <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
+  </si>
+  <si>
     <t>Lovita Classic Cookies арахіс ККФ 150г /16шт</t>
   </si>
   <si>
@@ -701,18 +881,15 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 135г /21шт /</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -728,6 +905,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
+  </si>
+  <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -743,70 +926,124 @@
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою вишня-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао ККФ 180г /28шт UA FP</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт</t>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
   </si>
   <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Multicake з начинкою чорниця-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ВКФ 185г /28шт /</t>
+  </si>
+  <si>
     <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ККФ 370г /24шт</t>
+  </si>
+  <si>
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт UA</t>
-  </si>
-  <si>
     <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з шоколадною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
-    <t>Candy Nut м"яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+    <t>Boo! Bear РЦ 1кг /5пак</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт /</t>
+    <t>Flaksi какао ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт /</t>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
+  </si>
+  <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ВКФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Sorrento ВКФ 2кг /5пак</t>
+    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Milaxy ВКФ 1кг /4пак</t>
+  </si>
+  <si>
+    <t>Sorrento ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Winter dream ВКФ 1кг /5пак</t>
   </si>
   <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
@@ -830,16 +1067,16 @@
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак АКЦІЯ</t>
+    <t>Ромашка ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
@@ -854,7 +1091,7 @@
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
-    <t>Монблан РЦ 240г /15шт</t>
+    <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
   </si>
   <si>
     <t>Монблан РЦ 240г /15шт /</t>
@@ -863,90 +1100,162 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочный ВКФ 260г /15шт</t>
+    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /18шт /</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -956,15 +1265,9 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -980,37 +1283,28 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP /</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA АКЦІЯ</t>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
     <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
@@ -1022,16 +1316,40 @@
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
+  </si>
+  <si>
+    <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
+  </si>
+  <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen зимовий ВКФ 100г /12шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1258,6 +1576,12 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1277,7 +1601,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C338"/>
+  <dimension ref="C444"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1342,7 +1666,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1350,7 +1674,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>174326</v>
+        <v>314976</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1358,7 +1682,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>21727</v>
+        <v>67230</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1366,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>3152</v>
+        <v>9794</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1374,7 +1698,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>293</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1382,7 +1706,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>236</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1390,7 +1714,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>22</v>
+        <v>732</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1398,47 +1722,47 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>579</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>647</v>
+      <c r="C19" s="16" t="n">
+        <v>1545</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="21" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B21" s="14" t="s">
+      <c r="C20" s="11" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>7609</v>
+      <c r="C21" s="16" t="n">
+        <v>1624</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>1883</v>
+      <c r="C22" s="11" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>1511</v>
+      <c r="C23" s="11" t="n">
+        <v>904</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1446,15 +1770,15 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>34</v>
+        <v>864</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16" t="n">
-        <v>3656</v>
+      <c r="C25" s="11" t="n">
+        <v>834</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1462,7 +1786,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>435</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1470,47 +1794,47 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B28" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="12" t="n">
-        <v>5752</v>
-      </c>
-    </row>
-    <row r="29" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B29" s="15" t="s">
+      <c r="C28" s="16" t="n">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="29" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B29" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>389</v>
+      <c r="C29" s="12" t="n">
+        <v>18569</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>960</v>
+      <c r="C30" s="16" t="n">
+        <v>2302</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>111</v>
+      <c r="C31" s="16" t="n">
+        <v>6100</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>172</v>
+      <c r="C32" s="16" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1518,7 +1842,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>1924</v>
+        <v>6606</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1526,7 +1850,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>113</v>
+        <v>480</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1534,7 +1858,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>626</v>
+        <v>893</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1542,23 +1866,23 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="38" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B38" s="15" t="s">
+      <c r="C37" s="16" t="n">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="38" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B38" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>481</v>
+      <c r="C38" s="12" t="n">
+        <v>10111</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1566,7 +1890,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>74</v>
+        <v>810</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1574,7 +1898,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>53</v>
+        <v>851</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1582,23 +1906,23 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B42" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="12" t="n">
-        <v>5214</v>
+      <c r="C42" s="11" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>204</v>
+      <c r="C43" s="16" t="n">
+        <v>1484</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1606,7 +1930,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1614,7 +1938,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1622,7 +1946,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>457</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1630,7 +1954,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>366</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1638,31 +1962,31 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>957</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>284</v>
+      <c r="C49" s="16" t="n">
+        <v>1160</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
       <c r="B50" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>1180</v>
+      <c r="C50" s="11" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>51</v>
+      <c r="C51" s="16" t="n">
+        <v>1025</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1670,7 +1994,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>566</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1686,15 +2010,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1702,47 +2026,47 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B57" s="13" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="12" t="n">
-        <v>152599</v>
-      </c>
-    </row>
-    <row r="58" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B58" s="14" t="s">
+      <c r="C57" s="11" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="12" t="n">
-        <v>54565</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C58" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>2972</v>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B60" s="15" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="60" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B60" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>2340</v>
+      <c r="C60" s="12" t="n">
+        <v>28756</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="16" t="n">
-        <v>2000</v>
+      <c r="C61" s="11" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -1750,7 +2074,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="16" t="n">
-        <v>1980</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1758,15 +2082,15 @@
         <v>62</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="true" outlineLevel="3">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C64" s="16" t="n">
-        <v>3600</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -1774,47 +2098,47 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>2323</v>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="true" outlineLevel="3">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
       <c r="C66" s="16" t="n">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="true" outlineLevel="3">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>17673</v>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C67" s="11" t="n">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
       <c r="C68" s="16" t="n">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C69" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>1980</v>
+      <c r="C70" s="11" t="n">
+        <v>792</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -1822,7 +2146,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="16" t="n">
-        <v>5579</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -1830,15 +2154,15 @@
         <v>71</v>
       </c>
       <c r="C72" s="16" t="n">
-        <v>4218</v>
-      </c>
-    </row>
-    <row r="73" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B73" s="14" t="s">
+        <v>8633</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="12" t="n">
-        <v>1132</v>
+      <c r="C73" s="11" t="n">
+        <v>305</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -1846,7 +2170,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>53</v>
+        <v>597</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -1854,31 +2178,31 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B76" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="76" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B76" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B77" s="15" t="s">
+      <c r="C76" s="12" t="n">
+        <v>247746</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B77" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C77" s="12" t="n">
+        <v>20632</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>74</v>
+      <c r="C78" s="16" t="n">
+        <v>3111</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -1886,119 +2210,119 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>172</v>
+        <v>611</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>270</v>
+      <c r="C80" s="16" t="n">
+        <v>1110</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>40</v>
+      <c r="C81" s="16" t="n">
+        <v>1860</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C82" s="16" t="n">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>9895</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C84" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="3">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C88" s="16" t="n">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C89" s="16" t="n">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C90" s="11" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B93" s="15" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B93" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="16" t="n">
-        <v>1150</v>
+      <c r="C93" s="12" t="n">
+        <v>6874</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2006,7 +2330,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>350</v>
+        <v>305</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2014,7 +2338,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>60</v>
+        <v>577</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2022,7 +2346,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>14</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
@@ -2030,15 +2354,15 @@
         <v>96</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>89</v>
+        <v>685</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>15</v>
+      <c r="C98" s="16" t="n">
+        <v>1630</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
@@ -2046,7 +2370,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>280</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2054,15 +2378,15 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>140</v>
+        <v>683</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>30</v>
+      <c r="C101" s="16" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="102" ht="11" customHeight="true" outlineLevel="3">
@@ -2070,7 +2394,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>327</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
@@ -2078,7 +2402,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>1</v>
+        <v>435</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2086,23 +2410,23 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B106" s="15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B106" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>117</v>
+      <c r="C106" s="12" t="n">
+        <v>43602</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2110,7 +2434,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>412</v>
+        <v>173</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2118,7 +2442,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>201</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2126,7 +2450,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>35</v>
+        <v>401</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2134,7 +2458,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2142,55 +2466,55 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>2</v>
+        <v>289</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="16" t="n">
-        <v>1267</v>
+      <c r="C112" s="11" t="n">
+        <v>646</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>14</v>
+      <c r="C113" s="16" t="n">
+        <v>8157</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
       <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="11" t="n">
-        <v>210</v>
+      <c r="C114" s="16" t="n">
+        <v>10970</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
       <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>202</v>
+      <c r="C115" s="16" t="n">
+        <v>8585</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="11" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B117" s="14" t="s">
+      <c r="C116" s="16" t="n">
+        <v>8690</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="12" t="n">
-        <v>10451</v>
+      <c r="C117" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2198,7 +2522,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2206,7 +2530,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2214,7 +2538,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2222,7 +2546,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>45</v>
+        <v>128</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2230,7 +2554,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>121</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2238,7 +2562,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2246,7 +2570,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2254,7 +2578,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>203</v>
+        <v>413</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2262,7 +2586,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>248</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2270,7 +2594,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>44</v>
+        <v>530</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2278,7 +2602,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>432</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2286,7 +2610,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>431</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2294,7 +2618,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2302,7 +2626,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>288</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2310,7 +2634,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>366</v>
+        <v>257</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2318,7 +2642,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>43</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2326,7 +2650,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>366</v>
+        <v>235</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2334,7 +2658,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>183</v>
+        <v>434</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2342,15 +2666,15 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>132</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>163</v>
+      <c r="C137" s="16" t="n">
+        <v>1663</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2358,7 +2682,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>198</v>
+        <v>46</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2366,7 +2690,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>288</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2374,15 +2698,15 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="141" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B141" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="141" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B141" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="11" t="n">
-        <v>66</v>
+      <c r="C141" s="12" t="n">
+        <v>20719</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2390,7 +2714,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>432</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2398,7 +2722,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>220</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2406,7 +2730,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2414,7 +2738,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2422,7 +2746,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>432</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2430,7 +2754,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>39</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2438,7 +2762,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>132</v>
+        <v>67</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2446,7 +2770,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>338</v>
+        <v>191</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2454,7 +2778,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>432</v>
+        <v>118</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2462,7 +2786,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2470,7 +2794,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>198</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2478,7 +2802,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>153</v>
+        <v>507</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2486,7 +2810,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>132</v>
+        <v>741</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2494,7 +2818,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2502,7 +2826,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>432</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2510,7 +2834,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>254</v>
+        <v>154</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2518,7 +2842,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>198</v>
+        <v>676</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2526,7 +2850,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>809</v>
+        <v>741</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2534,7 +2858,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>432</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2542,7 +2866,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>209</v>
+        <v>57</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2550,7 +2874,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2558,7 +2882,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>234</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2566,7 +2890,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>366</v>
+        <v>440</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2574,7 +2898,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2582,7 +2906,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2590,7 +2914,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>11</v>
+        <v>742</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2598,7 +2922,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2606,7 +2930,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>32</v>
+        <v>177</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2614,15 +2938,15 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="171" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B171" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="12" t="n">
-        <v>5768</v>
+      <c r="C171" s="11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2630,7 +2954,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2638,7 +2962,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>27</v>
+        <v>522</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2646,7 +2970,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>266</v>
+        <v>429</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2654,7 +2978,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>126</v>
+        <v>329</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2662,7 +2986,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>430</v>
+        <v>593</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2670,7 +2994,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2678,7 +3002,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>84</v>
+        <v>990</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2686,7 +3010,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>45</v>
+        <v>550</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2694,7 +3018,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>166</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2702,7 +3026,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>16</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2710,15 +3034,15 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>135</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>291</v>
+      <c r="C183" s="16" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2726,7 +3050,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>143</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2734,7 +3058,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2742,15 +3066,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>127</v>
+      <c r="C187" s="16" t="n">
+        <v>2672</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2758,7 +3082,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>93</v>
+        <v>150</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -2766,7 +3090,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>54</v>
+        <v>658</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2774,7 +3098,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2782,7 +3106,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>439</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2790,7 +3114,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>434</v>
+        <v>34</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2798,7 +3122,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2806,7 +3130,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>89</v>
+        <v>473</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2814,7 +3138,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2822,7 +3146,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>514</v>
+        <v>331</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2830,7 +3154,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>83</v>
+        <v>547</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2838,7 +3162,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>54</v>
+        <v>382</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -2846,7 +3170,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>264</v>
+        <v>963</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -2854,7 +3178,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>421</v>
+        <v>293</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2862,7 +3186,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2870,7 +3194,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>224</v>
+        <v>123</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2878,7 +3202,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>331</v>
+        <v>43</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -2886,15 +3210,15 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="205" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B205" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="205" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="12" t="n">
-        <v>1904</v>
+      <c r="C205" s="11" t="n">
+        <v>376</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2902,7 +3226,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2910,7 +3234,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>477</v>
+        <v>61</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -2918,7 +3242,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>253</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -2926,7 +3250,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>521</v>
+        <v>153</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -2934,7 +3258,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>6</v>
+        <v>356</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -2942,7 +3266,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -2950,7 +3274,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -2958,7 +3282,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -2966,7 +3290,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>154</v>
+        <v>228</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -2974,7 +3298,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -2982,7 +3306,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -2990,7 +3314,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -2998,15 +3322,15 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="219" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B219" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="219" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B219" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>35</v>
+      <c r="C219" s="12" t="n">
+        <v>17291</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3014,23 +3338,23 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="221" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B221" s="14" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="221" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B221" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="12" t="n">
-        <v>6615</v>
-      </c>
-    </row>
-    <row r="222" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C221" s="11" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="15" t="s">
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>8</v>
+        <v>517</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3038,7 +3362,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>6</v>
+        <v>136</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3046,7 +3370,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3054,15 +3378,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>374</v>
+        <v>440</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>393</v>
+      <c r="C226" s="16" t="n">
+        <v>1436</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3070,79 +3394,79 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="229" ht="22" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="230" ht="22" customHeight="true" outlineLevel="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="231" ht="22" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="true" outlineLevel="3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="233" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="234" ht="22" customHeight="true" outlineLevel="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="3">
       <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="235" ht="22" customHeight="true" outlineLevel="3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="15" t="s">
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="236" ht="22" customHeight="true" outlineLevel="3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>43</v>
+        <v>573</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3150,7 +3474,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>273</v>
+        <v>473</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3158,7 +3482,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>338</v>
+        <v>784</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3166,7 +3490,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>14</v>
+        <v>212</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3174,7 +3498,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>51</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3182,7 +3506,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>72</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3190,7 +3514,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>270</v>
+        <v>128</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3198,7 +3522,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>248</v>
+        <v>350</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3206,7 +3530,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>343</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3214,7 +3538,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="16" t="n">
-        <v>1303</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3222,7 +3546,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>14</v>
+        <v>800</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3230,7 +3554,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>400</v>
+        <v>449</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3238,7 +3562,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>947</v>
+        <v>744</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3246,23 +3570,23 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="250" ht="22" customHeight="true" outlineLevel="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="251" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C250" s="16" t="n">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>1</v>
+        <v>709</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3270,7 +3594,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>37</v>
+        <v>959</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3278,15 +3602,15 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="254" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B254" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="254" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="12" t="n">
-        <v>3571</v>
+      <c r="C254" s="11" t="n">
+        <v>814</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3294,15 +3618,15 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="256" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B256" s="15" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="256" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B256" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="11" t="n">
-        <v>68</v>
+      <c r="C256" s="12" t="n">
+        <v>1094</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3310,7 +3634,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>514</v>
+        <v>42</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3318,7 +3642,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>57</v>
+        <v>129</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3326,7 +3650,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3334,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3342,7 +3666,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>293</v>
+        <v>81</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3350,7 +3674,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3358,7 +3682,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>84</v>
+        <v>200</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3366,7 +3690,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3374,7 +3698,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3382,7 +3706,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3390,7 +3714,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3398,7 +3722,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3406,7 +3730,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3414,15 +3738,15 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="271" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B271" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B271" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>7</v>
+      <c r="C271" s="12" t="n">
+        <v>24280</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3430,7 +3754,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>53</v>
+        <v>551</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3438,7 +3762,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>626</v>
+        <v>590</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3446,7 +3770,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3454,7 +3778,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>596</v>
+        <v>703</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3462,7 +3786,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>38</v>
+        <v>228</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3470,23 +3794,23 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="278" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B278" s="14" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="278" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="17" t="n">
-        <v>143</v>
+      <c r="C278" s="11" t="n">
+        <v>907</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>25</v>
+      <c r="C279" s="16" t="n">
+        <v>1241</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3494,15 +3818,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B281" s="14" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="12" t="n">
-        <v>58555</v>
+      <c r="C281" s="11" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3510,7 +3834,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3518,39 +3842,39 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="284" ht="22" customHeight="true" outlineLevel="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="285" ht="22" customHeight="true" outlineLevel="3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="3">
       <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="16" t="n">
-        <v>4163</v>
-      </c>
-    </row>
-    <row r="286" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C285" s="11" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="11" t="n">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="287" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C286" s="16" t="n">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="16" t="n">
-        <v>4106</v>
+      <c r="C287" s="11" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="288" ht="22" customHeight="true" outlineLevel="3">
@@ -3558,23 +3882,23 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" ht="11" customHeight="true" outlineLevel="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="16" t="n">
-        <v>1174</v>
+      <c r="C290" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="291" ht="22" customHeight="true" outlineLevel="3">
@@ -3582,7 +3906,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>15</v>
+        <v>497</v>
       </c>
     </row>
     <row r="292" ht="22" customHeight="true" outlineLevel="3">
@@ -3590,7 +3914,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>162</v>
+        <v>9</v>
       </c>
     </row>
     <row r="293" ht="22" customHeight="true" outlineLevel="3">
@@ -3598,15 +3922,15 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>341</v>
+        <v>393</v>
       </c>
     </row>
     <row r="294" ht="22" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="16" t="n">
-        <v>9636</v>
+      <c r="C294" s="11" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="295" ht="22" customHeight="true" outlineLevel="3">
@@ -3614,15 +3938,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>429</v>
+        <v>15</v>
       </c>
     </row>
     <row r="296" ht="22" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="16" t="n">
-        <v>2526</v>
+      <c r="C296" s="11" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="true" outlineLevel="3">
@@ -3630,71 +3954,71 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="16" t="n">
-        <v>6953</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C298" s="11" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="16" t="n">
-        <v>3126</v>
+      <c r="C302" s="11" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="11" t="n">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C303" s="16" t="n">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="11" t="n">
-        <v>5</v>
+      <c r="C305" s="16" t="n">
+        <v>1456</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -3702,7 +4026,7 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>135</v>
+        <v>468</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -3710,39 +4034,39 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="308" ht="22" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="true" outlineLevel="3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>657</v>
+        <v>304</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -3750,79 +4074,79 @@
         <v>311</v>
       </c>
       <c r="C312" s="16" t="n">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="11" t="n">
-        <v>640</v>
+      <c r="C313" s="16" t="n">
+        <v>2648</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C314" s="16" t="n">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="315" ht="22" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="true" outlineLevel="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B317" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B317" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="11" t="n">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C317" s="12" t="n">
+        <v>21106</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="11" t="n">
-        <v>180</v>
+      <c r="C318" s="16" t="n">
+        <v>1030</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="11" t="n">
-        <v>223</v>
+      <c r="C319" s="16" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="16" t="n">
-        <v>2487</v>
-      </c>
-    </row>
-    <row r="321" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C320" s="11" t="n">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="16" t="n">
-        <v>1115</v>
+      <c r="C321" s="11" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -3830,7 +4154,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>320</v>
+        <v>186</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -3838,7 +4162,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>4</v>
+        <v>223</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -3846,31 +4170,31 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="325" ht="22" customHeight="true" outlineLevel="3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="16" t="n">
-        <v>1258</v>
+      <c r="C325" s="11" t="n">
+        <v>382</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C326" s="16" t="n">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="16" t="n">
-        <v>1766</v>
+      <c r="C327" s="11" t="n">
+        <v>342</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -3878,15 +4202,15 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>124</v>
+        <v>276</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="16" t="n">
-        <v>1718</v>
+      <c r="C329" s="11" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -3894,7 +4218,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>201</v>
+        <v>571</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -3902,7 +4226,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>10</v>
+        <v>413</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -3910,7 +4234,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>612</v>
+        <v>411</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -3918,7 +4242,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>10</v>
+        <v>307</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -3926,7 +4250,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>359</v>
+        <v>546</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -3934,31 +4258,879 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="336" ht="22" customHeight="true" outlineLevel="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>685</v>
+        <v>188</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="16" t="n">
-        <v>2259</v>
-      </c>
-    </row>
-    <row r="338" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C337" s="11" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="C338" s="16" t="n">
-        <v>3973</v>
+      <c r="C338" s="11" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B339" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C339" s="16" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B340" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="C340" s="11" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B341" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="C341" s="11" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B342" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C342" s="11" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B343" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="C343" s="11" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B344" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C344" s="11" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B345" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C345" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B346" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C346" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B347" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B348" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C348" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B349" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C349" s="11" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B350" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C350" s="11" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B351" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="C351" s="16" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C352" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B353" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C353" s="16" t="n">
+        <v>3277</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B354" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C354" s="16" t="n">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B355" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C355" s="11" t="n">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B356" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C356" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B357" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C357" s="17" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B358" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="C358" s="11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B359" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="C359" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B360" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C360" s="12" t="n">
+        <v>92053</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B361" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C361" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B362" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C362" s="11" t="n">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B363" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="C363" s="11" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B364" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C364" s="11" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B365" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C365" s="11" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B366" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C366" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="367" ht="33" customHeight="true" outlineLevel="3">
+      <c r="B367" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C367" s="16" t="n">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="368" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B368" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C368" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B369" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="C369" s="11" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B370" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C370" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="371" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B371" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C371" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B372" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C372" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B373" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C373" s="16" t="n">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B374" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C374" s="11" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B375" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C375" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B376" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C376" s="16" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B377" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C377" s="11" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B378" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C378" s="11" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B379" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C379" s="16" t="n">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B380" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C380" s="11" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B381" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C381" s="11" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B382" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C382" s="11" t="n">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B383" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C383" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B384" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C384" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B385" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C385" s="16" t="n">
+        <v>4685</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B386" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C386" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B387" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C387" s="11" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B388" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C388" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B389" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C389" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B390" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C390" s="16" t="n">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="391" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B391" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C391" s="11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B392" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="16" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B393" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C393" s="11" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B394" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C394" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B395" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="16" t="n">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="396" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B396" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C396" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B397" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C397" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B398" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C398" s="16" t="n">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="399" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B399" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="C399" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B400" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C400" s="16" t="n">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C401" s="11" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B402" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C402" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B403" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C403" s="16" t="n">
+        <v>7597</v>
+      </c>
+    </row>
+    <row r="404" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C404" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B406" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C406" s="16" t="n">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B407" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C407" s="11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="11" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="16" t="n">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="11" t="n">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="11" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="11" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="419" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="16" t="n">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="11" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="423" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="16" t="n">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="11" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B430" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B431" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="432" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B432" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B433" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B434" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="11" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B435" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="11" t="n">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B436" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="11" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="437" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B437" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="11" t="n">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="438" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B438" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="12" t="n">
+        <v>35283</v>
+      </c>
+    </row>
+    <row r="439" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B439" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="440" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B440" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="16" t="n">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="441" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B441" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="16" t="n">
+        <v>21315</v>
+      </c>
+    </row>
+    <row r="442" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B442" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="16" t="n">
+        <v>7776</v>
+      </c>
+    </row>
+    <row r="443" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B443" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="16" t="n">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="444" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B444" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="16" t="n">
+        <v>2140</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="495">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 14.10.2025 15:55:17</t>
+    <t>Период: на 02.12.2025 15:35:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -71,27 +71,51 @@
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Какао-порошок 100г/40 УБ</t>
   </si>
   <si>
@@ -122,6 +146,9 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
@@ -131,21 +158,33 @@
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
@@ -155,9 +194,6 @@
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
-    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
@@ -176,9 +212,15 @@
     <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Суміш зелені УБ 10г /24шт</t>
+  </si>
+  <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -191,12 +233,18 @@
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
+    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Часник гранульований сушений УБ 15г /42шт</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -239,10 +287,13 @@
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців Класична УБ 30г /24шт</t>
+    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>РОШЕН</t>
@@ -254,31 +305,34 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
@@ -287,13 +341,25 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
@@ -326,9 +392,15 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -359,12 +431,18 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
     <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -395,21 +473,9 @@
     <t>Wafers горіх ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers горіх ККФ 216г /16шт</t>
-  </si>
-  <si>
-    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Wafers какао ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -473,9 +539,6 @@
     <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -485,10 +548,7 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
@@ -500,6 +560,9 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -524,31 +587,40 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
@@ -557,19 +629,25 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
@@ -584,6 +662,9 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -596,6 +677,9 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -608,13 +692,19 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
@@ -623,12 +713,18 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -644,6 +740,9 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -686,9 +785,6 @@
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>CoffeeLike ВКФ 1кг /7пак /</t>
-  </si>
-  <si>
     <t>CoffeeLike КрКФ 1кг /7пак /</t>
   </si>
   <si>
@@ -767,12 +863,12 @@
     <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Молочна крапля КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Рачки ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Рошен джус мікс РЦ 1кг /8пак /</t>
-  </si>
-  <si>
     <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
   </si>
   <si>
@@ -803,15 +899,15 @@
     <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 256г /8шт</t>
-  </si>
-  <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -827,6 +923,9 @@
     <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 352г /7шт</t>
+  </si>
+  <si>
     <t>Стріла Подільска 200г/10</t>
   </si>
   <si>
@@ -887,9 +986,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -923,6 +1019,9 @@
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
+    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
@@ -944,6 +1043,9 @@
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
   </si>
   <si>
@@ -965,7 +1067,40 @@
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
+    <t>ПОДАРУНКИ</t>
+  </si>
+  <si>
+    <t>ПОДАРУНКИ 2026</t>
+  </si>
+  <si>
+    <t>Н/п №1 26 Солодка хатинка РЦ 274г /10шт UA+GR</t>
+  </si>
+  <si>
+    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
+  </si>
+  <si>
+    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
+  </si>
+  <si>
+    <t>Н/п №4 26 Новорічна ялинка РЦ 388г /9шт</t>
+  </si>
+  <si>
+    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №9 26 Різдвяний вінок РЦ 598г /6шт</t>
   </si>
   <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
@@ -974,12 +1109,12 @@
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
+    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -995,36 +1130,18 @@
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>KONAFETTO blanc ВКФ 1кг /5пак /</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -1034,9 +1151,6 @@
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1052,24 +1166,39 @@
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
+    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
@@ -1085,6 +1214,9 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1109,13 +1241,10 @@
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
@@ -1124,43 +1253,34 @@
     <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
@@ -1184,63 +1304,75 @@
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1250,6 +1382,9 @@
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
@@ -1259,25 +1394,31 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
-  </si>
-  <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
@@ -1289,21 +1430,39 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
@@ -1328,13 +1487,7 @@
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Кролик Roshen зимовий ВКФ 100г /12шт</t>
   </si>
   <si>
     <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
@@ -1601,7 +1754,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C444"/>
+  <dimension ref="C495"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1666,7 +1819,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>116</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1674,7 +1827,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>314976</v>
+        <v>331127</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1682,7 +1835,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>67230</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1690,7 +1843,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>9794</v>
+        <v>7887</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1698,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>393</v>
+        <v>620</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1706,7 +1859,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>56</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1714,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>732</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1722,31 +1875,31 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>1545</v>
+      <c r="C19" s="11" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>56</v>
+      <c r="C20" s="16" t="n">
+        <v>1070</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
       <c r="B21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>1624</v>
+      <c r="C21" s="11" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1754,7 +1907,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>86</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1762,7 +1915,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>904</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1770,7 +1923,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>864</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1778,7 +1931,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>834</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1786,63 +1939,63 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>102</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>174</v>
+      <c r="C27" s="16" t="n">
+        <v>1165</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="29" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B29" s="14" t="s">
+      <c r="C28" s="11" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>18569</v>
+      <c r="C29" s="11" t="n">
+        <v>448</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="16" t="n">
-        <v>2302</v>
+      <c r="C30" s="11" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>6100</v>
+      <c r="C31" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>1100</v>
+      <c r="C32" s="11" t="n">
+        <v>243</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="n">
-        <v>6606</v>
+      <c r="C33" s="11" t="n">
+        <v>227</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1850,7 +2003,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>480</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1858,7 +2011,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>893</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1866,47 +2019,47 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B37" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B37" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="16" t="n">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="38" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B38" s="14" t="s">
+      <c r="C37" s="12" t="n">
+        <v>22791</v>
+      </c>
+    </row>
+    <row r="38" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="12" t="n">
-        <v>10111</v>
+      <c r="C38" s="16" t="n">
+        <v>4310</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>810</v>
+      <c r="C39" s="16" t="n">
+        <v>6498</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>851</v>
+      <c r="C40" s="16" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>284</v>
+      <c r="C41" s="16" t="n">
+        <v>4174</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -1914,15 +2067,15 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>238</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="16" t="n">
-        <v>1484</v>
+      <c r="C43" s="11" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1930,7 +2083,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>240</v>
+        <v>794</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1938,7 +2091,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1946,23 +2099,23 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>50</v>
+        <v>504</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>118</v>
+      <c r="C47" s="16" t="n">
+        <v>1629</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>150</v>
+      <c r="C48" s="16" t="n">
+        <v>1535</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1970,23 +2123,23 @@
         <v>48</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="50" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B50" s="15" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="50" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B50" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>136</v>
+      <c r="C50" s="12" t="n">
+        <v>8409</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="16" t="n">
-        <v>1025</v>
+      <c r="C51" s="11" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1994,7 +2147,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>125</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2002,7 +2155,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2010,15 +2163,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2026,7 +2179,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>573</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2034,7 +2187,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>875</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2042,23 +2195,23 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>54</v>
+        <v>599</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="60" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B60" s="14" t="s">
+      <c r="C59" s="11" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="12" t="n">
-        <v>28756</v>
+      <c r="C60" s="11" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2066,47 +2219,47 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>170</v>
+        <v>567</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>1306</v>
+      <c r="C62" s="11" t="n">
+        <v>173</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="16" t="n">
-        <v>1307</v>
+      <c r="C63" s="11" t="n">
+        <v>567</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>1578</v>
+      <c r="C64" s="11" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>4334</v>
+      <c r="C65" s="11" t="n">
+        <v>871</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>1652</v>
+      <c r="C66" s="11" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -2114,23 +2267,23 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>959</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="16" t="n">
-        <v>2238</v>
-      </c>
-    </row>
-    <row r="69" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C68" s="11" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>9</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2138,23 +2291,23 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>792</v>
+        <v>741</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>4699</v>
+      <c r="C71" s="11" t="n">
+        <v>127</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="16" t="n">
-        <v>8633</v>
+      <c r="C72" s="11" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2162,15 +2315,15 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>305</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>597</v>
+      <c r="C74" s="16" t="n">
+        <v>1053</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2178,31 +2331,31 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="76" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B76" s="13" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="76" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B76" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>247746</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B77" s="14" t="s">
+        <v>13113</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="12" t="n">
-        <v>20632</v>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C77" s="11" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="16" t="n">
-        <v>3111</v>
+      <c r="C78" s="11" t="n">
+        <v>251</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2210,15 +2363,15 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>611</v>
+        <v>542</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>1110</v>
+      <c r="C80" s="11" t="n">
+        <v>452</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2226,279 +2379,279 @@
         <v>80</v>
       </c>
       <c r="C81" s="16" t="n">
-        <v>1860</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C82" s="11" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C84" s="16" t="n">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="true" outlineLevel="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C87" s="16" t="n">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
       <c r="C88" s="16" t="n">
-        <v>4820</v>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="true" outlineLevel="3">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="16" t="n">
-        <v>3666</v>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C89" s="11" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="91" ht="22" customHeight="true" outlineLevel="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="92" ht="22" customHeight="true" outlineLevel="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B93" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B93" s="13" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="12" t="n">
-        <v>6874</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B94" s="15" t="s">
+        <v>278927</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B94" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="11" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C94" s="12" t="n">
+        <v>85853</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C96" s="16" t="n">
+        <v>11351</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>685</v>
+      <c r="C97" s="16" t="n">
+        <v>4590</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>1630</v>
+      <c r="C98" s="11" t="n">
+        <v>521</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>72</v>
+      <c r="C99" s="16" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="16" t="n">
+        <v>9928</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C102" s="16" t="n">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>115</v>
+      <c r="C104" s="16" t="n">
+        <v>12930</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B106" s="14" t="s">
+      <c r="C105" s="16" t="n">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="12" t="n">
-        <v>43602</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C106" s="16" t="n">
+        <v>7848</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C108" s="16" t="n">
+        <v>8130</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C109" s="16" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C111" s="16" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="11" t="n">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="113" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C112" s="16" t="n">
+        <v>6462</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
       <c r="C113" s="16" t="n">
-        <v>8157</v>
-      </c>
-    </row>
-    <row r="114" ht="11" customHeight="true" outlineLevel="3">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="true" outlineLevel="3">
       <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
       <c r="C114" s="16" t="n">
-        <v>10970</v>
-      </c>
-    </row>
-    <row r="115" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B115" s="15" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="115" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B115" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="16" t="n">
-        <v>8585</v>
+      <c r="C115" s="12" t="n">
+        <v>9315</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2506,7 +2659,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="16" t="n">
-        <v>8690</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2514,7 +2667,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2522,7 +2675,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>43</v>
+        <v>511</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2530,7 +2683,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>30</v>
+        <v>783</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2538,7 +2691,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>30</v>
+        <v>632</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2546,7 +2699,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2554,7 +2707,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>232</v>
+        <v>785</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2562,7 +2715,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>154</v>
+        <v>539</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2570,15 +2723,15 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>74</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>413</v>
+      <c r="C125" s="16" t="n">
+        <v>1283</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2586,15 +2739,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>530</v>
+      <c r="C127" s="16" t="n">
+        <v>1240</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2602,23 +2755,23 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" ht="11" customHeight="true" outlineLevel="3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="true" outlineLevel="3">
       <c r="B129" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B130" s="15" t="s">
+      <c r="C129" s="16" t="n">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B130" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>3</v>
+      <c r="C130" s="12" t="n">
+        <v>16441</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2626,7 +2779,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>399</v>
+        <v>197</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2634,7 +2787,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>257</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2642,7 +2795,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>385</v>
+        <v>137</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2650,7 +2803,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>235</v>
+        <v>37</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2658,7 +2811,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>434</v>
+        <v>359</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2666,7 +2819,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>27</v>
+        <v>184</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2674,7 +2827,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="16" t="n">
-        <v>1663</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2682,7 +2835,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>46</v>
+        <v>175</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2690,31 +2843,31 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>243</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="141" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B141" s="14" t="s">
+      <c r="C140" s="16" t="n">
+        <v>5385</v>
+      </c>
+    </row>
+    <row r="141" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B141" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="12" t="n">
-        <v>20719</v>
+      <c r="C141" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>60</v>
+      <c r="C142" s="16" t="n">
+        <v>2140</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2722,7 +2875,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2730,7 +2883,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2738,7 +2891,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2746,7 +2899,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2754,7 +2907,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2762,7 +2915,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>67</v>
+        <v>158</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2770,7 +2923,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>191</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2778,7 +2931,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>118</v>
+        <v>302</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2786,7 +2939,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>190</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2794,7 +2947,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>14</v>
+        <v>585</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2802,7 +2955,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>507</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2810,7 +2963,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>741</v>
+        <v>78</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2818,7 +2971,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>19</v>
+        <v>135</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2826,7 +2979,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2834,7 +2987,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2842,7 +2995,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>676</v>
+        <v>65</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2850,7 +3003,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>741</v>
+        <v>706</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2858,7 +3011,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2866,7 +3019,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>57</v>
+        <v>730</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2874,15 +3027,15 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B163" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B163" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="11" t="n">
-        <v>7</v>
+      <c r="C163" s="12" t="n">
+        <v>40734</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2890,7 +3043,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>440</v>
+        <v>228</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2898,7 +3051,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2906,7 +3059,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2914,7 +3067,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>742</v>
+        <v>87</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2922,7 +3075,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2930,7 +3083,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>177</v>
+        <v>121</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2938,7 +3091,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2946,7 +3099,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2954,7 +3107,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2962,15 +3115,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>522</v>
+        <v>45</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>429</v>
+      <c r="C174" s="16" t="n">
+        <v>1156</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2978,7 +3131,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>329</v>
+        <v>391</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2986,15 +3139,15 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>593</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>7</v>
+      <c r="C177" s="16" t="n">
+        <v>1438</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3002,7 +3155,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>990</v>
+        <v>132</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3010,7 +3163,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>550</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3018,15 +3171,15 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="11" t="n">
-        <v>386</v>
+      <c r="C181" s="16" t="n">
+        <v>2285</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3034,15 +3187,15 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>11</v>
+        <v>317</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="16" t="n">
-        <v>2070</v>
+      <c r="C183" s="11" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3050,7 +3203,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>11</v>
+        <v>808</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3058,7 +3211,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3066,7 +3219,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -3074,7 +3227,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="16" t="n">
-        <v>2672</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3082,7 +3235,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3090,15 +3243,15 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>658</v>
+        <v>37</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="11" t="n">
-        <v>36</v>
+      <c r="C190" s="16" t="n">
+        <v>1384</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3106,7 +3259,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3114,15 +3267,15 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>34</v>
+        <v>234</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>199</v>
+      <c r="C193" s="16" t="n">
+        <v>1031</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3130,7 +3283,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>473</v>
+        <v>818</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3138,7 +3291,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3146,7 +3299,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>331</v>
+        <v>965</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3154,7 +3307,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>547</v>
+        <v>704</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3162,7 +3315,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>382</v>
+        <v>56</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3170,7 +3323,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>963</v>
+        <v>745</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3178,7 +3331,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>293</v>
+        <v>82</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3186,7 +3339,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3194,7 +3347,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>123</v>
+        <v>426</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3202,15 +3355,15 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="204" ht="11" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>134</v>
+        <v>714</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3218,7 +3371,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>376</v>
+        <v>110</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3226,7 +3379,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3234,15 +3387,15 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="208" ht="11" customHeight="true" outlineLevel="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="true" outlineLevel="3">
       <c r="B208" s="15" t="s">
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3250,15 +3403,15 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="210" ht="11" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>356</v>
+      <c r="C210" s="16" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3266,7 +3419,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>23</v>
+        <v>220</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3274,15 +3427,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>30</v>
+      <c r="C213" s="16" t="n">
+        <v>1047</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3290,15 +3443,15 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>228</v>
+        <v>205</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="11" t="n">
-        <v>34</v>
+      <c r="C215" s="16" t="n">
+        <v>2481</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3306,7 +3459,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>59</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3314,7 +3467,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>126</v>
+        <v>729</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3322,15 +3475,15 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="219" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B219" s="14" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="219" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="12" t="n">
-        <v>17291</v>
+      <c r="C219" s="11" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3338,7 +3491,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>537</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3346,7 +3499,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>539</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3354,7 +3507,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>517</v>
+        <v>266</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3362,7 +3515,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>136</v>
+        <v>424</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3370,7 +3523,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>63</v>
+        <v>768</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3378,15 +3531,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>440</v>
+        <v>692</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="16" t="n">
-        <v>1436</v>
+      <c r="C226" s="11" t="n">
+        <v>717</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3394,7 +3547,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>22</v>
+        <v>124</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3402,15 +3555,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>74</v>
+        <v>463</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>43</v>
+      <c r="C229" s="16" t="n">
+        <v>1300</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3418,23 +3571,23 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>112</v>
+        <v>290</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="11" t="n">
-        <v>533</v>
+      <c r="C231" s="16" t="n">
+        <v>2167</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>7</v>
+      <c r="C232" s="16" t="n">
+        <v>1336</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3442,7 +3595,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>27</v>
+        <v>960</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3450,15 +3603,15 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>511</v>
+        <v>40</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="11" t="n">
-        <v>467</v>
+      <c r="C235" s="16" t="n">
+        <v>1045</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3466,7 +3619,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>573</v>
+        <v>734</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3474,7 +3627,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>473</v>
+        <v>373</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3482,7 +3635,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>784</v>
+        <v>443</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3490,7 +3643,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>212</v>
+        <v>164</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3498,15 +3651,15 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>486</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>206</v>
+      <c r="C241" s="16" t="n">
+        <v>1454</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3514,7 +3667,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>128</v>
+        <v>279</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3530,15 +3683,15 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>475</v>
+        <v>451</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="16" t="n">
-        <v>1254</v>
+      <c r="C245" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3546,7 +3699,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>800</v>
+        <v>387</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3554,7 +3707,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>449</v>
+        <v>193</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3562,7 +3715,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>744</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3570,15 +3723,15 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>750</v>
+        <v>35</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="16" t="n">
-        <v>1075</v>
+      <c r="C250" s="11" t="n">
+        <v>270</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3586,15 +3739,15 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="252" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B252" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B252" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>959</v>
+      <c r="C252" s="12" t="n">
+        <v>19970</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3602,7 +3755,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>40</v>
+        <v>576</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3610,7 +3763,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>814</v>
+        <v>213</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3618,15 +3771,15 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="256" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B256" s="14" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="256" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="12" t="n">
-        <v>1094</v>
+      <c r="C256" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3634,15 +3787,15 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>42</v>
+        <v>177</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>129</v>
+      <c r="C258" s="16" t="n">
+        <v>2540</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3650,7 +3803,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3658,7 +3811,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3666,7 +3819,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>81</v>
+        <v>408</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3674,7 +3827,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3682,7 +3835,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>200</v>
+        <v>324</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3690,7 +3843,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3698,7 +3851,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>44</v>
+        <v>113</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3706,7 +3859,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>40</v>
+        <v>821</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3714,7 +3867,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>127</v>
+        <v>198</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3722,7 +3875,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>95</v>
+        <v>583</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3730,7 +3883,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>67</v>
+        <v>476</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3738,15 +3891,15 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B271" s="14" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="12" t="n">
-        <v>24280</v>
+      <c r="C271" s="11" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3754,7 +3907,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3762,7 +3915,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>590</v>
+        <v>368</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3770,7 +3923,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>11</v>
+        <v>209</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3778,7 +3931,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>703</v>
+        <v>782</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3786,15 +3939,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>228</v>
+        <v>277</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="11" t="n">
-        <v>721</v>
+      <c r="C277" s="16" t="n">
+        <v>1740</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3802,15 +3955,15 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>907</v>
+        <v>808</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="16" t="n">
-        <v>1241</v>
+      <c r="C279" s="11" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3818,15 +3971,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>67</v>
+        <v>210</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3834,23 +3987,23 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>29</v>
+        <v>594</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>63</v>
+      <c r="C283" s="16" t="n">
+        <v>1237</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="11" t="n">
-        <v>278</v>
+      <c r="C284" s="16" t="n">
+        <v>1074</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3858,7 +4011,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>588</v>
+        <v>379</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3866,7 +4019,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="16" t="n">
-        <v>1173</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3874,87 +4027,87 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B288" s="15" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B288" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="11" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="289" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C288" s="12" t="n">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="290" ht="22" customHeight="true" outlineLevel="3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="291" ht="22" customHeight="true" outlineLevel="3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="292" ht="22" customHeight="true" outlineLevel="3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="293" ht="22" customHeight="true" outlineLevel="3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="294" ht="22" customHeight="true" outlineLevel="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="true" outlineLevel="3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="true" outlineLevel="3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>31</v>
+        <v>280</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3962,7 +4115,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3970,7 +4123,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>40</v>
+        <v>107</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3978,7 +4131,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>54</v>
+        <v>114</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3986,7 +4139,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3994,31 +4147,31 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>71</v>
+        <v>126</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="16" t="n">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="304" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B304" s="15" t="s">
+      <c r="C303" s="11" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B304" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="11" t="n">
-        <v>16</v>
+      <c r="C304" s="12" t="n">
+        <v>17448</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="16" t="n">
-        <v>1456</v>
+      <c r="C305" s="11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -4026,7 +4179,7 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>468</v>
+        <v>264</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4034,7 +4187,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4042,7 +4195,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>643</v>
+        <v>99</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4050,7 +4203,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>152</v>
+        <v>228</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -4058,7 +4211,7 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>7</v>
+        <v>447</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -4066,39 +4219,39 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>304</v>
+        <v>419</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="16" t="n">
-        <v>4772</v>
+      <c r="C312" s="11" t="n">
+        <v>205</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="16" t="n">
-        <v>2648</v>
-      </c>
-    </row>
-    <row r="314" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C313" s="11" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="16" t="n">
-        <v>2721</v>
-      </c>
-    </row>
-    <row r="315" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C314" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>47</v>
+        <v>278</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4106,39 +4259,39 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B317" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="12" t="n">
-        <v>21106</v>
+      <c r="C317" s="11" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="16" t="n">
-        <v>1030</v>
+      <c r="C318" s="11" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="16" t="n">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C319" s="11" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>661</v>
+        <v>54</v>
       </c>
     </row>
     <row r="321" ht="22" customHeight="true" outlineLevel="3">
@@ -4146,71 +4299,71 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="323" ht="22" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="325" ht="11" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="325" ht="22" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="16" t="n">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="327" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C326" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="328" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="329" ht="11" customHeight="true" outlineLevel="3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>126</v>
+        <v>32</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4218,7 +4371,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>571</v>
+        <v>257</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4226,7 +4379,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>413</v>
+        <v>136</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4234,7 +4387,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>411</v>
+        <v>54</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4242,7 +4395,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>307</v>
+        <v>92</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4250,7 +4403,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>546</v>
+        <v>36</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4258,7 +4411,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>113</v>
+        <v>20</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4266,15 +4419,15 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>308</v>
+        <v>16</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4282,15 +4435,15 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="16" t="n">
-        <v>1388</v>
+      <c r="C339" s="11" t="n">
+        <v>775</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4298,7 +4451,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>621</v>
+        <v>30</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4306,7 +4459,7 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>179</v>
+        <v>216</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4314,7 +4467,7 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>409</v>
+        <v>695</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4322,7 +4475,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>615</v>
+        <v>151</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4330,7 +4483,7 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>310</v>
+        <v>7</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4338,15 +4491,15 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>9</v>
+        <v>266</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="11" t="n">
-        <v>16</v>
+      <c r="C346" s="16" t="n">
+        <v>5282</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4354,127 +4507,127 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>60</v>
+        <v>709</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C348" s="16" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B350" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B350" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>45</v>
+      <c r="C350" s="17" t="n">
+        <v>837</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B351" s="15" t="s">
+      <c r="B351" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="16" t="n">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B352" s="15" t="s">
+      <c r="C351" s="17" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B352" s="19" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B353" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B353" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="C353" s="16" t="n">
-        <v>3277</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B354" s="15" t="s">
+      <c r="C353" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B354" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="16" t="n">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B355" s="15" t="s">
+      <c r="C354" s="11" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B355" s="19" t="s">
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B356" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B356" s="19" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B357" s="14" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B357" s="19" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="17" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B358" s="15" t="s">
+      <c r="C357" s="11" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B358" s="19" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B359" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B359" s="19" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B360" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B360" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="12" t="n">
-        <v>92053</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B361" s="15" t="s">
+      <c r="C360" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B361" s="19" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B362" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B362" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="11" t="n">
-        <v>963</v>
+      <c r="C362" s="12" t="n">
+        <v>16614</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4482,7 +4635,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>122</v>
+        <v>958</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4490,15 +4643,15 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="11" t="n">
-        <v>378</v>
+      <c r="C365" s="16" t="n">
+        <v>1728</v>
       </c>
     </row>
     <row r="366" ht="22" customHeight="true" outlineLevel="3">
@@ -4506,63 +4659,63 @@
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="367" ht="33" customHeight="true" outlineLevel="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="C367" s="16" t="n">
-        <v>4339</v>
-      </c>
-    </row>
-    <row r="368" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C367" s="11" t="n">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="371" ht="22" customHeight="true" outlineLevel="3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="16" t="n">
-        <v>1094</v>
+      <c r="C373" s="11" t="n">
+        <v>435</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
@@ -4570,7 +4723,7 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>255</v>
+        <v>394</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4578,39 +4731,39 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="16" t="n">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="377" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C376" s="11" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="16" t="n">
-        <v>3931</v>
+      <c r="C379" s="11" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="380" ht="11" customHeight="true" outlineLevel="3">
@@ -4618,15 +4771,15 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>859</v>
+        <v>336</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4634,7 +4787,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>751</v>
+        <v>879</v>
       </c>
     </row>
     <row r="383" ht="11" customHeight="true" outlineLevel="3">
@@ -4642,7 +4795,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>8</v>
+        <v>273</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4650,31 +4803,31 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="16" t="n">
-        <v>4685</v>
-      </c>
-    </row>
-    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C385" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
       <c r="B387" s="15" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>970</v>
+        <v>215</v>
       </c>
     </row>
     <row r="388" ht="22" customHeight="true" outlineLevel="3">
@@ -4682,23 +4835,23 @@
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="16" t="n">
-        <v>4124</v>
+      <c r="C390" s="11" t="n">
+        <v>164</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4706,15 +4859,15 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
       <c r="B392" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="C392" s="16" t="n">
-        <v>1320</v>
+      <c r="C392" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4722,111 +4875,111 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C394" s="16" t="n">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="C395" s="16" t="n">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="396" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C395" s="11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
       <c r="B396" s="15" t="s">
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="397" ht="22" customHeight="true" outlineLevel="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="398" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C397" s="16" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="16" t="n">
-        <v>2388</v>
-      </c>
-    </row>
-    <row r="399" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C398" s="11" t="n">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="3">
       <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="16" t="n">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="401" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B401" s="15" t="s">
+      <c r="C400" s="11" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B401" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="C401" s="11" t="n">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C401" s="17" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="16" t="n">
-        <v>7597</v>
-      </c>
-    </row>
-    <row r="404" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B404" s="15" t="s">
+      <c r="C403" s="11" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B404" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="C404" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C404" s="12" t="n">
+        <v>68893</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
       <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="406" ht="22" customHeight="true" outlineLevel="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="16" t="n">
-        <v>1066</v>
+      <c r="C406" s="11" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
@@ -4834,31 +4987,31 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="15" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="409" ht="22" customHeight="true" outlineLevel="3">
       <c r="B409" s="15" t="s">
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="410" ht="33" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C410" s="11" t="n">
-        <v>78</v>
+      <c r="C410" s="16" t="n">
+        <v>2097</v>
       </c>
     </row>
     <row r="411" ht="22" customHeight="true" outlineLevel="3">
@@ -4866,15 +5019,15 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="true" outlineLevel="3">
       <c r="B412" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="C412" s="16" t="n">
-        <v>1013</v>
+      <c r="C412" s="11" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="413" ht="22" customHeight="true" outlineLevel="3">
@@ -4882,7 +5035,7 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>19</v>
+        <v>197</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="true" outlineLevel="3">
@@ -4890,7 +5043,7 @@
         <v>413</v>
       </c>
       <c r="C414" s="11" t="n">
-        <v>772</v>
+        <v>97</v>
       </c>
     </row>
     <row r="415" ht="11" customHeight="true" outlineLevel="3">
@@ -4898,7 +5051,7 @@
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
     </row>
     <row r="416" ht="11" customHeight="true" outlineLevel="3">
@@ -4906,31 +5059,31 @@
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="417" ht="22" customHeight="true" outlineLevel="3">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="3">
       <c r="B417" s="15" t="s">
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
       <c r="B418" s="15" t="s">
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>229</v>
+        <v>195</v>
       </c>
     </row>
     <row r="419" ht="22" customHeight="true" outlineLevel="3">
       <c r="B419" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="C419" s="11" t="n">
-        <v>49</v>
+      <c r="C419" s="16" t="n">
+        <v>1892</v>
       </c>
     </row>
     <row r="420" ht="11" customHeight="true" outlineLevel="3">
@@ -4938,23 +5091,23 @@
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="3">
       <c r="B421" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="C421" s="16" t="n">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="422" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C421" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="3">
       <c r="B422" s="15" t="s">
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="423" ht="11" customHeight="true" outlineLevel="3">
@@ -4962,23 +5115,23 @@
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>395</v>
+        <v>162</v>
       </c>
     </row>
     <row r="424" ht="11" customHeight="true" outlineLevel="3">
       <c r="B424" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="C424" s="16" t="n">
-        <v>4562</v>
+      <c r="C424" s="11" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="425" ht="11" customHeight="true" outlineLevel="3">
       <c r="B425" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="C425" s="11" t="n">
-        <v>130</v>
+      <c r="C425" s="16" t="n">
+        <v>2861</v>
       </c>
     </row>
     <row r="426" ht="22" customHeight="true" outlineLevel="3">
@@ -4986,87 +5139,87 @@
         <v>425</v>
       </c>
       <c r="C426" s="11" t="n">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
       <c r="B427" s="15" t="s">
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="15" t="s">
         <v>427</v>
       </c>
       <c r="C428" s="11" t="n">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
       <c r="B429" s="15" t="s">
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="430" ht="22" customHeight="true" outlineLevel="3">
       <c r="B430" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="C430" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C430" s="16" t="n">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
       <c r="B431" s="15" t="s">
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="432" ht="11" customHeight="true" outlineLevel="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="432" ht="22" customHeight="true" outlineLevel="3">
       <c r="B432" s="15" t="s">
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
       <c r="B433" s="15" t="s">
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="434" ht="22" customHeight="true" outlineLevel="3">
       <c r="B434" s="15" t="s">
         <v>433</v>
       </c>
       <c r="C434" s="11" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="435" ht="22" customHeight="true" outlineLevel="3">
       <c r="B435" s="15" t="s">
         <v>434</v>
       </c>
       <c r="C435" s="11" t="n">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="436" ht="22" customHeight="true" outlineLevel="3">
       <c r="B436" s="15" t="s">
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>251</v>
+        <v>304</v>
       </c>
     </row>
     <row r="437" ht="22" customHeight="true" outlineLevel="3">
@@ -5074,63 +5227,471 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="438" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B438" s="18" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="438" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B438" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="12" t="n">
-        <v>35283</v>
-      </c>
-    </row>
-    <row r="439" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B439" s="19" t="s">
+      <c r="C438" s="11" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B439" s="15" t="s">
         <v>438</v>
       </c>
       <c r="C439" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="440" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B440" s="19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B440" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="C440" s="16" t="n">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="441" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B441" s="19" t="s">
+      <c r="C440" s="11" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B441" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="C441" s="16" t="n">
-        <v>21315</v>
-      </c>
-    </row>
-    <row r="442" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B442" s="19" t="s">
+      <c r="C441" s="11" t="n">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="442" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B442" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="C442" s="16" t="n">
-        <v>7776</v>
-      </c>
-    </row>
-    <row r="443" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B443" s="19" t="s">
+      <c r="C442" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="443" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B443" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="C443" s="16" t="n">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="444" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B444" s="19" t="s">
+      <c r="C443" s="11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="444" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B444" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="C444" s="16" t="n">
-        <v>2140</v>
+      <c r="C444" s="11" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="445" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B445" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="11" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="446" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B446" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="11" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="447" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B447" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="16" t="n">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="448" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B448" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="449" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B449" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="450" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B450" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="451" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B451" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="11" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="452" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B452" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="11" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="453" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B453" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="11" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="454" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B454" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B455" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="11" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B456" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="457" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B457" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="11" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B458" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="459" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B459" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B460" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="16" t="n">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B461" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="11" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B462" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="11" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B463" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="16" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B464" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="465" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B465" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="16" t="n">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="466" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B466" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C466" s="11" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="467" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B467" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="16" t="n">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B468" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="469" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B469" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="11" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="470" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B470" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="11" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="471" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B471" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C471" s="11" t="n">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B472" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C472" s="16" t="n">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="473" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B473" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="C473" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="474" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B474" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C474" s="11" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="475" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B475" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="C475" s="11" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="476" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B476" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C476" s="11" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B477" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="C477" s="16" t="n">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B478" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="C478" s="11" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="479" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B479" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="C479" s="11" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="480" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B480" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="C480" s="16" t="n">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="481" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B481" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="C481" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="482" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B482" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C482" s="11" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="483" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B483" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="C483" s="11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="484" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B484" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="C484" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="485" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B485" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C485" s="11" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="486" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B486" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C486" s="11" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="487" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B487" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C487" s="11" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="488" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B488" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="C488" s="16" t="n">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="489" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B489" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C489" s="11" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="490" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B490" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="C490" s="12" t="n">
+        <v>18808</v>
+      </c>
+    </row>
+    <row r="491" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B491" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="C491" s="11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="492" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B492" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="C492" s="16" t="n">
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="493" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B493" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="C493" s="16" t="n">
+        <v>8448</v>
+      </c>
+    </row>
+    <row r="494" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B494" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="C494" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="495" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B495" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="C495" s="11" t="n">
+        <v>780</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 02.12.2025 15:35:13</t>
+    <t>Период: на 23.12.2025 16:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -65,16 +65,13 @@
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Желе апельсин УБ 78г /56шт</t>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ОПТ</t>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе вишня УБ 78г /56шт</t>
@@ -83,9 +80,6 @@
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
@@ -119,12 +113,6 @@
     <t>Какао-порошок 100г/40 УБ</t>
   </si>
   <si>
-    <t>Какао-порошок 22% УБ 60г /26шт</t>
-  </si>
-  <si>
-    <t>Какао-порошок УБ 100г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
@@ -146,12 +134,18 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
   </si>
   <si>
@@ -296,6 +290,9 @@
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Суміш перців Класична УБ 30г /24шт</t>
+  </si>
+  <si>
     <t>РОШЕН</t>
   </si>
   <si>
@@ -314,9 +311,6 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -338,9 +332,6 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -365,12 +356,6 @@
     <t>БІСКВІТИ</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
-  </si>
-  <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -380,9 +365,6 @@
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
-    <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>РУЛЕТ П'янка вишня ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -437,9 +419,6 @@
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -452,9 +431,6 @@
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -473,6 +449,9 @@
     <t>Wafers горіх ВКФ 72г /22шт AR /</t>
   </si>
   <si>
+    <t>Wafers горіх ККФ 216г /16шт</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
@@ -488,9 +467,6 @@
     <t>Wafers лимон ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
@@ -503,9 +479,6 @@
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -608,9 +581,6 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
@@ -668,18 +638,12 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -692,9 +656,6 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -707,6 +668,9 @@
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
@@ -731,7 +695,7 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
@@ -749,9 +713,6 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -785,9 +746,6 @@
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>CoffeeLike КрКФ 1кг /7пак /</t>
-  </si>
-  <si>
     <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
@@ -809,9 +767,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -869,6 +824,9 @@
     <t>Рачки ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Рошен джус мікс РЦ 1кг /8пак /</t>
+  </si>
+  <si>
     <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
   </si>
   <si>
@@ -893,7 +851,7 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW</t>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
@@ -944,9 +902,6 @@
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
   </si>
   <si>
@@ -1028,18 +983,12 @@
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -1073,9 +1022,6 @@
     <t>ПОДАРУНКИ 2026</t>
   </si>
   <si>
-    <t>Н/п №1 26 Солодка хатинка РЦ 274г /10шт UA+GR</t>
-  </si>
-  <si>
     <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
   </si>
   <si>
@@ -1085,24 +1031,12 @@
     <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
   </si>
   <si>
-    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №4 26 Новорічна ялинка РЦ 388г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
-  </si>
-  <si>
     <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
   </si>
   <si>
     <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
   </si>
   <si>
-    <t>Н/п №9 26 Різдвяний вінок РЦ 598г /6шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
@@ -1130,18 +1064,33 @@
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -1151,21 +1100,27 @@
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
+    <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Winter dream ВКФ 1кг /5пак</t>
-  </si>
-  <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
+    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1190,15 +1145,9 @@
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
@@ -1220,6 +1169,9 @@
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -1328,9 +1280,6 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1352,13 +1301,10 @@
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
@@ -1388,9 +1334,6 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1403,36 +1346,24 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1442,27 +1373,18 @@
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
@@ -1472,9 +1394,6 @@
     <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1490,19 +1409,10 @@
     <t>ФІГУРКИ</t>
   </si>
   <si>
-    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
-  </si>
-  <si>
     <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
   </si>
   <si>
     <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1754,7 +1664,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C495"/>
+  <dimension ref="C465"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1819,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>209</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1827,7 +1737,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>331127</v>
+        <v>284090</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1835,7 +1745,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>52200</v>
+        <v>58717</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1843,7 +1753,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7887</v>
+        <v>7731</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1851,7 +1761,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>620</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1859,7 +1769,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1867,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>249</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1875,7 +1785,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>24</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1883,15 +1793,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>280</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1070</v>
+      <c r="C20" s="11" t="n">
+        <v>368</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1899,7 +1809,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>144</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1907,7 +1817,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>202</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1915,7 +1825,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>483</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1923,7 +1833,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1931,7 +1841,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>444</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1939,15 +1849,15 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="16" t="n">
-        <v>1165</v>
+      <c r="C27" s="11" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1955,7 +1865,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1963,7 +1873,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>448</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1971,7 +1881,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>405</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1979,63 +1889,63 @@
         <v>30</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>300</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="33" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B33" s="15" t="s">
+      <c r="C32" s="16" t="n">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="33" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B33" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>227</v>
+      <c r="C33" s="12" t="n">
+        <v>26936</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>342</v>
+      <c r="C34" s="16" t="n">
+        <v>1647</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>144</v>
+      <c r="C35" s="16" t="n">
+        <v>3787</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B37" s="14" t="s">
+      <c r="C36" s="16" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="12" t="n">
-        <v>22791</v>
+      <c r="C37" s="16" t="n">
+        <v>4403</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="16" t="n">
-        <v>4310</v>
+      <c r="C38" s="11" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -2043,15 +1953,15 @@
         <v>38</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>6498</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="16" t="n">
-        <v>1100</v>
+      <c r="C40" s="11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -2059,15 +1969,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>4174</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>580</v>
+      <c r="C42" s="16" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -2075,7 +1985,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -2083,23 +1993,23 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>794</v>
+        <v>824</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>1</v>
+      <c r="C45" s="16" t="n">
+        <v>1540</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>504</v>
+      <c r="C46" s="16" t="n">
+        <v>1460</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -2107,31 +2017,31 @@
         <v>46</v>
       </c>
       <c r="C47" s="16" t="n">
-        <v>1629</v>
-      </c>
-    </row>
-    <row r="48" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B48" s="15" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B48" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>1535</v>
+      <c r="C48" s="12" t="n">
+        <v>8699</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="16" t="n">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="50" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B50" s="14" t="s">
+      <c r="C49" s="11" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="50" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B50" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>8409</v>
+      <c r="C50" s="11" t="n">
+        <v>271</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2139,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>171</v>
+        <v>550</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2147,7 +2057,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>271</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2155,7 +2065,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>362</v>
+        <v>733</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2163,7 +2073,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>132</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2171,7 +2081,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>300</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2179,7 +2089,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>180</v>
+        <v>960</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2187,7 +2097,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>174</v>
+        <v>647</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2195,7 +2105,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>599</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -2203,7 +2113,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>247</v>
+        <v>335</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2211,7 +2121,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2219,7 +2129,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>567</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2227,7 +2137,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>173</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2235,7 +2145,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>567</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2243,7 +2153,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2251,7 +2161,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>871</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2259,15 +2169,15 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="67" ht="11" customHeight="true" outlineLevel="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>140</v>
+        <v>213</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2275,15 +2185,15 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>213</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2291,7 +2201,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>741</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2299,7 +2209,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>127</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2307,7 +2217,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>64</v>
+        <v>991</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2315,15 +2225,15 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B74" s="15" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B74" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>1053</v>
+      <c r="C74" s="12" t="n">
+        <v>15351</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2331,15 +2241,15 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="76" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B76" s="14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="76" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="12" t="n">
-        <v>13113</v>
+      <c r="C76" s="16" t="n">
+        <v>1186</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2347,7 +2257,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2355,39 +2265,39 @@
         <v>77</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>251</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>542</v>
+      <c r="C79" s="16" t="n">
+        <v>2510</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>452</v>
+      <c r="C80" s="16" t="n">
+        <v>1039</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>2624</v>
+      <c r="C81" s="11" t="n">
+        <v>894</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>450</v>
+      <c r="C82" s="16" t="n">
+        <v>1005</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
@@ -2395,47 +2305,47 @@
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>700</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="16" t="n">
-        <v>1146</v>
+      <c r="C84" s="11" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>10</v>
+      <c r="C85" s="16" t="n">
+        <v>2309</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>310</v>
+      <c r="C86" s="16" t="n">
+        <v>3674</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>2068</v>
+      <c r="C87" s="11" t="n">
+        <v>270</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>3337</v>
+      <c r="C88" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2443,7 +2353,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>570</v>
+        <v>690</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2451,7 +2361,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>172</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2459,39 +2369,39 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B92" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B92" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B93" s="13" t="s">
+      <c r="C92" s="12" t="n">
+        <v>225373</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B93" s="14" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="12" t="n">
-        <v>278927</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B94" s="14" t="s">
+        <v>77900</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="12" t="n">
-        <v>85853</v>
+      <c r="C94" s="11" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>724</v>
+      <c r="C95" s="16" t="n">
+        <v>7091</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="true" outlineLevel="3">
@@ -2499,47 +2409,47 @@
         <v>95</v>
       </c>
       <c r="C96" s="16" t="n">
-        <v>11351</v>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="true" outlineLevel="3">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
       <c r="C97" s="16" t="n">
-        <v>4590</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C98" s="16" t="n">
+        <v>5893</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="16" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C99" s="11" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
       <c r="C100" s="16" t="n">
-        <v>9928</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="16" t="n">
-        <v>1455</v>
+      <c r="C101" s="11" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
@@ -2547,15 +2457,15 @@
         <v>101</v>
       </c>
       <c r="C102" s="16" t="n">
-        <v>1140</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>150</v>
+      <c r="C103" s="16" t="n">
+        <v>14190</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="true" outlineLevel="3">
@@ -2563,7 +2473,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="16" t="n">
-        <v>12930</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="true" outlineLevel="3">
@@ -2571,7 +2481,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="16" t="n">
-        <v>8760</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="true" outlineLevel="3">
@@ -2579,7 +2489,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="16" t="n">
-        <v>7848</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="true" outlineLevel="3">
@@ -2587,15 +2497,15 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="16" t="n">
-        <v>8130</v>
+      <c r="C108" s="11" t="n">
+        <v>830</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="true" outlineLevel="3">
@@ -2603,15 +2513,15 @@
         <v>108</v>
       </c>
       <c r="C109" s="16" t="n">
-        <v>3700</v>
+        <v>11501</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>90</v>
+      <c r="C110" s="16" t="n">
+        <v>12196</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="true" outlineLevel="3">
@@ -2619,47 +2529,47 @@
         <v>110</v>
       </c>
       <c r="C111" s="16" t="n">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B112" s="15" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B112" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="16" t="n">
-        <v>6462</v>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C112" s="12" t="n">
+        <v>6564</v>
+      </c>
+    </row>
+    <row r="113" ht="11" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="16" t="n">
-        <v>2940</v>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C113" s="11" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="114" ht="11" customHeight="true" outlineLevel="3">
       <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="16" t="n">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="115" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B115" s="14" t="s">
+      <c r="C114" s="11" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="115" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="12" t="n">
-        <v>9315</v>
+      <c r="C115" s="16" t="n">
+        <v>1171</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="16" t="n">
-        <v>1164</v>
+      <c r="C116" s="11" t="n">
+        <v>444</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2667,7 +2577,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>100</v>
+        <v>687</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2675,7 +2585,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>511</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2683,7 +2593,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>783</v>
+        <v>630</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2691,7 +2601,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>632</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2699,7 +2609,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>72</v>
+        <v>749</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2707,31 +2617,31 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="123" ht="11" customHeight="true" outlineLevel="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B124" s="15" t="s">
+      <c r="C123" s="16" t="n">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>199</v>
+      <c r="C124" s="12" t="n">
+        <v>13357</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="16" t="n">
-        <v>1283</v>
+      <c r="C125" s="11" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2739,15 +2649,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>180</v>
+        <v>293</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="16" t="n">
-        <v>1240</v>
+      <c r="C127" s="11" t="n">
+        <v>347</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2755,31 +2665,31 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="129" ht="22" customHeight="true" outlineLevel="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="129" ht="11" customHeight="true" outlineLevel="3">
       <c r="B129" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="16" t="n">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B130" s="14" t="s">
+      <c r="C129" s="11" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="12" t="n">
-        <v>16441</v>
+      <c r="C130" s="11" t="n">
+        <v>367</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>197</v>
+      <c r="C131" s="16" t="n">
+        <v>3371</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2787,15 +2697,15 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>70</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>137</v>
+      <c r="C133" s="16" t="n">
+        <v>2169</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2803,15 +2713,15 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>359</v>
+      <c r="C135" s="16" t="n">
+        <v>2365</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2819,15 +2729,15 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>184</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="16" t="n">
-        <v>3296</v>
+      <c r="C137" s="11" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2835,7 +2745,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>175</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2843,15 +2753,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="16" t="n">
-        <v>5385</v>
+      <c r="C140" s="11" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2859,15 +2769,15 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="16" t="n">
-        <v>2140</v>
+      <c r="C142" s="11" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2875,7 +2785,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>10</v>
+        <v>524</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2883,7 +2793,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2891,7 +2801,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2899,7 +2809,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>55</v>
+        <v>559</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2907,7 +2817,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>148</v>
+        <v>69</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2915,7 +2825,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>158</v>
+        <v>280</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2923,7 +2833,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>156</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2931,7 +2841,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>302</v>
+        <v>245</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2939,7 +2849,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>313</v>
+        <v>167</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2947,7 +2857,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>585</v>
+        <v>46</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2955,15 +2865,15 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="154" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B154" s="15" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="154" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B154" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>78</v>
+      <c r="C154" s="12" t="n">
+        <v>31430</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2971,7 +2881,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>135</v>
+        <v>222</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2979,7 +2889,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2987,7 +2897,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2995,7 +2905,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>65</v>
+        <v>114</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -3003,7 +2913,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>706</v>
+        <v>125</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -3011,7 +2921,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>46</v>
+        <v>121</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -3019,7 +2929,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>730</v>
+        <v>94</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -3027,15 +2937,15 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B163" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="12" t="n">
-        <v>40734</v>
+      <c r="C163" s="11" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -3043,15 +2953,15 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>88</v>
+      <c r="C165" s="16" t="n">
+        <v>1151</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -3059,7 +2969,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>83</v>
+        <v>306</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -3067,7 +2977,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -3075,7 +2985,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>8</v>
+        <v>578</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -3083,7 +2993,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>121</v>
+        <v>220</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3091,7 +3001,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -3099,15 +3009,15 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="11" t="n">
-        <v>17</v>
+      <c r="C172" s="16" t="n">
+        <v>1837</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3115,15 +3025,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>45</v>
+        <v>260</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="16" t="n">
-        <v>1156</v>
+      <c r="C174" s="11" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3131,7 +3041,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>391</v>
+        <v>546</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3139,15 +3049,15 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>16</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="16" t="n">
-        <v>1438</v>
+      <c r="C177" s="11" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3155,7 +3065,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>132</v>
+        <v>746</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3163,7 +3073,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>468</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3171,15 +3081,15 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="16" t="n">
-        <v>2285</v>
+      <c r="C181" s="11" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3187,7 +3097,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>317</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3195,7 +3105,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>86</v>
+        <v>322</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3203,7 +3113,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>808</v>
+        <v>213</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3211,7 +3121,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>132</v>
+        <v>565</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3219,15 +3129,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>84</v>
+        <v>325</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="16" t="n">
-        <v>1601</v>
+      <c r="C187" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3235,7 +3145,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>206</v>
+        <v>56</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3243,15 +3153,15 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>37</v>
+        <v>618</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="16" t="n">
-        <v>1384</v>
+      <c r="C190" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3259,7 +3169,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3267,23 +3177,23 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>234</v>
+        <v>420</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="16" t="n">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="194" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C193" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>818</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3291,7 +3201,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>325</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3299,7 +3209,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>965</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3307,15 +3217,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="198" ht="11" customHeight="true" outlineLevel="3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3323,15 +3233,15 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="200" ht="11" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>82</v>
+        <v>703</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3339,7 +3249,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3347,7 +3257,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>426</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3355,23 +3265,23 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="204" ht="22" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>714</v>
+        <v>496</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>110</v>
+      <c r="C205" s="16" t="n">
+        <v>1594</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3379,7 +3289,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>20</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3387,15 +3297,15 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="true" outlineLevel="3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="15" t="s">
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3403,15 +3313,15 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="210" ht="22" customHeight="true" outlineLevel="3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="16" t="n">
-        <v>1093</v>
+      <c r="C210" s="11" t="n">
+        <v>255</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3419,7 +3329,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>220</v>
+        <v>245</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3427,15 +3337,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>2</v>
+        <v>768</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="16" t="n">
-        <v>1047</v>
+      <c r="C213" s="11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3443,15 +3353,15 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>205</v>
+        <v>377</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="16" t="n">
-        <v>2481</v>
+      <c r="C215" s="11" t="n">
+        <v>345</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3459,7 +3369,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>513</v>
+        <v>845</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3467,7 +3377,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>729</v>
+        <v>764</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3475,7 +3385,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>427</v>
+        <v>290</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3483,7 +3393,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>31</v>
+        <v>862</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3491,7 +3401,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>2</v>
+        <v>634</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3499,7 +3409,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>79</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3507,7 +3417,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>266</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3515,7 +3425,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>424</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3523,7 +3433,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>768</v>
+        <v>364</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3531,15 +3441,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>692</v>
+        <v>373</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>717</v>
+      <c r="C226" s="16" t="n">
+        <v>5395</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3547,7 +3457,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3555,15 +3465,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>463</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>1300</v>
+      <c r="C229" s="11" t="n">
+        <v>981</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3571,23 +3481,23 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>290</v>
+        <v>144</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="16" t="n">
-        <v>2167</v>
+      <c r="C231" s="11" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="16" t="n">
-        <v>1336</v>
+      <c r="C232" s="11" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3595,7 +3505,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>960</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3603,15 +3513,15 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>40</v>
+        <v>175</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="16" t="n">
-        <v>1045</v>
+      <c r="C235" s="11" t="n">
+        <v>430</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3619,7 +3529,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>734</v>
+        <v>60</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3627,7 +3537,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>373</v>
+        <v>712</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3635,15 +3545,15 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="239" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B239" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B239" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>164</v>
+      <c r="C239" s="12" t="n">
+        <v>21533</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3651,15 +3561,15 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>8</v>
+        <v>642</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="16" t="n">
-        <v>1454</v>
+      <c r="C241" s="11" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3667,7 +3577,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>279</v>
+        <v>913</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3675,15 +3585,15 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>451</v>
+      <c r="C244" s="16" t="n">
+        <v>2628</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3691,7 +3601,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3699,7 +3609,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>387</v>
+        <v>74</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3707,7 +3617,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>193</v>
+        <v>374</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3715,7 +3625,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>4</v>
+        <v>112</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3723,7 +3633,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>35</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3731,7 +3641,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>270</v>
+        <v>43</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3739,15 +3649,15 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="252" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B252" s="14" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="12" t="n">
-        <v>19970</v>
+      <c r="C252" s="11" t="n">
+        <v>884</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3755,7 +3665,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3763,7 +3673,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>213</v>
+        <v>188</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3771,7 +3681,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>895</v>
+        <v>565</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3779,7 +3689,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3787,15 +3697,15 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="16" t="n">
-        <v>2540</v>
+      <c r="C258" s="11" t="n">
+        <v>666</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3803,7 +3713,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>12</v>
+        <v>459</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3811,15 +3721,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>74</v>
+        <v>895</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>408</v>
+      <c r="C261" s="16" t="n">
+        <v>1468</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3827,7 +3737,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>165</v>
+        <v>435</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3835,7 +3745,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>324</v>
+        <v>829</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3843,7 +3753,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>7</v>
+        <v>613</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3851,7 +3761,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>113</v>
+        <v>695</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3859,23 +3769,23 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>821</v>
+        <v>29</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="11" t="n">
-        <v>198</v>
+      <c r="C267" s="16" t="n">
+        <v>1112</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="11" t="n">
-        <v>583</v>
+      <c r="C268" s="16" t="n">
+        <v>1046</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3883,7 +3793,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>476</v>
+        <v>782</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3891,23 +3801,23 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>379</v>
+        <v>419</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>161</v>
+      <c r="C271" s="16" t="n">
+        <v>1122</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>550</v>
+      <c r="C272" s="16" t="n">
+        <v>1242</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3915,15 +3825,15 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="274" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B274" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="274" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B274" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="11" t="n">
-        <v>209</v>
+      <c r="C274" s="12" t="n">
+        <v>2530</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3931,7 +3841,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3939,15 +3849,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>277</v>
+        <v>206</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="16" t="n">
-        <v>1740</v>
+      <c r="C277" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3955,7 +3865,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>808</v>
+        <v>541</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3963,7 +3873,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>720</v>
+        <v>66</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3971,7 +3881,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>968</v>
+        <v>94</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3979,7 +3889,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>210</v>
+        <v>292</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3987,23 +3897,23 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>594</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="16" t="n">
-        <v>1237</v>
+      <c r="C283" s="11" t="n">
+        <v>233</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="16" t="n">
-        <v>1074</v>
+      <c r="C284" s="11" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -4011,15 +3921,15 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>379</v>
+        <v>141</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="16" t="n">
-        <v>1533</v>
+      <c r="C286" s="11" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -4027,15 +3937,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B288" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="12" t="n">
-        <v>2689</v>
+      <c r="C288" s="11" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -4043,15 +3953,15 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B290" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B290" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="11" t="n">
-        <v>275</v>
+      <c r="C290" s="12" t="n">
+        <v>16003</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -4059,7 +3969,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>226</v>
+        <v>118</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -4067,7 +3977,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -4075,7 +3985,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -4083,7 +3993,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>313</v>
+        <v>217</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4091,7 +4001,7 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>145</v>
+        <v>218</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4099,7 +4009,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>257</v>
+        <v>500</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4107,7 +4017,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>280</v>
+        <v>254</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -4115,15 +4025,15 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>107</v>
+        <v>43</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4131,7 +4041,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>114</v>
+        <v>230</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -4139,7 +4049,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>67</v>
+        <v>131</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4147,7 +4057,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>126</v>
+        <v>207</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -4155,15 +4065,15 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B304" s="14" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="12" t="n">
-        <v>17448</v>
+      <c r="C304" s="11" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4171,71 +4081,71 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="306" ht="11" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="306" ht="22" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="307" ht="22" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="308" ht="11" customHeight="true" outlineLevel="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="308" ht="22" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="309" ht="11" customHeight="true" outlineLevel="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="310" ht="11" customHeight="true" outlineLevel="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>326</v>
+        <v>170</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -4243,7 +4153,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4251,7 +4161,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>278</v>
+        <v>165</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4259,7 +4169,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>174</v>
+        <v>67</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4267,7 +4177,7 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>186</v>
+        <v>54</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4275,7 +4185,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>418</v>
+        <v>376</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4283,7 +4193,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>229</v>
+        <v>36</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4291,167 +4201,167 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C321" s="16" t="n">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="323" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C322" s="16" t="n">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="325" ht="22" customHeight="true" outlineLevel="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C325" s="16" t="n">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="true" outlineLevel="3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="328" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>32</v>
+        <v>742</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="11" t="n">
-        <v>257</v>
+      <c r="C330" s="16" t="n">
+        <v>1065</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="332" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C331" s="16" t="n">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="332" ht="22" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B333" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B333" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="11" t="n">
-        <v>92</v>
+      <c r="C333" s="17" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B334" s="15" t="s">
+      <c r="B334" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B335" s="15" t="s">
+      <c r="C334" s="17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B335" s="19" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="336" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B336" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B336" s="19" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B337" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B337" s="19" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B338" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B338" s="19" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B339" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B339" s="19" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="340" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B340" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B340" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="11" t="n">
-        <v>30</v>
+      <c r="C340" s="12" t="n">
+        <v>19230</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4459,47 +4369,47 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>216</v>
+        <v>754</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="11" t="n">
-        <v>695</v>
+      <c r="C342" s="16" t="n">
+        <v>1112</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="11" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C343" s="16" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="11" t="n">
-        <v>7</v>
+      <c r="C344" s="16" t="n">
+        <v>1012</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="11" t="n">
-        <v>266</v>
+      <c r="C345" s="16" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="16" t="n">
-        <v>5282</v>
+      <c r="C346" s="11" t="n">
+        <v>521</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4507,127 +4417,127 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>709</v>
+        <v>200</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="16" t="n">
-        <v>2879</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C348" s="11" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B350" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="17" t="n">
-        <v>837</v>
+      <c r="C350" s="11" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B351" s="18" t="s">
+      <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="17" t="n">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B352" s="19" t="s">
+      <c r="C351" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B353" s="19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B354" s="19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B355" s="19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B356" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B357" s="19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B358" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B359" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B360" s="19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B361" s="19" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B362" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="12" t="n">
-        <v>16614</v>
+      <c r="C362" s="11" t="n">
+        <v>417</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4635,7 +4545,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>958</v>
+        <v>39</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4643,23 +4553,23 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>614</v>
+        <v>431</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="16" t="n">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C365" s="11" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>172</v>
+        <v>375</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4667,7 +4577,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>885</v>
+        <v>168</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4675,7 +4585,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>194</v>
+        <v>29</v>
       </c>
     </row>
     <row r="369" ht="11" customHeight="true" outlineLevel="3">
@@ -4683,15 +4593,15 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>525</v>
+        <v>83</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4699,7 +4609,7 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>378</v>
+        <v>49</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4707,15 +4617,15 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>435</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
@@ -4723,7 +4633,7 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>394</v>
+        <v>92</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4731,7 +4641,7 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4739,15 +4649,15 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>569</v>
+        <v>148</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="11" t="n">
-        <v>627</v>
+      <c r="C377" s="16" t="n">
+        <v>3951</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
@@ -4755,23 +4665,23 @@
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="11" t="n">
-        <v>71</v>
+      <c r="C379" s="16" t="n">
+        <v>1351</v>
       </c>
     </row>
     <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="11" t="n">
-        <v>75</v>
+      <c r="C380" s="16" t="n">
+        <v>1523</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
@@ -4779,7 +4689,7 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>336</v>
+        <v>656</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4787,7 +4697,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>879</v>
+        <v>311</v>
       </c>
     </row>
     <row r="383" ht="11" customHeight="true" outlineLevel="3">
@@ -4795,7 +4705,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>273</v>
+        <v>52</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4803,15 +4713,15 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="385" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B385" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B385" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="11" t="n">
-        <v>144</v>
+      <c r="C385" s="17" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="386" ht="11" customHeight="true" outlineLevel="3">
@@ -4819,7 +4729,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4827,15 +4737,15 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="388" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B388" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B388" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="11" t="n">
-        <v>40</v>
+      <c r="C388" s="12" t="n">
+        <v>36545</v>
       </c>
     </row>
     <row r="389" ht="11" customHeight="true" outlineLevel="3">
@@ -4843,7 +4753,7 @@
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="390" ht="11" customHeight="true" outlineLevel="3">
@@ -4851,23 +4761,23 @@
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="391" ht="22" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="391" ht="11" customHeight="true" outlineLevel="3">
       <c r="B391" s="15" t="s">
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="392" ht="11" customHeight="true" outlineLevel="3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
       <c r="B392" s="15" t="s">
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>37</v>
+        <v>404</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4875,47 +4785,47 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="394" ht="33" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="16" t="n">
-        <v>2713</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="396" ht="22" customHeight="true" outlineLevel="3">
       <c r="B396" s="15" t="s">
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="16" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C397" s="11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>673</v>
+        <v>106</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -4923,7 +4833,7 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>173</v>
+        <v>106</v>
       </c>
     </row>
     <row r="400" ht="11" customHeight="true" outlineLevel="3">
@@ -4931,39 +4841,39 @@
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B401" s="14" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="C401" s="17" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C401" s="11" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B404" s="14" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="C404" s="12" t="n">
-        <v>68893</v>
+      <c r="C404" s="11" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="405" ht="11" customHeight="true" outlineLevel="3">
@@ -4971,7 +4881,7 @@
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>163</v>
+        <v>8</v>
       </c>
     </row>
     <row r="406" ht="11" customHeight="true" outlineLevel="3">
@@ -4979,7 +4889,7 @@
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
@@ -4987,31 +4897,31 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
       <c r="B408" s="15" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
       <c r="B409" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="C409" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="410" ht="33" customHeight="true" outlineLevel="3">
+      <c r="C409" s="16" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C410" s="16" t="n">
-        <v>2097</v>
+      <c r="C410" s="11" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="411" ht="22" customHeight="true" outlineLevel="3">
@@ -5019,7 +4929,7 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="true" outlineLevel="3">
@@ -5027,7 +4937,7 @@
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>19</v>
+        <v>511</v>
       </c>
     </row>
     <row r="413" ht="22" customHeight="true" outlineLevel="3">
@@ -5035,39 +4945,39 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>197</v>
+        <v>36</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="11" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C414" s="16" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="415" ht="22" customHeight="true" outlineLevel="3">
       <c r="B415" s="15" t="s">
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
       <c r="B416" s="15" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
       <c r="B417" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="C417" s="11" t="n">
-        <v>103</v>
+      <c r="C417" s="16" t="n">
+        <v>1159</v>
       </c>
     </row>
     <row r="418" ht="22" customHeight="true" outlineLevel="3">
@@ -5075,63 +4985,63 @@
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>195</v>
+        <v>91</v>
       </c>
     </row>
     <row r="419" ht="22" customHeight="true" outlineLevel="3">
       <c r="B419" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="C419" s="16" t="n">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C419" s="11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="420" ht="22" customHeight="true" outlineLevel="3">
       <c r="B420" s="15" t="s">
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
       <c r="B421" s="15" t="s">
         <v>420</v>
       </c>
       <c r="C421" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
       <c r="B422" s="15" t="s">
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="423" ht="11" customHeight="true" outlineLevel="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
       <c r="B423" s="15" t="s">
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
       <c r="B424" s="15" t="s">
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
       <c r="B425" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="C425" s="16" t="n">
-        <v>2861</v>
+      <c r="C425" s="11" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="426" ht="22" customHeight="true" outlineLevel="3">
@@ -5139,7 +5049,7 @@
         <v>425</v>
       </c>
       <c r="C426" s="11" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="427" ht="22" customHeight="true" outlineLevel="3">
@@ -5147,7 +5057,7 @@
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>550</v>
+        <v>112</v>
       </c>
     </row>
     <row r="428" ht="22" customHeight="true" outlineLevel="3">
@@ -5155,7 +5065,7 @@
         <v>427</v>
       </c>
       <c r="C428" s="11" t="n">
-        <v>359</v>
+        <v>572</v>
       </c>
     </row>
     <row r="429" ht="22" customHeight="true" outlineLevel="3">
@@ -5163,15 +5073,15 @@
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="430" ht="22" customHeight="true" outlineLevel="3">
       <c r="B430" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="C430" s="16" t="n">
-        <v>1653</v>
+      <c r="C430" s="11" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="431" ht="22" customHeight="true" outlineLevel="3">
@@ -5179,7 +5089,7 @@
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="432" ht="22" customHeight="true" outlineLevel="3">
@@ -5187,7 +5097,7 @@
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>306</v>
+        <v>36</v>
       </c>
     </row>
     <row r="433" ht="22" customHeight="true" outlineLevel="3">
@@ -5195,23 +5105,23 @@
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="434" ht="22" customHeight="true" outlineLevel="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="3">
       <c r="B434" s="15" t="s">
         <v>433</v>
       </c>
       <c r="C434" s="11" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="435" ht="22" customHeight="true" outlineLevel="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="435" ht="11" customHeight="true" outlineLevel="3">
       <c r="B435" s="15" t="s">
         <v>434</v>
       </c>
       <c r="C435" s="11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="436" ht="22" customHeight="true" outlineLevel="3">
@@ -5219,7 +5129,7 @@
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>304</v>
+        <v>9</v>
       </c>
     </row>
     <row r="437" ht="22" customHeight="true" outlineLevel="3">
@@ -5227,7 +5137,7 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>706</v>
+        <v>25</v>
       </c>
     </row>
     <row r="438" ht="22" customHeight="true" outlineLevel="3">
@@ -5235,7 +5145,7 @@
         <v>437</v>
       </c>
       <c r="C438" s="11" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
     </row>
     <row r="439" ht="22" customHeight="true" outlineLevel="3">
@@ -5243,7 +5153,7 @@
         <v>438</v>
       </c>
       <c r="C439" s="11" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="440" ht="22" customHeight="true" outlineLevel="3">
@@ -5251,7 +5161,7 @@
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
-        <v>199</v>
+        <v>37</v>
       </c>
     </row>
     <row r="441" ht="22" customHeight="true" outlineLevel="3">
@@ -5259,7 +5169,7 @@
         <v>440</v>
       </c>
       <c r="C441" s="11" t="n">
-        <v>953</v>
+        <v>716</v>
       </c>
     </row>
     <row r="442" ht="22" customHeight="true" outlineLevel="3">
@@ -5267,39 +5177,39 @@
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
     </row>
     <row r="443" ht="22" customHeight="true" outlineLevel="3">
       <c r="B443" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="C443" s="11" t="n">
-        <v>26</v>
+      <c r="C443" s="16" t="n">
+        <v>2523</v>
       </c>
     </row>
     <row r="444" ht="22" customHeight="true" outlineLevel="3">
       <c r="B444" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="C444" s="11" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="445" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C444" s="16" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
       <c r="B445" s="15" t="s">
         <v>444</v>
       </c>
       <c r="C445" s="11" t="n">
-        <v>155</v>
+        <v>380</v>
       </c>
     </row>
     <row r="446" ht="22" customHeight="true" outlineLevel="3">
       <c r="B446" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="C446" s="11" t="n">
-        <v>613</v>
+      <c r="C446" s="16" t="n">
+        <v>3148</v>
       </c>
     </row>
     <row r="447" ht="22" customHeight="true" outlineLevel="3">
@@ -5307,31 +5217,31 @@
         <v>446</v>
       </c>
       <c r="C447" s="16" t="n">
-        <v>2299</v>
-      </c>
-    </row>
-    <row r="448" ht="22" customHeight="true" outlineLevel="3">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="448" ht="11" customHeight="true" outlineLevel="3">
       <c r="B448" s="15" t="s">
         <v>447</v>
       </c>
       <c r="C448" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="449" ht="22" customHeight="true" outlineLevel="3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="449" ht="11" customHeight="true" outlineLevel="3">
       <c r="B449" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="C449" s="11" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="450" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C449" s="16" t="n">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
       <c r="B450" s="15" t="s">
         <v>449</v>
       </c>
       <c r="C450" s="11" t="n">
-        <v>36</v>
+        <v>240</v>
       </c>
     </row>
     <row r="451" ht="22" customHeight="true" outlineLevel="3">
@@ -5339,7 +5249,7 @@
         <v>450</v>
       </c>
       <c r="C451" s="11" t="n">
-        <v>649</v>
+        <v>473</v>
       </c>
     </row>
     <row r="452" ht="11" customHeight="true" outlineLevel="3">
@@ -5347,351 +5257,111 @@
         <v>451</v>
       </c>
       <c r="C452" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="453" ht="11" customHeight="true" outlineLevel="3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="453" ht="22" customHeight="true" outlineLevel="3">
       <c r="B453" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="C453" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="454" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C453" s="16" t="n">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="454" ht="11" customHeight="true" outlineLevel="3">
       <c r="B454" s="15" t="s">
         <v>453</v>
       </c>
       <c r="C454" s="11" t="n">
-        <v>11</v>
+        <v>428</v>
       </c>
     </row>
     <row r="455" ht="22" customHeight="true" outlineLevel="3">
       <c r="B455" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="C455" s="11" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="456" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C455" s="16" t="n">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="456" ht="11" customHeight="true" outlineLevel="3">
       <c r="B456" s="15" t="s">
         <v>455</v>
       </c>
       <c r="C456" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="457" ht="22" customHeight="true" outlineLevel="3">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="457" ht="11" customHeight="true" outlineLevel="3">
       <c r="B457" s="15" t="s">
         <v>456</v>
       </c>
       <c r="C457" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="458" ht="22" customHeight="true" outlineLevel="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="458" ht="11" customHeight="true" outlineLevel="3">
       <c r="B458" s="15" t="s">
         <v>457</v>
       </c>
       <c r="C458" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="459" ht="22" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459" ht="11" customHeight="true" outlineLevel="3">
       <c r="B459" s="15" t="s">
         <v>458</v>
       </c>
       <c r="C459" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="460" ht="22" customHeight="true" outlineLevel="3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="460" ht="11" customHeight="true" outlineLevel="3">
       <c r="B460" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="C460" s="16" t="n">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="461" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C460" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="461" ht="11" customHeight="true" outlineLevel="3">
       <c r="B461" s="15" t="s">
         <v>460</v>
       </c>
       <c r="C461" s="11" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="462" ht="22" customHeight="true" outlineLevel="3">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="462" ht="11" customHeight="true" outlineLevel="3">
       <c r="B462" s="15" t="s">
         <v>461</v>
       </c>
       <c r="C462" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="463" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B463" s="15" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="463" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B463" s="18" t="s">
         <v>462</v>
       </c>
-      <c r="C463" s="16" t="n">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="464" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B464" s="15" t="s">
+      <c r="C463" s="17" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="464" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B464" s="19" t="s">
         <v>463</v>
       </c>
       <c r="C464" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="465" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B465" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="465" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B465" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="C465" s="16" t="n">
-        <v>2887</v>
-      </c>
-    </row>
-    <row r="466" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B466" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="C466" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="467" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B467" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="C467" s="16" t="n">
-        <v>3657</v>
-      </c>
-    </row>
-    <row r="468" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B468" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="C468" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="469" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B469" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="C469" s="11" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="470" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B470" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="C470" s="11" t="n">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="471" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B471" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="C471" s="11" t="n">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="472" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B472" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="C472" s="16" t="n">
-        <v>3283</v>
-      </c>
-    </row>
-    <row r="473" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B473" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="C473" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="474" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B474" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="C474" s="11" t="n">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="475" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B475" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="C475" s="11" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="476" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B476" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="C476" s="11" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B477" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="C477" s="16" t="n">
-        <v>4027</v>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B478" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="C478" s="11" t="n">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="479" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B479" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="C479" s="11" t="n">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B480" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="C480" s="16" t="n">
-        <v>3524</v>
-      </c>
-    </row>
-    <row r="481" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B481" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="C481" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="482" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B482" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="C482" s="11" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="483" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B483" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="C483" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="484" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B484" s="15" t="s">
-        <v>483</v>
-      </c>
-      <c r="C484" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="485" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B485" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="C485" s="11" t="n">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="486" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B486" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="C486" s="11" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="487" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B487" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="C487" s="11" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="488" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B488" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="C488" s="16" t="n">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="489" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B489" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="C489" s="11" t="n">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="490" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B490" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="C490" s="12" t="n">
-        <v>18808</v>
-      </c>
-    </row>
-    <row r="491" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B491" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="C491" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="492" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B492" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="C492" s="16" t="n">
-        <v>9240</v>
-      </c>
-    </row>
-    <row r="493" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B493" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="C493" s="16" t="n">
-        <v>8448</v>
-      </c>
-    </row>
-    <row r="494" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B494" s="19" t="s">
-        <v>493</v>
-      </c>
-      <c r="C494" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="495" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B495" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="C495" s="11" t="n">
-        <v>780</v>
+      <c r="C465" s="11" t="n">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:12</t>
+    <t>Период: на 16.01.2026 15:05:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,57 +62,39 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Какао-порошок 100г/40 УБ</t>
   </si>
   <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
@@ -134,21 +116,12 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
@@ -167,78 +140,45 @@
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Приправа до курки УБ 25г /34шт</t>
-  </si>
-  <si>
-    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
-    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
-    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Часник гранульований сушений УБ 15г /42шт</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -278,18 +218,9 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
@@ -314,15 +245,9 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -332,30 +257,21 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
+  </si>
+  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -401,9 +317,6 @@
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -413,21 +326,12 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -467,6 +371,9 @@
     <t>Wafers лимон ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
@@ -518,9 +425,6 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -530,54 +434,33 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -590,24 +473,15 @@
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -623,9 +497,6 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -641,9 +512,6 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -653,12 +521,6 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -671,48 +533,30 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -752,9 +596,6 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -845,16 +686,13 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
+    <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
@@ -863,9 +701,6 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -878,9 +713,6 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -932,9 +764,6 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -950,9 +779,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
@@ -968,15 +794,9 @@
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
@@ -995,12 +815,6 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -1016,42 +830,15 @@
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>ПОДАРУНКИ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ 2026</t>
-  </si>
-  <si>
-    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
-  </si>
-  <si>
-    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
-  </si>
-  <si>
-    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
-    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
@@ -1064,45 +851,30 @@
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>KONAFETTO nero ККФ 1кг /5пак /</t>
   </si>
   <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1112,33 +884,18 @@
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
-    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1151,12 +908,6 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
@@ -1169,9 +920,6 @@
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -1187,21 +935,12 @@
     <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1211,9 +950,6 @@
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
@@ -1238,30 +974,15 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1289,9 +1010,6 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1304,21 +1022,12 @@
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1340,15 +1049,18 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1358,6 +1070,9 @@
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1391,7 +1106,7 @@
     <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
@@ -1404,15 +1119,6 @@
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
-  </si>
-  <si>
-    <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1639,12 +1345,6 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1664,7 +1364,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C465"/>
+  <dimension ref="C367"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1729,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1737,7 +1437,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>284090</v>
+        <v>210747</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1745,7 +1445,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>58717</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1753,23 +1453,23 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7731</v>
+        <v>7928</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>340</v>
+      <c r="C15" s="16" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>560</v>
+      <c r="C16" s="16" t="n">
+        <v>1187</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1777,7 +1477,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>24</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1785,15 +1485,15 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>672</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>245</v>
+      <c r="C19" s="16" t="n">
+        <v>1133</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1801,7 +1501,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>368</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1809,7 +1509,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>859</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1817,15 +1517,15 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>388</v>
+      <c r="C23" s="16" t="n">
+        <v>1155</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1833,7 +1533,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>208</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1841,71 +1541,71 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>377</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B27" s="15" t="s">
+      <c r="C26" s="16" t="n">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B27" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>168</v>
+      <c r="C27" s="12" t="n">
+        <v>17045</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>65</v>
+      <c r="C28" s="16" t="n">
+        <v>2462</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>432</v>
+      <c r="C29" s="16" t="n">
+        <v>3138</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>131</v>
+      <c r="C30" s="16" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>68</v>
+      <c r="C31" s="16" t="n">
+        <v>3863</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>2428</v>
-      </c>
-    </row>
-    <row r="33" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B33" s="14" t="s">
+      <c r="C32" s="11" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>26936</v>
+      <c r="C33" s="11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1913,31 +1613,31 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>1647</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="16" t="n">
-        <v>3787</v>
+      <c r="C35" s="11" t="n">
+        <v>627</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="16" t="n">
-        <v>1100</v>
+      <c r="C36" s="11" t="n">
+        <v>481</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="16" t="n">
-        <v>4403</v>
+      <c r="C37" s="11" t="n">
+        <v>388</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1945,15 +1645,15 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="39" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B39" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="39" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="16" t="n">
-        <v>5308</v>
+      <c r="C39" s="12" t="n">
+        <v>3861</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1961,23 +1661,23 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>28</v>
+        <v>652</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>1360</v>
+      <c r="C41" s="11" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>3360</v>
+      <c r="C42" s="11" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1985,7 +1685,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1</v>
+        <v>375</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1993,39 +1693,39 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>824</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="16" t="n">
-        <v>1540</v>
+      <c r="C45" s="11" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="16" t="n">
-        <v>1460</v>
+      <c r="C46" s="11" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="16" t="n">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="48" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B48" s="14" t="s">
+      <c r="C47" s="11" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="12" t="n">
-        <v>8699</v>
+      <c r="C48" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -2033,7 +1733,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>293</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2041,7 +1741,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>271</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2049,7 +1749,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>550</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2057,7 +1757,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2065,15 +1765,15 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="54" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B54" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="54" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B54" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>379</v>
+      <c r="C54" s="12" t="n">
+        <v>17005</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2081,7 +1781,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>174</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2089,7 +1789,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>960</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2097,7 +1797,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>647</v>
+        <v>513</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2105,23 +1805,23 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>119</v>
+        <v>439</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>335</v>
+      <c r="C59" s="16" t="n">
+        <v>4117</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>173</v>
+      <c r="C60" s="16" t="n">
+        <v>1488</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2129,15 +1829,15 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>367</v>
+        <v>572</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="n">
-        <v>83</v>
+      <c r="C62" s="16" t="n">
+        <v>1550</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2145,7 +1845,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>515</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2153,31 +1853,31 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>75</v>
+        <v>518</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>108</v>
+      <c r="C65" s="16" t="n">
+        <v>1954</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C66" s="16" t="n">
+        <v>5074</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>213</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2185,127 +1885,127 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="69" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B69" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B69" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="70" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B70" s="15" t="s">
+      <c r="C69" s="12" t="n">
+        <v>164908</v>
+      </c>
+    </row>
+    <row r="70" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B70" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C70" s="12" t="n">
+        <v>55410</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" ht="11" customHeight="true" outlineLevel="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="73" ht="11" customHeight="true" outlineLevel="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="true" outlineLevel="3">
       <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="11" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B74" s="14" t="s">
+      <c r="C73" s="16" t="n">
+        <v>4968</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="12" t="n">
-        <v>15351</v>
+      <c r="C74" s="16" t="n">
+        <v>8413</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="76" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C75" s="16" t="n">
+        <v>5535</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+        <v>6925</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C77" s="16" t="n">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C78" s="16" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
       <c r="C79" s="16" t="n">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="80" ht="11" customHeight="true" outlineLevel="3">
+        <v>5505</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="81" ht="11" customHeight="true" outlineLevel="3">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C81" s="16" t="n">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B83" s="15" t="s">
+        <v>11195</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B83" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>10</v>
+      <c r="C83" s="12" t="n">
+        <v>2786</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
@@ -2313,23 +2013,23 @@
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>419</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>2309</v>
+      <c r="C85" s="11" t="n">
+        <v>797</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="16" t="n">
-        <v>3674</v>
+      <c r="C86" s="11" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2337,7 +2037,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>270</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2345,7 +2045,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2353,7 +2053,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>690</v>
+        <v>305</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2361,7 +2061,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2369,175 +2069,175 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B92" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="12" t="n">
-        <v>225373</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B93" s="14" t="s">
+      <c r="C92" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="12" t="n">
-        <v>77900</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C93" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>165</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>7091</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B96" s="15" t="s">
+      <c r="C95" s="11" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B96" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="16" t="n">
-        <v>1878</v>
+      <c r="C96" s="12" t="n">
+        <v>15303</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>1346</v>
+      <c r="C97" s="11" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>5893</v>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C98" s="11" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="true" outlineLevel="3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="16" t="n">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C100" s="11" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="true" outlineLevel="3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
       <c r="C102" s="16" t="n">
-        <v>9300</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="16" t="n">
-        <v>14190</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="16" t="n">
-        <v>3615</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>3630</v>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C105" s="11" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="16" t="n">
-        <v>2110</v>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C106" s="11" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="true" outlineLevel="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="16" t="n">
-        <v>11501</v>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C109" s="11" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="16" t="n">
-        <v>12196</v>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C110" s="11" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="16" t="n">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B112" s="14" t="s">
+      <c r="C111" s="11" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="12" t="n">
-        <v>6564</v>
+      <c r="C112" s="11" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,7 +2245,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>462</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2553,15 +2253,15 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>613</v>
+        <v>714</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
       <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="16" t="n">
-        <v>1171</v>
+      <c r="C115" s="11" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2569,7 +2269,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>444</v>
+        <v>86</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2577,7 +2277,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>687</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2585,7 +2285,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2593,7 +2293,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>630</v>
+        <v>121</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2601,7 +2301,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>170</v>
+        <v>663</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2609,7 +2309,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>749</v>
+        <v>231</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2617,23 +2317,23 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="123" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B123" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B123" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="16" t="n">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B124" s="14" t="s">
+      <c r="C123" s="12" t="n">
+        <v>18781</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="12" t="n">
-        <v>13357</v>
+      <c r="C124" s="11" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2641,7 +2341,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>263</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2649,7 +2349,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>293</v>
+        <v>43</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2657,7 +2357,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>347</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2665,7 +2365,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>37</v>
+        <v>115</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2673,7 +2373,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>277</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2681,15 +2381,15 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>367</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="16" t="n">
-        <v>3371</v>
+      <c r="C131" s="11" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2697,31 +2397,31 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>175</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="16" t="n">
-        <v>2169</v>
+      <c r="C133" s="11" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
       <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>50</v>
+      <c r="C134" s="16" t="n">
+        <v>1109</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="16" t="n">
-        <v>2365</v>
+      <c r="C135" s="11" t="n">
+        <v>279</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2729,7 +2429,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2737,7 +2437,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2745,15 +2445,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="11" t="n">
-        <v>106</v>
+      <c r="C139" s="16" t="n">
+        <v>1114</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2761,7 +2461,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>136</v>
+        <v>285</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2769,7 +2469,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2777,7 +2477,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2785,7 +2485,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>524</v>
+        <v>31</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2793,7 +2493,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>81</v>
+        <v>217</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2801,7 +2501,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>205</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2809,7 +2509,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>559</v>
+        <v>316</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2817,7 +2517,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>69</v>
+        <v>808</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2825,7 +2525,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>280</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2833,7 +2533,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2841,7 +2541,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>245</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2849,7 +2549,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>167</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2857,23 +2557,23 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="153" ht="11" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="true" outlineLevel="3">
       <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="154" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B154" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="154" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="12" t="n">
-        <v>31430</v>
+      <c r="C154" s="11" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2881,15 +2581,15 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="156" ht="11" customHeight="true" outlineLevel="3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="true" outlineLevel="3">
       <c r="B156" s="15" t="s">
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>113</v>
+        <v>193</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2897,15 +2597,15 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="158" ht="11" customHeight="true" outlineLevel="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="true" outlineLevel="3">
       <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>114</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2913,7 +2613,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>125</v>
+        <v>33</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2921,7 +2621,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2929,7 +2629,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2937,7 +2637,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>107</v>
+        <v>844</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2945,7 +2645,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2953,15 +2653,15 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>213</v>
+        <v>498</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="16" t="n">
-        <v>1151</v>
+      <c r="C165" s="11" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2969,7 +2669,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>306</v>
+        <v>135</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2977,7 +2677,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>16</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2985,7 +2685,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>578</v>
+        <v>154</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2993,7 +2693,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>220</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3001,7 +2701,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -3009,15 +2709,15 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>25</v>
+        <v>956</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="16" t="n">
-        <v>1837</v>
+      <c r="C172" s="11" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3025,7 +2725,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>260</v>
+        <v>111</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -3033,23 +2733,23 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="11" t="n">
-        <v>546</v>
+      <c r="C175" s="16" t="n">
+        <v>1247</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="11" t="n">
-        <v>207</v>
+      <c r="C176" s="16" t="n">
+        <v>4427</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3057,7 +2757,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3065,7 +2765,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>746</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3073,7 +2773,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>193</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3081,7 +2781,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3089,7 +2789,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3097,7 +2797,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>13</v>
+        <v>156</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3105,7 +2805,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3113,7 +2813,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>213</v>
+        <v>37</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3121,7 +2821,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>565</v>
+        <v>588</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3129,15 +2829,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="187" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B187" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B187" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>26</v>
+      <c r="C187" s="12" t="n">
+        <v>20384</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3145,7 +2845,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>56</v>
+        <v>413</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3153,7 +2853,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>618</v>
+        <v>108</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3161,7 +2861,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>25</v>
+        <v>700</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3169,15 +2869,15 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>20</v>
+        <v>709</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="11" t="n">
-        <v>420</v>
+      <c r="C192" s="16" t="n">
+        <v>2290</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3185,15 +2885,15 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="194" ht="22" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>453</v>
+        <v>359</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3201,7 +2901,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3209,7 +2909,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>20</v>
+        <v>236</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3217,15 +2917,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="198" ht="22" customHeight="true" outlineLevel="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>30</v>
+        <v>402</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3233,15 +2933,15 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="200" ht="22" customHeight="true" outlineLevel="3">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>703</v>
+        <v>884</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3249,7 +2949,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>260</v>
+        <v>223</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3257,7 +2957,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>2</v>
+        <v>276</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3265,7 +2965,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>79</v>
+        <v>138</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3273,15 +2973,15 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>496</v>
+        <v>259</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="16" t="n">
-        <v>1594</v>
+      <c r="C205" s="11" t="n">
+        <v>517</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3289,7 +2989,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>438</v>
+        <v>173</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3297,7 +2997,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>497</v>
+        <v>653</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3305,15 +3005,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>31</v>
+        <v>708</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>331</v>
+      <c r="C209" s="16" t="n">
+        <v>1628</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3321,7 +3021,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>255</v>
+        <v>990</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3329,15 +3029,15 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>245</v>
+        <v>601</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="11" t="n">
-        <v>768</v>
+      <c r="C212" s="16" t="n">
+        <v>1186</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3345,7 +3045,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3353,15 +3053,15 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>377</v>
+        <v>611</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="11" t="n">
-        <v>345</v>
+      <c r="C215" s="16" t="n">
+        <v>1042</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3369,15 +3069,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>845</v>
+        <v>403</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>764</v>
+      <c r="C217" s="16" t="n">
+        <v>1050</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3385,15 +3085,15 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>290</v>
+        <v>932</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>862</v>
+      <c r="C219" s="16" t="n">
+        <v>1872</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3401,15 +3101,15 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="221" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B221" s="15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="221" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B221" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="11" t="n">
-        <v>219</v>
+      <c r="C221" s="12" t="n">
+        <v>1875</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3417,7 +3117,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>40</v>
+        <v>251</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3425,7 +3125,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>535</v>
+        <v>203</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3433,7 +3133,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>364</v>
+        <v>340</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3441,15 +3141,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>373</v>
+        <v>78</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="16" t="n">
-        <v>5395</v>
+      <c r="C226" s="11" t="n">
+        <v>142</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3457,7 +3157,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>123</v>
+        <v>195</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3465,7 +3165,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3473,7 +3173,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>981</v>
+        <v>98</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3481,7 +3181,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3489,7 +3189,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>350</v>
+        <v>212</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3497,7 +3197,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3505,15 +3205,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B234" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B234" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>175</v>
+      <c r="C234" s="12" t="n">
+        <v>15552</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3521,7 +3221,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>430</v>
+        <v>231</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3529,7 +3229,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3537,7 +3237,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>712</v>
+        <v>219</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3545,15 +3245,15 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B239" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="12" t="n">
-        <v>21533</v>
+      <c r="C239" s="11" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3561,7 +3261,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>642</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3569,7 +3269,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3577,23 +3277,23 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="243" ht="11" customHeight="true" outlineLevel="3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="243" ht="22" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>440</v>
+        <v>71</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="16" t="n">
-        <v>2628</v>
+      <c r="C244" s="11" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3601,7 +3301,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>12</v>
+        <v>184</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3609,7 +3309,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>74</v>
+        <v>134</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3617,7 +3317,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>374</v>
+        <v>207</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3625,71 +3325,71 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="249" ht="11" customHeight="true" outlineLevel="3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="250" ht="11" customHeight="true" outlineLevel="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="251" ht="11" customHeight="true" outlineLevel="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="252" ht="11" customHeight="true" outlineLevel="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="253" ht="11" customHeight="true" outlineLevel="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="254" ht="11" customHeight="true" outlineLevel="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="254" ht="22" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="true" outlineLevel="3">
       <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="256" ht="11" customHeight="true" outlineLevel="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="256" ht="22" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>194</v>
+        <v>59</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3697,7 +3397,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3705,7 +3405,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>666</v>
+        <v>190</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3713,7 +3413,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>459</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3721,7 +3421,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>895</v>
+        <v>35</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3729,15 +3429,15 @@
         <v>260</v>
       </c>
       <c r="C261" s="16" t="n">
-        <v>1468</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="11" t="n">
-        <v>435</v>
+      <c r="C262" s="16" t="n">
+        <v>1352</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3745,7 +3445,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>829</v>
+        <v>469</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3753,7 +3453,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>613</v>
+        <v>436</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3761,7 +3461,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>695</v>
+        <v>925</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3769,7 +3469,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>29</v>
+        <v>570</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3777,63 +3477,63 @@
         <v>266</v>
       </c>
       <c r="C267" s="16" t="n">
-        <v>1112</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="16" t="n">
-        <v>1046</v>
+      <c r="C268" s="11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="11" t="n">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="270" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C269" s="16" t="n">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B271" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B271" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="16" t="n">
-        <v>1122</v>
+      <c r="C271" s="12" t="n">
+        <v>14908</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="16" t="n">
-        <v>1242</v>
+      <c r="C272" s="11" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="11" t="n">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="274" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B274" s="14" t="s">
+      <c r="C273" s="16" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="274" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B274" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="12" t="n">
-        <v>2530</v>
+      <c r="C274" s="16" t="n">
+        <v>2006</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3841,7 +3541,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>61</v>
+        <v>417</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3849,7 +3549,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>206</v>
+        <v>286</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3857,7 +3557,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>235</v>
+        <v>722</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3865,7 +3565,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>541</v>
+        <v>283</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3873,7 +3573,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>66</v>
+        <v>276</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3881,7 +3581,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>94</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3889,7 +3589,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>292</v>
+        <v>499</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3897,7 +3597,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>16</v>
+        <v>130</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3905,7 +3605,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>233</v>
+        <v>440</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3913,7 +3613,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3921,7 +3621,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>141</v>
+        <v>571</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3929,7 +3629,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>257</v>
+        <v>376</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3937,7 +3637,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>43</v>
+        <v>363</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3945,7 +3645,7 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>59</v>
+        <v>650</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3953,15 +3653,15 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B290" s="14" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="12" t="n">
-        <v>16003</v>
+      <c r="C290" s="11" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3969,7 +3669,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3977,7 +3677,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>172</v>
+        <v>123</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3985,7 +3685,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3993,7 +3693,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>217</v>
+        <v>75</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4001,23 +3701,23 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>218</v>
+        <v>111</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="11" t="n">
-        <v>500</v>
+      <c r="C296" s="16" t="n">
+        <v>2195</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="C297" s="11" t="n">
-        <v>254</v>
+      <c r="C297" s="16" t="n">
+        <v>1580</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -4025,15 +3725,15 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4041,15 +3741,15 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B301" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B301" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="11" t="n">
-        <v>131</v>
+      <c r="C301" s="17" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4057,7 +3757,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>207</v>
+        <v>95</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -4065,15 +3765,15 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B304" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B304" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="11" t="n">
-        <v>101</v>
+      <c r="C304" s="12" t="n">
+        <v>19751</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4081,15 +3781,15 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="306" ht="22" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>135</v>
+        <v>188</v>
       </c>
     </row>
     <row r="307" ht="22" customHeight="true" outlineLevel="3">
@@ -4097,7 +3797,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>91</v>
+        <v>549</v>
       </c>
     </row>
     <row r="308" ht="22" customHeight="true" outlineLevel="3">
@@ -4105,7 +3805,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>156</v>
+        <v>38</v>
       </c>
     </row>
     <row r="309" ht="22" customHeight="true" outlineLevel="3">
@@ -4113,7 +3813,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="310" ht="22" customHeight="true" outlineLevel="3">
@@ -4121,31 +3821,31 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>170</v>
+        <v>103</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -4153,15 +3853,15 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="315" ht="22" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>165</v>
+        <v>411</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4169,7 +3869,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4177,7 +3877,7 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4185,111 +3885,111 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="319" ht="22" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="321" ht="11" customHeight="true" outlineLevel="3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="16" t="n">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C321" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="16" t="n">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C322" s="11" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="323" ht="22" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="325" ht="11" customHeight="true" outlineLevel="3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="325" ht="22" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="16" t="n">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C325" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="327" ht="11" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="328" ht="11" customHeight="true" outlineLevel="3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="329" ht="11" customHeight="true" outlineLevel="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="16" t="n">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="331" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C330" s="11" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="331" ht="22" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="16" t="n">
-        <v>2766</v>
+      <c r="C331" s="11" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="332" ht="22" customHeight="true" outlineLevel="3">
@@ -4297,119 +3997,119 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B333" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="17" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B334" s="18" t="s">
+      <c r="C333" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="17" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B335" s="19" t="s">
+      <c r="C334" s="11" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="335" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="336" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B336" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="336" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B337" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B338" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B339" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="340" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B340" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="340" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="12" t="n">
-        <v>19230</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C340" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="16" t="n">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C342" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="16" t="n">
-        <v>1367</v>
+      <c r="C343" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="16" t="n">
-        <v>1012</v>
+      <c r="C344" s="11" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="16" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C345" s="11" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="11" t="n">
-        <v>521</v>
+      <c r="C346" s="16" t="n">
+        <v>2039</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4417,15 +4117,15 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>314</v>
+        <v>941</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4433,15 +4133,15 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>88</v>
+      <c r="C350" s="16" t="n">
+        <v>2448</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4449,15 +4149,15 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4465,7 +4165,7 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>181</v>
+        <v>247</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4473,7 +4173,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>135</v>
+        <v>792</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4481,15 +4181,15 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="356" ht="22" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>406</v>
+        <v>548</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4497,15 +4197,15 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="358" ht="22" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="11" t="n">
-        <v>206</v>
+      <c r="C358" s="16" t="n">
+        <v>1576</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
@@ -4513,15 +4213,15 @@
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="360" ht="22" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>472</v>
+        <v>801</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4529,7 +4229,7 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>94</v>
+        <v>700</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4537,7 +4237,7 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>417</v>
+        <v>19</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4545,7 +4245,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4553,7 +4253,7 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>431</v>
+        <v>152</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
@@ -4561,15 +4261,15 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="11" t="n">
-        <v>375</v>
+      <c r="C366" s="16" t="n">
+        <v>1850</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4577,791 +4277,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="368" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B368" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="C368" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B369" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="C369" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B370" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="C370" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="371" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B371" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="C371" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B372" s="15" t="s">
-        <v>371</v>
-      </c>
-      <c r="C372" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="373" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B373" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="C373" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B374" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="C374" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B375" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="C375" s="11" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B376" s="15" t="s">
-        <v>375</v>
-      </c>
-      <c r="C376" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B377" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="C377" s="16" t="n">
-        <v>3951</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B378" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="C378" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="379" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B379" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="C379" s="16" t="n">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B380" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="C380" s="16" t="n">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B381" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="C381" s="11" t="n">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="382" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B382" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="C382" s="11" t="n">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B383" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="C383" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="384" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B384" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="C384" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B385" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="C385" s="17" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B386" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="C386" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B387" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="C387" s="11" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B388" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="C388" s="12" t="n">
-        <v>36545</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B389" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="C389" s="11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B390" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="C390" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="391" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B391" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="C391" s="11" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B392" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="C392" s="11" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="393" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B393" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C393" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="394" ht="33" customHeight="true" outlineLevel="3">
-      <c r="B394" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="C394" s="16" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="395" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B395" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="C395" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="396" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B396" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="C396" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="397" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B397" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="C397" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="398" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B398" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C398" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B399" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="C399" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B400" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="C400" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B401" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="C401" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B402" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="C402" s="11" t="n">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B403" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="C403" s="11" t="n">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B404" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="C404" s="11" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B405" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="C405" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B406" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="C406" s="11" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B407" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="C407" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B408" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="C408" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B409" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C409" s="16" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B410" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C410" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="411" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C411" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B412" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C412" s="11" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B413" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C413" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="414" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B414" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C414" s="16" t="n">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="415" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B415" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="C415" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="416" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B416" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C416" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="417" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B417" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="C417" s="16" t="n">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="418" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B418" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="C418" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="419" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B419" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="C419" s="11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="420" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B420" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C420" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="421" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B421" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="C421" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="422" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B422" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="C422" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="423" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B423" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="C423" s="11" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="424" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B424" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="C424" s="11" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="425" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B425" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="C425" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="426" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B426" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="C426" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="427" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B427" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C427" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="428" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B428" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="C428" s="11" t="n">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="429" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B429" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="C429" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="430" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B430" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="C430" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="431" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B431" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="C431" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="432" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B432" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="C432" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="433" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B433" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="C433" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="434" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B434" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="C434" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="435" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B435" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="C435" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="436" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B436" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="C436" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="437" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B437" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="C437" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="438" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B438" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C438" s="11" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="439" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B439" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C439" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="440" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B440" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C440" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B441" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="C441" s="11" t="n">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="442" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B442" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="C442" s="11" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="443" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B443" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="C443" s="16" t="n">
-        <v>2523</v>
-      </c>
-    </row>
-    <row r="444" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B444" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="C444" s="16" t="n">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="445" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B445" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="C445" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="446" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B446" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="C446" s="16" t="n">
-        <v>3148</v>
-      </c>
-    </row>
-    <row r="447" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B447" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="C447" s="16" t="n">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="448" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B448" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="C448" s="11" t="n">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="449" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B449" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="C449" s="16" t="n">
-        <v>2295</v>
-      </c>
-    </row>
-    <row r="450" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B450" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="C450" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="451" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B451" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="C451" s="11" t="n">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="452" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B452" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="C452" s="11" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B453" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="C453" s="16" t="n">
-        <v>3390</v>
-      </c>
-    </row>
-    <row r="454" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B454" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="C454" s="11" t="n">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="455" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B455" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C455" s="16" t="n">
-        <v>3226</v>
-      </c>
-    </row>
-    <row r="456" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B456" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="C456" s="11" t="n">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B457" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C457" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="458" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B458" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="C458" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B459" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="C459" s="11" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B460" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="C460" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B461" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="C461" s="11" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="462" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B462" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="C462" s="11" t="n">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="463" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B463" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="C463" s="17" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="464" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B464" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="C464" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="465" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B465" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="C465" s="11" t="n">
-        <v>312</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.01.2026 15:05:12</t>
+    <t>Период: на 30.01.2026 8:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -128,22 +128,28 @@
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт</t>
-  </si>
-  <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
+    <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до плову УБ 25г /36шт</t>
@@ -161,9 +167,6 @@
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -182,12 +185,6 @@
     <t>СПЕЦІЇ</t>
   </si>
   <si>
-    <t>Гвоздика ціла УБ 10г /30шт</t>
-  </si>
-  <si>
-    <t>Кориця мелена УБ 15г /38шт</t>
-  </si>
-  <si>
     <t>Коріандр мелений УБ 20г /30шт</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>Паприка копчена мелена УБ 20г /34шт</t>
   </si>
   <si>
-    <t>Паприка мелена УБ 20г /34шт</t>
-  </si>
-  <si>
     <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
@@ -233,9 +227,6 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
@@ -260,9 +251,6 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
@@ -290,15 +278,9 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -329,6 +311,9 @@
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -356,9 +341,6 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ККФ 216г /16шт</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -380,9 +362,6 @@
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
@@ -425,9 +404,6 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -503,9 +479,6 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -527,9 +500,6 @@
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -551,9 +521,6 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -629,9 +596,6 @@
     <t>Peppinezzz РЦ 0.9кг /6пак</t>
   </si>
   <si>
-    <t>Roshen Butter-Milk КрКФ 1кг /8шт</t>
-  </si>
-  <si>
     <t>Roshen Yogurtini РЦ 1кг /8шт</t>
   </si>
   <si>
@@ -686,6 +650,9 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
@@ -713,6 +680,9 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -728,9 +698,6 @@
     <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
   </si>
   <si>
-    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
-  </si>
-  <si>
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
@@ -755,18 +722,12 @@
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies арахіс ККФ 150г /16шт</t>
-  </si>
-  <si>
     <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
   </si>
   <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
@@ -779,12 +740,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
   </si>
   <si>
@@ -824,12 +779,12 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
   </si>
   <si>
-    <t>До кави пряжене молоко ККФ 370г /24шт</t>
-  </si>
-  <si>
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
+    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
@@ -839,6 +794,9 @@
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
@@ -890,6 +848,9 @@
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -908,6 +869,9 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
@@ -953,66 +917,45 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
@@ -1031,9 +974,6 @@
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
@@ -1049,9 +989,6 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1073,13 +1010,10 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
@@ -1097,9 +1031,6 @@
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
@@ -1107,9 +1038,6 @@
   </si>
   <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
-    <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
@@ -1364,7 +1292,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C367"/>
+  <dimension ref="C343"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1429,7 +1357,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1437,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>210747</v>
+        <v>120262</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1445,7 +1373,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>45839</v>
+        <v>27903</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1453,23 +1381,23 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7928</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>1800</v>
+      <c r="C15" s="11" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>1187</v>
+      <c r="C16" s="11" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1477,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1485,15 +1413,15 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>1133</v>
+      <c r="C19" s="11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1501,7 +1429,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>267</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1509,7 +1437,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>232</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1517,15 +1445,15 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>65</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>1155</v>
+      <c r="C23" s="11" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1533,7 +1461,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1541,15 +1469,15 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>51</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>1290</v>
+      <c r="C26" s="11" t="n">
+        <v>627</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="2">
@@ -1557,7 +1485,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>17045</v>
+        <v>10761</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1565,7 +1493,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>2462</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1573,7 +1501,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>3138</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1589,7 +1517,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>3863</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1597,7 +1525,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>208</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1613,7 +1541,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>4261</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1621,7 +1549,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>627</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1629,7 +1557,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>481</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1637,7 +1565,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>388</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1645,15 +1573,15 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="39" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B39" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="12" t="n">
-        <v>3861</v>
+      <c r="C39" s="11" t="n">
+        <v>331</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1661,7 +1589,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>652</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1669,15 +1597,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B42" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B42" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>101</v>
+      <c r="C42" s="12" t="n">
+        <v>2111</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1685,7 +1613,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>375</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1693,7 +1621,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>586</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1701,7 +1629,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>480</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1709,7 +1637,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1717,7 +1645,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1725,7 +1653,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1733,7 +1661,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1741,7 +1669,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>338</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1749,7 +1677,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1757,7 +1685,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>38</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1765,23 +1693,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="54" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B54" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="12" t="n">
-        <v>17005</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B55" s="15" t="s">
+      <c r="C54" s="11" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B55" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>53</v>
+      <c r="C55" s="12" t="n">
+        <v>10811</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1789,7 +1717,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1797,15 +1725,15 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>513</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>439</v>
+      <c r="C58" s="16" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1813,7 +1741,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>4117</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1821,7 +1749,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>1488</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1829,95 +1757,95 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>572</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>1550</v>
+      <c r="C62" s="11" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="11" t="n">
-        <v>10</v>
+      <c r="C63" s="16" t="n">
+        <v>1273</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="11" t="n">
-        <v>518</v>
+      <c r="C64" s="16" t="n">
+        <v>2756</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>1954</v>
+      <c r="C65" s="11" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>5074</v>
-      </c>
-    </row>
-    <row r="67" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B67" s="15" t="s">
+      <c r="C66" s="11" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B67" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="68" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B68" s="15" t="s">
+      <c r="C67" s="12" t="n">
+        <v>92359</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B68" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="69" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B69" s="13" t="s">
+      <c r="C68" s="12" t="n">
+        <v>33742</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="12" t="n">
-        <v>164908</v>
-      </c>
-    </row>
-    <row r="70" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B70" s="14" t="s">
+      <c r="C69" s="11" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="12" t="n">
-        <v>55410</v>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C70" s="16" t="n">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C71" s="16" t="n">
+        <v>5288</v>
+      </c>
+    </row>
+    <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>67</v>
+        <v>765</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="true" outlineLevel="3">
@@ -1925,23 +1853,23 @@
         <v>72</v>
       </c>
       <c r="C73" s="16" t="n">
-        <v>4968</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C74" s="16" t="n">
-        <v>8413</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="16" t="n">
-        <v>5535</v>
+      <c r="C75" s="11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="true" outlineLevel="3">
@@ -1949,7 +1877,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>6925</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="true" outlineLevel="3">
@@ -1957,7 +1885,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>3810</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="true" outlineLevel="3">
@@ -1965,47 +1893,47 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B79" s="15" t="s">
+        <v>8305</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B79" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>5505</v>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C79" s="12" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>4890</v>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C80" s="11" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C81" s="11" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>11195</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B83" s="14" t="s">
+      <c r="C82" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="12" t="n">
-        <v>2786</v>
+      <c r="C83" s="11" t="n">
+        <v>292</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
@@ -2013,7 +1941,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>229</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -2021,7 +1949,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>797</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2029,7 +1957,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>234</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2037,7 +1965,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2045,23 +1973,23 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B90" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B90" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>66</v>
+      <c r="C90" s="12" t="n">
+        <v>8500</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2069,7 +1997,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2077,7 +2005,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>82</v>
+        <v>139</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2085,7 +2013,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>23</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2093,39 +2021,39 @@
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B96" s="14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="12" t="n">
-        <v>15303</v>
+      <c r="C96" s="11" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>169</v>
+      <c r="C97" s="16" t="n">
+        <v>2818</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>202</v>
+      <c r="C98" s="16" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
@@ -2133,7 +2061,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>224</v>
+        <v>775</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2141,7 +2069,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>284</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
@@ -2149,31 +2077,31 @@
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" ht="11" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="16" t="n">
-        <v>3945</v>
+      <c r="C102" s="11" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="16" t="n">
-        <v>2968</v>
+      <c r="C103" s="11" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="16" t="n">
-        <v>3050</v>
+      <c r="C104" s="11" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
@@ -2181,7 +2109,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>79</v>
+        <v>190</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
@@ -2189,7 +2117,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>121</v>
+        <v>621</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2197,7 +2125,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2205,7 +2133,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>123</v>
+        <v>438</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2213,7 +2141,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2221,7 +2149,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>289</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2229,7 +2157,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>813</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2237,7 +2165,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>81</v>
+        <v>271</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2245,7 +2173,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2253,7 +2181,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>714</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2261,15 +2189,15 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B116" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="116" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B116" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="11" t="n">
-        <v>86</v>
+      <c r="C116" s="12" t="n">
+        <v>13260</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2277,7 +2205,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>33</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2285,7 +2213,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2293,7 +2221,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2301,7 +2229,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>663</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2309,7 +2237,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>231</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2317,15 +2245,15 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="123" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B123" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="12" t="n">
-        <v>18781</v>
+      <c r="C123" s="11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2333,7 +2261,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2341,7 +2269,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2349,15 +2277,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>42</v>
+      <c r="C127" s="16" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2365,7 +2293,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>115</v>
+        <v>242</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2373,7 +2301,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2381,7 +2309,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2389,7 +2317,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>65</v>
+        <v>207</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2397,7 +2325,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>67</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2405,15 +2333,15 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
       <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="16" t="n">
-        <v>1109</v>
+      <c r="C134" s="11" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2421,7 +2349,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>279</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2429,7 +2357,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>28</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2437,7 +2365,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>133</v>
+        <v>53</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2445,15 +2373,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>72</v>
+        <v>308</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="16" t="n">
-        <v>1114</v>
+      <c r="C139" s="11" t="n">
+        <v>756</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2461,7 +2389,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2469,7 +2397,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2477,7 +2405,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>51</v>
+        <v>353</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2485,7 +2413,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2493,15 +2421,15 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="145" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="true" outlineLevel="3">
       <c r="B145" s="15" t="s">
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>84</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2509,7 +2437,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>316</v>
+        <v>111</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2517,15 +2445,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="148" ht="11" customHeight="true" outlineLevel="3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2533,15 +2461,15 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="150" ht="11" customHeight="true" outlineLevel="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="true" outlineLevel="3">
       <c r="B150" s="15" t="s">
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>358</v>
+        <v>382</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2549,7 +2477,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2557,15 +2485,15 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="153" ht="22" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,7 +2501,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2581,15 +2509,15 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="true" outlineLevel="3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="15" t="s">
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>193</v>
+        <v>46</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2597,15 +2525,15 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="158" ht="22" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2613,7 +2541,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>33</v>
+        <v>145</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2621,7 +2549,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2629,7 +2557,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>152</v>
+        <v>112</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2637,7 +2565,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>844</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2645,7 +2573,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>124</v>
+        <v>92</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2653,7 +2581,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>498</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2661,15 +2589,15 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>191</v>
+        <v>361</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="11" t="n">
-        <v>135</v>
+      <c r="C166" s="16" t="n">
+        <v>4011</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2677,7 +2605,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>212</v>
+        <v>85</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2685,7 +2613,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>154</v>
+        <v>429</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,7 +2621,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>116</v>
+        <v>49</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2701,7 +2629,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,7 +2637,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>956</v>
+        <v>155</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2717,7 +2645,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>207</v>
+        <v>302</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2725,7 +2653,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2733,23 +2661,23 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>15</v>
+        <v>577</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="16" t="n">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="176" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B176" s="15" t="s">
+      <c r="C175" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B176" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="16" t="n">
-        <v>4427</v>
+      <c r="C176" s="12" t="n">
+        <v>7729</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2757,7 +2685,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>108</v>
+        <v>169</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +2693,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>386</v>
+        <v>82</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2773,7 +2701,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>450</v>
+        <v>69</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2781,7 +2709,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>52</v>
+        <v>182</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2789,7 +2717,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>56</v>
+        <v>466</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2797,7 +2725,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2805,7 +2733,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2813,7 +2741,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2821,7 +2749,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>588</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2829,15 +2757,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="187" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B187" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="187" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="12" t="n">
-        <v>20384</v>
+      <c r="C187" s="11" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2845,7 +2773,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>413</v>
+        <v>342</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -2853,7 +2781,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>108</v>
+        <v>506</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2861,7 +2789,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>700</v>
+        <v>43</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2869,15 +2797,15 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>709</v>
+        <v>57</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="16" t="n">
-        <v>2290</v>
+      <c r="C192" s="11" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2885,7 +2813,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>74</v>
+        <v>448</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2893,7 +2821,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>359</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2901,7 +2829,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>59</v>
+        <v>379</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2909,15 +2837,15 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>236</v>
+        <v>155</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="11" t="n">
-        <v>101</v>
+      <c r="C197" s="16" t="n">
+        <v>1120</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2925,7 +2853,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>402</v>
+        <v>704</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -2933,7 +2861,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>570</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -2941,7 +2869,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>884</v>
+        <v>572</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2949,7 +2877,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>223</v>
+        <v>29</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2957,7 +2885,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>276</v>
+        <v>41</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,7 +2893,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>138</v>
+        <v>572</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -2973,7 +2901,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>259</v>
+        <v>110</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -2981,7 +2909,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>517</v>
+        <v>171</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2989,7 +2917,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>173</v>
+        <v>73</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2997,7 +2925,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>653</v>
+        <v>463</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3005,15 +2933,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="209" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B209" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="209" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B209" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="16" t="n">
-        <v>1628</v>
+      <c r="C209" s="12" t="n">
+        <v>1203</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3021,7 +2949,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>990</v>
+        <v>89</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3029,15 +2957,15 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>601</v>
+        <v>86</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="16" t="n">
-        <v>1186</v>
+      <c r="C212" s="11" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,7 +2973,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>29</v>
+        <v>171</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,15 +2981,15 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>611</v>
+        <v>64</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="16" t="n">
-        <v>1042</v>
+      <c r="C215" s="11" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3069,15 +2997,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>403</v>
+        <v>121</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="16" t="n">
-        <v>1050</v>
+      <c r="C217" s="11" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3085,15 +3013,15 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>932</v>
+        <v>77</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="16" t="n">
-        <v>1872</v>
+      <c r="C219" s="11" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3101,15 +3029,15 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="221" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B221" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="221" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B221" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="12" t="n">
-        <v>1875</v>
+      <c r="C221" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3117,7 +3045,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>251</v>
+        <v>34</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3125,15 +3053,15 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="224" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B224" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="224" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B224" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="11" t="n">
-        <v>340</v>
+      <c r="C224" s="12" t="n">
+        <v>6689</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3141,7 +3069,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3149,7 +3077,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>142</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3157,7 +3085,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3165,7 +3093,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>171</v>
+        <v>205</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3173,7 +3101,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>98</v>
+        <v>260</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3181,7 +3109,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3189,15 +3117,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="232" ht="11" customHeight="true" outlineLevel="3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3205,15 +3133,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B234" s="14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="12" t="n">
-        <v>15552</v>
+      <c r="C234" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3221,7 +3149,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>231</v>
+        <v>133</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3229,47 +3157,47 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="237" ht="11" customHeight="true" outlineLevel="3">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="237" ht="22" customHeight="true" outlineLevel="3">
       <c r="B237" s="15" t="s">
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="238" ht="11" customHeight="true" outlineLevel="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="238" ht="22" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="239" ht="11" customHeight="true" outlineLevel="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="240" ht="11" customHeight="true" outlineLevel="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="240" ht="22" customHeight="true" outlineLevel="3">
       <c r="B240" s="15" t="s">
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="241" ht="11" customHeight="true" outlineLevel="3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="241" ht="22" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>106</v>
+        <v>37</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3277,15 +3205,15 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="243" ht="22" customHeight="true" outlineLevel="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3293,7 +3221,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>41</v>
+        <v>285</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3301,7 +3229,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>184</v>
+        <v>18</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,7 +3237,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>134</v>
+        <v>722</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3317,7 +3245,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>207</v>
+        <v>934</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3325,47 +3253,47 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="249" ht="22" customHeight="true" outlineLevel="3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="250" ht="22" customHeight="true" outlineLevel="3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="251" ht="22" customHeight="true" outlineLevel="3">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="252" ht="22" customHeight="true" outlineLevel="3">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="true" outlineLevel="3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="254" ht="22" customHeight="true" outlineLevel="3">
@@ -3373,23 +3301,23 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="255" ht="22" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="256" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B256" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B256" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="11" t="n">
-        <v>59</v>
+      <c r="C256" s="12" t="n">
+        <v>8340</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3397,7 +3325,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>207</v>
+        <v>413</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3405,39 +3333,39 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="259" ht="11" customHeight="true" outlineLevel="3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="259" ht="22" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>338</v>
+        <v>9</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>35</v>
+      <c r="C260" s="16" t="n">
+        <v>1864</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="16" t="n">
-        <v>1187</v>
+      <c r="C261" s="11" t="n">
+        <v>367</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="16" t="n">
-        <v>1352</v>
+      <c r="C262" s="11" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3445,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>469</v>
+        <v>256</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3453,7 +3381,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>436</v>
+        <v>125</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3461,7 +3389,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>925</v>
+        <v>133</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3469,15 +3397,15 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>570</v>
+        <v>129</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="16" t="n">
-        <v>4609</v>
+      <c r="C267" s="11" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3485,31 +3413,31 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="16" t="n">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="270" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C269" s="11" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B271" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="12" t="n">
-        <v>14908</v>
+      <c r="C271" s="11" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3517,23 +3445,23 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>560</v>
+        <v>126</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="16" t="n">
-        <v>1030</v>
+      <c r="C273" s="11" t="n">
+        <v>349</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="16" t="n">
-        <v>2006</v>
+      <c r="C274" s="11" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3541,7 +3469,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>417</v>
+        <v>436</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3549,15 +3477,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="277" ht="11" customHeight="true" outlineLevel="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="277" ht="22" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>722</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3565,7 +3493,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>283</v>
+        <v>85</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3573,7 +3501,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>276</v>
+        <v>111</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3581,7 +3509,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>220</v>
+        <v>107</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3589,7 +3517,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>499</v>
+        <v>158</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3597,7 +3525,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,7 +3533,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>440</v>
+        <v>129</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3613,7 +3541,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>148</v>
+        <v>27</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3621,7 +3549,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>571</v>
+        <v>851</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3629,7 +3557,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>376</v>
+        <v>49</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3637,7 +3565,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>363</v>
+        <v>26</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3645,15 +3573,15 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="289" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B289" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B289" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="11" t="n">
-        <v>788</v>
+      <c r="C289" s="17" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3661,7 +3589,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3669,15 +3597,15 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B292" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B292" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="11" t="n">
-        <v>123</v>
+      <c r="C292" s="12" t="n">
+        <v>10977</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3685,7 +3613,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3693,39 +3621,39 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="296" ht="11" customHeight="true" outlineLevel="3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="16" t="n">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="297" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C296" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="C297" s="16" t="n">
-        <v>1580</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C297" s="11" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>423</v>
+        <v>50</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3733,7 +3661,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>6</v>
+        <v>163</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3741,15 +3669,15 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B301" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="17" t="n">
-        <v>159</v>
+      <c r="C301" s="11" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3757,7 +3685,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3765,31 +3693,31 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B304" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="12" t="n">
-        <v>19751</v>
-      </c>
-    </row>
-    <row r="305" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C304" s="11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="306" ht="11" customHeight="true" outlineLevel="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="306" ht="22" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="307" ht="22" customHeight="true" outlineLevel="3">
@@ -3797,7 +3725,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>549</v>
+        <v>36</v>
       </c>
     </row>
     <row r="308" ht="22" customHeight="true" outlineLevel="3">
@@ -3805,7 +3733,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="309" ht="22" customHeight="true" outlineLevel="3">
@@ -3813,7 +3741,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="310" ht="22" customHeight="true" outlineLevel="3">
@@ -3821,31 +3749,31 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>103</v>
+        <v>16</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -3853,7 +3781,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>142</v>
+        <v>29</v>
       </c>
     </row>
     <row r="315" ht="22" customHeight="true" outlineLevel="3">
@@ -3861,23 +3789,23 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="316" ht="11" customHeight="true" outlineLevel="3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="316" ht="22" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="317" ht="22" customHeight="true" outlineLevel="3">
       <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -3885,7 +3813,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>108</v>
+        <v>197</v>
       </c>
     </row>
     <row r="319" ht="22" customHeight="true" outlineLevel="3">
@@ -3893,7 +3821,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="true" outlineLevel="3">
@@ -3901,7 +3829,7 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>216</v>
+        <v>25</v>
       </c>
     </row>
     <row r="321" ht="22" customHeight="true" outlineLevel="3">
@@ -3909,7 +3837,7 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="322" ht="22" customHeight="true" outlineLevel="3">
@@ -3917,7 +3845,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="323" ht="22" customHeight="true" outlineLevel="3">
@@ -3925,31 +3853,31 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>157</v>
+        <v>215</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C325" s="16" t="n">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="true" outlineLevel="3">
@@ -3957,55 +3885,55 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="328" ht="22" customHeight="true" outlineLevel="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>87</v>
+        <v>178</v>
       </c>
     </row>
     <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="330" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C329" s="16" t="n">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="331" ht="22" customHeight="true" outlineLevel="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="332" ht="22" customHeight="true" outlineLevel="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="333" ht="22" customHeight="true" outlineLevel="3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>96</v>
+        <v>173</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="true" outlineLevel="3">
@@ -4013,15 +3941,15 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="335" ht="22" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>56</v>
+        <v>259</v>
       </c>
     </row>
     <row r="336" ht="22" customHeight="true" outlineLevel="3">
@@ -4029,7 +3957,7 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>16</v>
+        <v>129</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -4037,7 +3965,7 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>21</v>
+        <v>197</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4045,239 +3973,47 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="340" ht="22" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="342" ht="22" customHeight="true" outlineLevel="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="344" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B344" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="C344" s="11" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B345" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="C345" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="346" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B346" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C346" s="16" t="n">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="347" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B347" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="C347" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="348" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B348" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="C348" s="11" t="n">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B349" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="C349" s="11" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B350" s="15" t="s">
         <v>349</v>
-      </c>
-      <c r="C350" s="16" t="n">
-        <v>2448</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B351" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="C351" s="11" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="352" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B352" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="C352" s="11" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B353" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="C353" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B354" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C354" s="11" t="n">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B355" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="C355" s="11" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="356" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B356" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="C356" s="11" t="n">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B357" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="C357" s="11" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="358" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B358" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="C358" s="16" t="n">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B359" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C359" s="11" t="n">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="360" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B360" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="C360" s="11" t="n">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B361" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="C361" s="11" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B362" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="C362" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="363" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B363" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="C363" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="364" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B364" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="C364" s="11" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B365" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="C365" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B366" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="C366" s="16" t="n">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B367" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="C367" s="11" t="n">
-        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="350">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 30.01.2026 8:15:12</t>
+    <t>Период: на 11.02.2026 19:55:11</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -89,9 +89,6 @@
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Какао-порошок 100г/40 УБ</t>
-  </si>
-  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 35г /36шт</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -137,6 +137,9 @@
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
@@ -152,7 +155,10 @@
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до плову УБ 25г /36шт</t>
+    <t>Приправа до м'яса УБ 25г /34шт</t>
+  </si>
+  <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт</t>
@@ -167,6 +173,9 @@
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -185,6 +194,12 @@
     <t>СПЕЦІЇ</t>
   </si>
   <si>
+    <t>Гвоздика ціла УБ 10г /30шт</t>
+  </si>
+  <si>
+    <t>Кориця мелена УБ 15г /38шт</t>
+  </si>
+  <si>
     <t>Коріандр мелений УБ 20г /30шт</t>
   </si>
   <si>
@@ -197,6 +212,9 @@
     <t>Паприка копчена мелена УБ 20г /34шт</t>
   </si>
   <si>
+    <t>Паприка мелена УБ 20г /34шт</t>
+  </si>
+  <si>
     <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
@@ -233,18 +251,9 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
@@ -284,9 +293,6 @@
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -320,18 +326,33 @@
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
@@ -341,6 +362,9 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -410,21 +434,12 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -437,12 +452,12 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -452,34 +467,46 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
@@ -509,9 +536,6 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -578,9 +602,6 @@
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
-    <t>Milky Splash з молочною начинкою ВКФ 1кг /5пак</t>
-  </si>
-  <si>
     <t>Minky Binky з желейною начинкою РЦ 1кг /6пак</t>
   </si>
   <si>
@@ -596,6 +617,9 @@
     <t>Peppinezzz РЦ 0.9кг /6пак</t>
   </si>
   <si>
+    <t>Roshen Butter-Milk КрКФ 1кг /8шт</t>
+  </si>
+  <si>
     <t>Roshen Yogurtini РЦ 1кг /8шт</t>
   </si>
   <si>
@@ -656,9 +680,6 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -698,6 +719,9 @@
     <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
   </si>
   <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
@@ -722,12 +746,18 @@
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
+    <t>Lovita Classic Cookies арахіс ККФ 150г /16шт</t>
+  </si>
+  <si>
     <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
   </si>
   <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
@@ -740,6 +770,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
+  </si>
+  <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
   </si>
   <si>
@@ -761,15 +797,9 @@
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
-  </si>
-  <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -779,12 +809,12 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ККФ 370г /24шт</t>
+  </si>
+  <si>
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
@@ -818,18 +848,15 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White 1кг/5</t>
-  </si>
-  <si>
-    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
     <t>KONAFETTO nero ККФ 1кг /5пак /</t>
   </si>
   <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
@@ -842,12 +869,18 @@
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -857,15 +890,27 @@
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
@@ -911,15 +956,9 @@
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -932,15 +971,9 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
@@ -974,6 +1007,9 @@
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
+  </si>
+  <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
@@ -983,9 +1019,6 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
@@ -998,9 +1031,6 @@
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1013,31 +1043,22 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
+  </si>
+  <si>
+    <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
@@ -1292,7 +1313,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C343"/>
+  <dimension ref="C350"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1357,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1365,7 +1386,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>120262</v>
+        <v>175785</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1373,7 +1394,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>27903</v>
+        <v>41777</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1381,7 +1402,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>4220</v>
+        <v>6845</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1389,7 +1410,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1397,15 +1418,15 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>230</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
       <c r="B17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>543</v>
+      <c r="C17" s="16" t="n">
+        <v>1421</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1421,15 +1442,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>74</v>
+        <v>674</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>488</v>
+      <c r="C20" s="16" t="n">
+        <v>1051</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1437,7 +1458,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1445,7 +1466,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>264</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1453,7 +1474,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>750</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1461,31 +1482,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>16</v>
+        <v>838</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B26" s="15" t="s">
+      <c r="C25" s="16" t="n">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B26" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B27" s="14" t="s">
+      <c r="C26" s="12" t="n">
+        <v>15267</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>10761</v>
+      <c r="C27" s="16" t="n">
+        <v>2901</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1493,15 +1514,15 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>1401</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>1574</v>
+      <c r="C29" s="11" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1517,7 +1538,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>1506</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1525,7 +1546,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1541,7 +1562,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>3721</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1549,7 +1570,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>442</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1557,7 +1578,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1565,7 +1586,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>59</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1573,7 +1594,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>42</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1581,7 +1602,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>331</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1589,7 +1610,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>232</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1597,23 +1618,23 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B42" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="12" t="n">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B43" s="15" t="s">
+      <c r="C42" s="11" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B43" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>471</v>
+      <c r="C43" s="12" t="n">
+        <v>6097</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1621,7 +1642,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>140</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1629,7 +1650,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>99</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1637,7 +1658,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>428</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1645,7 +1666,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>198</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1653,7 +1674,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>123</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1661,7 +1682,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>86</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1669,7 +1690,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>108</v>
+        <v>862</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1677,7 +1698,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>71</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1685,7 +1706,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>197</v>
+        <v>645</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1693,7 +1714,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1701,15 +1722,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B55" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="12" t="n">
-        <v>10811</v>
+      <c r="C55" s="11" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1717,31 +1738,31 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>350</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B58" s="15" t="s">
+      <c r="C57" s="16" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B58" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>3510</v>
+      <c r="C58" s="12" t="n">
+        <v>13568</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>1210</v>
+      <c r="C59" s="11" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1749,7 +1770,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>1362</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1757,15 +1778,15 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>10</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="n">
-        <v>72</v>
+      <c r="C62" s="16" t="n">
+        <v>1048</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1773,7 +1794,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>1273</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -1781,63 +1802,63 @@
         <v>63</v>
       </c>
       <c r="C64" s="16" t="n">
-        <v>2756</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>93</v>
+      <c r="C65" s="16" t="n">
+        <v>2158</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="67" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B67" s="13" t="s">
+      <c r="C66" s="16" t="n">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>92359</v>
-      </c>
-    </row>
-    <row r="68" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B68" s="14" t="s">
+      <c r="C67" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="12" t="n">
-        <v>33742</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C68" s="11" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="true" outlineLevel="3">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>1948</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>5288</v>
+      <c r="C71" s="11" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -1845,23 +1866,23 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B73" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B73" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="16" t="n">
-        <v>6200</v>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B74" s="15" t="s">
+      <c r="C73" s="12" t="n">
+        <v>134008</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B74" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>1800</v>
+      <c r="C74" s="12" t="n">
+        <v>18997</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="true" outlineLevel="3">
@@ -1869,7 +1890,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>360</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="true" outlineLevel="3">
@@ -1877,15 +1898,15 @@
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>4814</v>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="true" outlineLevel="3">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>4100</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="true" outlineLevel="3">
@@ -1893,39 +1914,39 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>8305</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B79" s="14" t="s">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="12" t="n">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="80" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C79" s="16" t="n">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C80" s="16" t="n">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B82" s="15" t="s">
+      <c r="C81" s="16" t="n">
+        <v>6235</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B82" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>71</v>
+      <c r="C82" s="12" t="n">
+        <v>1959</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
@@ -1933,7 +1954,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
@@ -1941,7 +1962,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>178</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -1949,7 +1970,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>326</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -1957,7 +1978,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>75</v>
+        <v>298</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -1965,7 +1986,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>9</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -1976,20 +1997,20 @@
         <v>312</v>
       </c>
     </row>
-    <row r="89" ht="22" customHeight="true" outlineLevel="3">
+    <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B90" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="12" t="n">
-        <v>8500</v>
+      <c r="C90" s="11" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -1997,15 +2018,15 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B92" s="15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B92" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>139</v>
+      <c r="C92" s="12" t="n">
+        <v>58424</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2013,7 +2034,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>237</v>
+        <v>339</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2021,7 +2042,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2029,7 +2050,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>344</v>
+        <v>437</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2037,15 +2058,15 @@
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>45</v>
+        <v>328</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>2818</v>
+      <c r="C97" s="11" t="n">
+        <v>523</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
@@ -2053,15 +2074,15 @@
         <v>97</v>
       </c>
       <c r="C98" s="16" t="n">
-        <v>1400</v>
+        <v>18725</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>775</v>
+      <c r="C99" s="16" t="n">
+        <v>24643</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2069,15 +2090,15 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>74</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>115</v>
+      <c r="C101" s="16" t="n">
+        <v>9375</v>
       </c>
     </row>
     <row r="102" ht="11" customHeight="true" outlineLevel="3">
@@ -2085,7 +2106,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
@@ -2093,7 +2114,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2101,7 +2122,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
@@ -2109,7 +2130,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>190</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
@@ -2117,7 +2138,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>621</v>
+        <v>74</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2125,7 +2146,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2133,7 +2154,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>438</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2141,7 +2162,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2149,15 +2170,15 @@
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2165,7 +2186,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>271</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2173,7 +2194,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>59</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2181,7 +2202,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>131</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2189,15 +2210,15 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B116" s="14" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="116" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="12" t="n">
-        <v>13260</v>
+      <c r="C116" s="11" t="n">
+        <v>721</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2205,7 +2226,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>198</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2213,7 +2234,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>21</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2221,7 +2242,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2229,7 +2250,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>17</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2237,7 +2258,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2245,7 +2266,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>111</v>
+        <v>487</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2253,15 +2274,15 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B124" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>34</v>
+      <c r="C124" s="12" t="n">
+        <v>16458</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2269,7 +2290,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>31</v>
+        <v>193</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2277,15 +2298,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="16" t="n">
-        <v>1009</v>
+      <c r="C127" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2293,7 +2314,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>242</v>
+        <v>86</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2301,7 +2322,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2309,7 +2330,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2317,7 +2338,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>207</v>
+        <v>78</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2325,7 +2346,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>140</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2333,7 +2354,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2341,7 +2362,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>159</v>
+        <v>68</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2349,7 +2370,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>1</v>
+        <v>844</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2357,7 +2378,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2365,7 +2386,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2373,7 +2394,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>308</v>
+        <v>47</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2381,7 +2402,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>756</v>
+        <v>81</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2389,7 +2410,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>4</v>
+        <v>147</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2397,7 +2418,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>50</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2405,7 +2426,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>353</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2413,7 +2434,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>13</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2421,15 +2442,15 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" ht="22" customHeight="true" outlineLevel="3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="15" t="s">
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>319</v>
+        <v>50</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2437,7 +2458,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>111</v>
+        <v>210</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2445,15 +2466,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="148" ht="22" customHeight="true" outlineLevel="3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2461,7 +2482,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="150" ht="22" customHeight="true" outlineLevel="3">
@@ -2469,23 +2490,23 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="151" ht="11" customHeight="true" outlineLevel="3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="true" outlineLevel="3">
       <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="true" outlineLevel="3">
       <c r="B152" s="15" t="s">
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2493,15 +2514,15 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>148</v>
+        <v>107</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>78</v>
+      <c r="C154" s="16" t="n">
+        <v>1692</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2509,23 +2530,23 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="156" ht="11" customHeight="true" outlineLevel="3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="true" outlineLevel="3">
       <c r="B156" s="15" t="s">
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="157" ht="11" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2533,23 +2554,23 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="160" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C159" s="16" t="n">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="true" outlineLevel="3">
       <c r="B160" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>110</v>
+        <v>332</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2557,7 +2578,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>112</v>
+        <v>47</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2565,7 +2586,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>174</v>
+        <v>134</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,7 +2594,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2581,7 +2602,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>13</v>
+        <v>231</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2589,15 +2610,15 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>361</v>
+        <v>41</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="16" t="n">
-        <v>4011</v>
+      <c r="C166" s="11" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2605,7 +2626,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2613,7 +2634,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>429</v>
+        <v>193</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2621,7 +2642,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2629,7 +2650,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>56</v>
+        <v>212</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2637,7 +2658,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2645,7 +2666,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>302</v>
+        <v>101</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2653,15 +2674,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>18</v>
+        <v>251</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>577</v>
+      <c r="C174" s="16" t="n">
+        <v>3500</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2669,15 +2690,15 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="176" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B176" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="176" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B176" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="12" t="n">
-        <v>7729</v>
+      <c r="C176" s="11" t="n">
+        <v>182</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2685,7 +2706,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>169</v>
+        <v>37</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,7 +2714,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>82</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2701,7 +2722,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,7 +2730,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>182</v>
+        <v>287</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2717,7 +2738,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>466</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2725,7 +2746,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>74</v>
+        <v>554</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2733,15 +2754,15 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="184" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B184" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B184" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>46</v>
+      <c r="C184" s="12" t="n">
+        <v>11535</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2749,7 +2770,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>100</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2757,7 +2778,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +2786,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>132</v>
+        <v>851</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2773,15 +2794,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>342</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>506</v>
+      <c r="C189" s="16" t="n">
+        <v>1050</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2789,7 +2810,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2797,7 +2818,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2805,7 +2826,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2813,7 +2834,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>448</v>
+        <v>115</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2821,7 +2842,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2829,7 +2850,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>379</v>
+        <v>284</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2837,15 +2858,15 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>155</v>
+        <v>255</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="16" t="n">
-        <v>1120</v>
+      <c r="C197" s="11" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2853,7 +2874,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>704</v>
+        <v>370</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -2861,7 +2882,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -2869,7 +2890,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>572</v>
+        <v>305</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2877,7 +2898,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>29</v>
+        <v>354</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2885,7 +2906,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2893,7 +2914,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>572</v>
+        <v>156</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -2901,7 +2922,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>110</v>
+        <v>680</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -2909,7 +2930,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>171</v>
+        <v>524</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2917,7 +2938,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>73</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2925,7 +2946,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>463</v>
+        <v>229</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -2933,15 +2954,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="209" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B209" s="14" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="209" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="12" t="n">
-        <v>1203</v>
+      <c r="C209" s="11" t="n">
+        <v>905</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -2949,7 +2970,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>89</v>
+        <v>49</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -2957,7 +2978,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>86</v>
+        <v>761</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,7 +2986,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>29</v>
+        <v>542</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -2973,7 +2994,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>171</v>
+        <v>811</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -2981,7 +3002,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>64</v>
+        <v>356</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -2989,7 +3010,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>65</v>
+        <v>422</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -2997,15 +3018,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="217" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B217" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="217" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B217" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>82</v>
+      <c r="C217" s="12" t="n">
+        <v>2015</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3013,7 +3034,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>77</v>
+        <v>295</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3021,7 +3042,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>148</v>
+        <v>32</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3029,7 +3050,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>107</v>
+        <v>251</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3037,7 +3058,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,7 +3066,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>34</v>
+        <v>301</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,15 +3074,15 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="224" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B224" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="224" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B224" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="12" t="n">
-        <v>6689</v>
+      <c r="C224" s="11" t="n">
+        <v>341</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3069,7 +3090,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3077,7 +3098,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>55</v>
+        <v>335</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3085,7 +3106,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3093,7 +3114,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3101,7 +3122,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>260</v>
+        <v>34</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3109,23 +3130,23 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="231" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B231" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B231" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="11" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C231" s="12" t="n">
+        <v>7036</v>
+      </c>
+    </row>
+    <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>58</v>
+        <v>274</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3133,7 +3154,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>113</v>
+        <v>210</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3141,7 +3162,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>75</v>
+        <v>289</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3149,7 +3170,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>133</v>
+        <v>182</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3157,31 +3178,31 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="237" ht="22" customHeight="true" outlineLevel="3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="15" t="s">
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="238" ht="22" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="239" ht="22" customHeight="true" outlineLevel="3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>44</v>
+        <v>397</v>
       </c>
     </row>
     <row r="240" ht="22" customHeight="true" outlineLevel="3">
@@ -3189,15 +3210,15 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="241" ht="22" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3205,7 +3226,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3213,7 +3234,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>139</v>
+        <v>195</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3221,7 +3242,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>285</v>
+        <v>222</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3229,79 +3250,79 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="246" ht="11" customHeight="true" outlineLevel="3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="246" ht="22" customHeight="true" outlineLevel="3">
       <c r="B246" s="15" t="s">
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="247" ht="11" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="247" ht="22" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="248" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="249" ht="11" customHeight="true" outlineLevel="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="250" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="251" ht="11" customHeight="true" outlineLevel="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="252" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="253" ht="11" customHeight="true" outlineLevel="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="254" ht="22" customHeight="true" outlineLevel="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,15 +3330,15 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="256" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B256" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="256" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="12" t="n">
-        <v>8340</v>
+      <c r="C256" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3325,7 +3346,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>413</v>
+        <v>130</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3333,23 +3354,23 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="259" ht="22" customHeight="true" outlineLevel="3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>9</v>
+        <v>451</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="16" t="n">
-        <v>1864</v>
+      <c r="C260" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3357,7 +3378,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>367</v>
+        <v>615</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3365,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>192</v>
+        <v>705</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3373,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3381,23 +3402,23 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="266" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B266" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B266" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="11" t="n">
-        <v>129</v>
+      <c r="C266" s="12" t="n">
+        <v>9085</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3405,7 +3426,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>94</v>
+        <v>221</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3413,23 +3434,23 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="269" ht="11" customHeight="true" outlineLevel="3">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>440</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="11" t="n">
-        <v>61</v>
+      <c r="C270" s="16" t="n">
+        <v>1061</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3437,7 +3458,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>168</v>
+        <v>302</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3445,7 +3466,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>126</v>
+        <v>94</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3453,7 +3474,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>349</v>
+        <v>544</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3461,7 +3482,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>438</v>
+        <v>92</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3469,7 +3490,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>436</v>
+        <v>97</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3477,15 +3498,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="277" ht="22" customHeight="true" outlineLevel="3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>4</v>
+        <v>400</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3493,7 +3514,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3501,7 +3522,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>111</v>
+        <v>150</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3509,7 +3530,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>107</v>
+        <v>328</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3517,7 +3538,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>158</v>
+        <v>257</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3525,7 +3546,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>80</v>
+        <v>334</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3533,7 +3554,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>129</v>
+        <v>329</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3541,7 +3562,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>27</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3549,7 +3570,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>851</v>
+        <v>550</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3557,31 +3578,31 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="287" ht="11" customHeight="true" outlineLevel="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="289" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B289" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="17" t="n">
-        <v>159</v>
+      <c r="C289" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3589,31 +3610,31 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="291" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B292" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="12" t="n">
-        <v>10977</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C292" s="11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3621,7 +3642,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>168</v>
+        <v>51</v>
       </c>
     </row>
     <row r="295" ht="22" customHeight="true" outlineLevel="3">
@@ -3629,15 +3650,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="true" outlineLevel="3">
@@ -3645,15 +3666,15 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="11" t="n">
-        <v>50</v>
+      <c r="C298" s="16" t="n">
+        <v>1358</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3661,7 +3682,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>163</v>
+        <v>363</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3669,15 +3690,15 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>102</v>
+        <v>409</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3685,7 +3706,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3693,55 +3714,55 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="304" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B304" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B304" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C304" s="17" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="306" ht="22" customHeight="true" outlineLevel="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="307" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B307" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B307" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="308" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C307" s="12" t="n">
+        <v>8353</v>
+      </c>
+    </row>
+    <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>30</v>
+        <v>148</v>
       </c>
     </row>
     <row r="310" ht="22" customHeight="true" outlineLevel="3">
@@ -3749,7 +3770,7 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>237</v>
+        <v>127</v>
       </c>
     </row>
     <row r="311" ht="22" customHeight="true" outlineLevel="3">
@@ -3757,7 +3778,7 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="312" ht="22" customHeight="true" outlineLevel="3">
@@ -3765,15 +3786,15 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>16</v>
+        <v>329</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -3781,23 +3802,23 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="315" ht="22" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="true" outlineLevel="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>15</v>
+        <v>149</v>
       </c>
     </row>
     <row r="317" ht="22" customHeight="true" outlineLevel="3">
@@ -3805,15 +3826,15 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="318" ht="11" customHeight="true" outlineLevel="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="318" ht="22" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>197</v>
+        <v>342</v>
       </c>
     </row>
     <row r="319" ht="22" customHeight="true" outlineLevel="3">
@@ -3821,7 +3842,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>43</v>
+        <v>373</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="true" outlineLevel="3">
@@ -3829,7 +3850,7 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="321" ht="22" customHeight="true" outlineLevel="3">
@@ -3837,7 +3858,7 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>108</v>
+        <v>148</v>
       </c>
     </row>
     <row r="322" ht="22" customHeight="true" outlineLevel="3">
@@ -3845,7 +3866,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>6</v>
+        <v>170</v>
       </c>
     </row>
     <row r="323" ht="22" customHeight="true" outlineLevel="3">
@@ -3853,31 +3874,31 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>215</v>
+        <v>143</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="16" t="n">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C325" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>80</v>
+        <v>527</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="true" outlineLevel="3">
@@ -3885,23 +3906,23 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="328" ht="11" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="16" t="n">
-        <v>1972</v>
+      <c r="C329" s="11" t="n">
+        <v>177</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -3909,31 +3930,31 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="331" ht="11" customHeight="true" outlineLevel="3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="331" ht="22" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="332" ht="11" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="332" ht="22" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="true" outlineLevel="3">
@@ -3941,7 +3962,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -3949,7 +3970,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>259</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" ht="22" customHeight="true" outlineLevel="3">
@@ -3957,7 +3978,7 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>129</v>
+        <v>477</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -3965,7 +3986,7 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -3973,15 +3994,15 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>12</v>
+        <v>574</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -3989,7 +4010,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>220</v>
+        <v>307</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -3997,7 +4018,7 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>73</v>
+        <v>250</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4005,7 +4026,7 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>928</v>
+        <v>268</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4013,7 +4034,63 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B344" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C344" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B345" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C345" s="11" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B346" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C346" s="11" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B347" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B348" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C348" s="11" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B349" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C349" s="11" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B350" s="15" t="s">
         <v>349</v>
+      </c>
+      <c r="C350" s="11" t="n">
+        <v>645</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="354">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 11.02.2026 19:55:11</t>
+    <t>Период: на 16.02.2026 7:55:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -161,6 +161,9 @@
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до плову УБ 25г /36шт</t>
+  </si>
+  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
@@ -176,9 +179,6 @@
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
-  </si>
-  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
@@ -248,21 +248,42 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
@@ -338,9 +359,6 @@
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -602,6 +620,9 @@
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
+    <t>Milky Splash з молочною начинкою ВКФ 1кг /5пак</t>
+  </si>
+  <si>
     <t>Minky Binky з желейною начинкою РЦ 1кг /6пак</t>
   </si>
   <si>
@@ -797,9 +818,6 @@
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -851,9 +869,6 @@
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
-  </si>
-  <si>
     <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -914,6 +929,9 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1044,12 +1062,6 @@
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
@@ -1313,7 +1325,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C350"/>
+  <dimension ref="C354"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1378,7 +1390,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1386,7 +1398,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>175785</v>
+        <v>132811</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1394,7 +1406,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41777</v>
+        <v>28389</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1402,15 +1414,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>6845</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>770</v>
+      <c r="C15" s="16" t="n">
+        <v>1060</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1418,7 +1430,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>378</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1426,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>1421</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1442,15 +1454,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>674</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1051</v>
+      <c r="C20" s="11" t="n">
+        <v>709</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1466,7 +1478,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1474,7 +1486,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>361</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1482,7 +1494,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>838</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1490,7 +1502,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>1155</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="2">
@@ -1498,7 +1510,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>15267</v>
+        <v>9846</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1506,15 +1518,15 @@
         <v>26</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>2901</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>3843</v>
+      <c r="C28" s="11" t="n">
+        <v>541</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1522,7 +1534,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>434</v>
+        <v>383</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1537,8 +1549,8 @@
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>1616</v>
+      <c r="C31" s="11" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1562,7 +1574,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>3411</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1570,7 +1582,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>312</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1586,7 +1598,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1602,7 +1614,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1610,7 +1622,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1618,7 +1630,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>158</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -1626,7 +1638,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="2">
@@ -1634,7 +1646,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>6097</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1642,7 +1654,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>277</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1650,7 +1662,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>194</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1658,7 +1670,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1666,7 +1678,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1674,7 +1686,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1682,7 +1694,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1690,7 +1702,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>862</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1698,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>272</v>
+        <v>847</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1706,7 +1718,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>645</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1714,7 +1726,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>9</v>
+        <v>624</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1722,7 +1734,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1730,7 +1742,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>260</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1738,15 +1750,15 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="16" t="n">
-        <v>2225</v>
+      <c r="C57" s="11" t="n">
+        <v>895</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="2">
@@ -1754,7 +1766,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="12" t="n">
-        <v>13568</v>
+        <v>7941</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1762,15 +1774,15 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>192</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>1213</v>
+      <c r="C60" s="11" t="n">
+        <v>948</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1778,15 +1790,15 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>527</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>1048</v>
+      <c r="C62" s="11" t="n">
+        <v>623</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1794,15 +1806,15 @@
         <v>62</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>2005</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>1059</v>
+      <c r="C64" s="11" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -1810,15 +1822,15 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>2158</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>1016</v>
+      <c r="C66" s="11" t="n">
+        <v>991</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -1834,7 +1846,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>188</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -1842,15 +1854,15 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>779</v>
+        <v>697</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>3165</v>
+      <c r="C70" s="11" t="n">
+        <v>607</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -1858,7 +1870,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -1866,7 +1878,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="1">
@@ -1874,7 +1886,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="12" t="n">
-        <v>134008</v>
+        <v>104422</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="2">
@@ -1882,7 +1894,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>18997</v>
+        <v>24247</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="true" outlineLevel="3">
@@ -1890,7 +1902,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="true" outlineLevel="3">
@@ -1898,31 +1910,31 @@
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="16" t="n">
-        <v>2588</v>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C77" s="11" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>4790</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="true" outlineLevel="3">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>1964</v>
+      <c r="C79" s="11" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="true" outlineLevel="3">
@@ -1930,79 +1942,79 @@
         <v>79</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>2120</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>6235</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B82" s="14" t="s">
+      <c r="C81" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="12" t="n">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C82" s="16" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C85" s="16" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C87" s="16" t="n">
+        <v>5365</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B89" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="89" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B89" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>57</v>
+      <c r="C89" s="17" t="n">
+        <v>857</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2010,7 +2022,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>144</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2018,15 +2030,15 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B92" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="12" t="n">
-        <v>58424</v>
+      <c r="C92" s="11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2034,7 +2046,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>339</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2042,7 +2054,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2050,7 +2062,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>437</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2058,7 +2070,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>328</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
@@ -2066,23 +2078,23 @@
         <v>96</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>523</v>
+        <v>127</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>18725</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B99" s="15" t="s">
+      <c r="C98" s="11" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B99" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="16" t="n">
-        <v>24643</v>
+      <c r="C99" s="12" t="n">
+        <v>41053</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2090,15 +2102,15 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>125</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="16" t="n">
-        <v>9375</v>
+      <c r="C101" s="11" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="102" ht="11" customHeight="true" outlineLevel="3">
@@ -2106,7 +2118,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>38</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
@@ -2114,7 +2126,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>154</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2122,23 +2134,23 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>149</v>
+      <c r="C105" s="16" t="n">
+        <v>13300</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>74</v>
+      <c r="C106" s="16" t="n">
+        <v>19643</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2146,15 +2158,15 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>143</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>102</v>
+      <c r="C108" s="16" t="n">
+        <v>4550</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2162,7 +2174,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>181</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2170,15 +2182,15 @@
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>176</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2186,7 +2198,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>140</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2194,7 +2206,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>359</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2202,7 +2214,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2210,7 +2222,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>209</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2218,15 +2230,15 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>128</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2234,7 +2246,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2242,7 +2254,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>33</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2250,7 +2262,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>158</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2258,7 +2270,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>115</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2266,7 +2278,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>487</v>
+        <v>660</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2274,15 +2286,15 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B124" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="12" t="n">
-        <v>16458</v>
+      <c r="C124" s="11" t="n">
+        <v>193</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2290,7 +2302,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>193</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2298,7 +2310,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2306,7 +2318,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>68</v>
+        <v>163</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2314,7 +2326,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>86</v>
+        <v>433</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2322,15 +2334,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B130" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B130" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>106</v>
+      <c r="C130" s="12" t="n">
+        <v>14878</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2338,7 +2350,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>78</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2346,7 +2358,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2354,7 +2366,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2362,7 +2374,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2370,7 +2382,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>844</v>
+        <v>90</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2378,7 +2390,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>235</v>
+        <v>104</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2386,7 +2398,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2394,7 +2406,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2402,7 +2414,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2410,7 +2422,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2418,7 +2430,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>178</v>
+        <v>799</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2426,7 +2438,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>23</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2434,7 +2446,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>302</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2442,7 +2454,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>443</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2450,7 +2462,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2458,7 +2470,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2466,7 +2478,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>355</v>
+        <v>47</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2474,7 +2486,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2482,31 +2494,31 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="150" ht="22" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150" ht="11" customHeight="true" outlineLevel="3">
       <c r="B150" s="15" t="s">
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="151" ht="22" customHeight="true" outlineLevel="3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="151" ht="11" customHeight="true" outlineLevel="3">
       <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="152" ht="22" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="15" t="s">
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2514,15 +2526,15 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>107</v>
+        <v>355</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="16" t="n">
-        <v>1692</v>
+      <c r="C154" s="11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2530,7 +2542,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>297</v>
+        <v>14</v>
       </c>
     </row>
     <row r="156" ht="22" customHeight="true" outlineLevel="3">
@@ -2538,7 +2550,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>132</v>
+        <v>728</v>
       </c>
     </row>
     <row r="157" ht="22" customHeight="true" outlineLevel="3">
@@ -2546,31 +2558,31 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="158" ht="11" customHeight="true" outlineLevel="3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="true" outlineLevel="3">
       <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="16" t="n">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="160" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C159" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="11" t="n">
-        <v>332</v>
+      <c r="C160" s="16" t="n">
+        <v>1626</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2578,23 +2590,23 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="162" ht="11" customHeight="true" outlineLevel="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2602,23 +2614,23 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>231</v>
+        <v>51</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="166" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C165" s="16" t="n">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>144</v>
+        <v>315</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2626,7 +2638,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2634,7 +2646,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>193</v>
+        <v>132</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2642,7 +2654,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2650,7 +2662,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2658,7 +2670,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>174</v>
+        <v>39</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2666,7 +2678,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2674,15 +2686,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>251</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="16" t="n">
-        <v>3500</v>
+      <c r="C174" s="11" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2690,7 +2702,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>220</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2698,7 +2710,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>182</v>
+        <v>27</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2706,7 +2718,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>37</v>
+        <v>174</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2714,7 +2726,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>179</v>
+        <v>99</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2722,15 +2734,15 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>287</v>
+      <c r="C180" s="16" t="n">
+        <v>3424</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2738,7 +2750,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2746,7 +2758,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>554</v>
+        <v>174</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2754,15 +2766,15 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="184" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B184" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="184" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="12" t="n">
-        <v>11535</v>
+      <c r="C184" s="11" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2770,7 +2782,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>185</v>
+        <v>149</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2778,7 +2790,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>56</v>
+        <v>287</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2786,7 +2798,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>851</v>
+        <v>60</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2794,23 +2806,23 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>186</v>
+        <v>530</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="16" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="190" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B190" s="15" t="s">
+      <c r="C189" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B190" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="11" t="n">
-        <v>74</v>
+      <c r="C190" s="12" t="n">
+        <v>6449</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2818,7 +2830,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2826,7 +2838,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2834,7 +2846,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>115</v>
+        <v>570</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2842,7 +2854,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2850,7 +2862,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>284</v>
+        <v>101</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2858,7 +2870,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>255</v>
+        <v>74</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2866,7 +2878,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2874,7 +2886,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>370</v>
+        <v>18</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -2882,7 +2894,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -2890,7 +2902,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>305</v>
+        <v>50</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2898,7 +2910,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>354</v>
+        <v>125</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2906,7 +2918,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2914,7 +2926,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -2922,7 +2934,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>680</v>
+        <v>131</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -2930,7 +2942,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>524</v>
+        <v>277</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2938,7 +2950,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>460</v>
+        <v>58</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2946,7 +2958,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>229</v>
+        <v>185</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -2954,7 +2966,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>713</v>
+        <v>335</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -2962,7 +2974,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>905</v>
+        <v>123</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -2970,7 +2982,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -2978,7 +2990,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>761</v>
+        <v>501</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -2986,7 +2998,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>542</v>
+        <v>31</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -2994,7 +3006,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>811</v>
+        <v>357</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3002,7 +3014,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>356</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3010,7 +3022,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3018,15 +3030,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="217" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B217" s="14" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="217" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="12" t="n">
-        <v>2015</v>
+      <c r="C217" s="11" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3034,7 +3046,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>295</v>
+        <v>624</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3042,7 +3054,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3050,7 +3062,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>251</v>
+        <v>494</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3058,7 +3070,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3066,7 +3078,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>301</v>
+        <v>35</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3074,15 +3086,15 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="224" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B224" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="224" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B224" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="11" t="n">
-        <v>341</v>
+      <c r="C224" s="12" t="n">
+        <v>1189</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3090,7 +3102,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>68</v>
+        <v>280</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3098,7 +3110,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>335</v>
+        <v>28</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3106,7 +3118,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>174</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3114,7 +3126,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3130,15 +3142,15 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="231" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B231" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="231" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="12" t="n">
-        <v>7036</v>
+      <c r="C231" s="11" t="n">
+        <v>334</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3146,7 +3158,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3154,7 +3166,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3162,7 +3174,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>289</v>
+        <v>170</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3170,7 +3182,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>182</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3178,7 +3190,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>192</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3186,15 +3198,15 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="238" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B238" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B238" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="11" t="n">
-        <v>343</v>
+      <c r="C238" s="12" t="n">
+        <v>5082</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3202,15 +3214,15 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="240" ht="22" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="15" t="s">
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3218,7 +3230,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3226,7 +3238,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3234,7 +3246,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3242,7 +3254,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>222</v>
+        <v>62</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3250,15 +3262,15 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="246" ht="22" customHeight="true" outlineLevel="3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="15" t="s">
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="247" ht="22" customHeight="true" outlineLevel="3">
@@ -3266,47 +3278,47 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="248" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="249" ht="22" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="250" ht="22" customHeight="true" outlineLevel="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="251" ht="22" customHeight="true" outlineLevel="3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="252" ht="22" customHeight="true" outlineLevel="3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>117</v>
+        <v>367</v>
       </c>
     </row>
     <row r="253" ht="22" customHeight="true" outlineLevel="3">
@@ -3314,63 +3326,63 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="254" ht="11" customHeight="true" outlineLevel="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="254" ht="22" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="true" outlineLevel="3">
       <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="256" ht="11" customHeight="true" outlineLevel="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="256" ht="22" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="257" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="258" ht="11" customHeight="true" outlineLevel="3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="258" ht="22" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="259" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259" ht="22" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="260" ht="11" customHeight="true" outlineLevel="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="260" ht="22" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3378,7 +3390,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>615</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3386,7 +3398,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>705</v>
+        <v>79</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3394,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>254</v>
+        <v>225</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3402,23 +3414,23 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="265" ht="22" customHeight="true" outlineLevel="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="266" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B266" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="12" t="n">
-        <v>9085</v>
+      <c r="C266" s="11" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3426,7 +3438,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>221</v>
+        <v>882</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3434,39 +3446,39 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="269" ht="22" customHeight="true" outlineLevel="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>9</v>
+        <v>217</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="16" t="n">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C270" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="272" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B272" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B272" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>94</v>
+      <c r="C272" s="12" t="n">
+        <v>6204</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3474,7 +3486,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>544</v>
+        <v>155</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3482,23 +3494,23 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="275" ht="11" customHeight="true" outlineLevel="3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="275" ht="22" customHeight="true" outlineLevel="3">
       <c r="B275" s="15" t="s">
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="11" t="n">
-        <v>248</v>
+      <c r="C276" s="16" t="n">
+        <v>1001</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3506,7 +3518,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>400</v>
+        <v>277</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3514,7 +3526,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3522,7 +3534,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>150</v>
+        <v>464</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3530,7 +3542,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>328</v>
+        <v>55</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3538,7 +3550,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>257</v>
+        <v>93</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3546,7 +3558,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>334</v>
+        <v>218</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3554,7 +3566,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>329</v>
+        <v>370</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3562,7 +3574,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>223</v>
+        <v>128</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3570,7 +3582,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>550</v>
+        <v>265</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3578,23 +3590,23 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="287" ht="22" customHeight="true" outlineLevel="3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>148</v>
+        <v>309</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3602,7 +3614,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3610,23 +3622,23 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="291" ht="22" customHeight="true" outlineLevel="3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
     </row>
     <row r="293" ht="22" customHeight="true" outlineLevel="3">
@@ -3634,7 +3646,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>66</v>
+        <v>124</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3642,39 +3654,39 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="296" ht="11" customHeight="true" outlineLevel="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="16" t="n">
-        <v>1358</v>
+      <c r="C298" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3682,15 +3694,15 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3698,15 +3710,15 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="302" ht="11" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="302" ht="22" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3714,15 +3726,15 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B304" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="17" t="n">
-        <v>147</v>
+      <c r="C304" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3730,7 +3742,7 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>83</v>
+        <v>133</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -3738,15 +3750,15 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B307" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="12" t="n">
-        <v>8353</v>
+      <c r="C307" s="11" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3754,7 +3766,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3762,47 +3774,47 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B310" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B310" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C310" s="17" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="true" outlineLevel="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B313" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B313" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="314" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C313" s="12" t="n">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -3810,15 +3822,15 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="316" ht="11" customHeight="true" outlineLevel="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="316" ht="22" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>149</v>
+        <v>75</v>
       </c>
     </row>
     <row r="317" ht="22" customHeight="true" outlineLevel="3">
@@ -3826,7 +3838,7 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318" ht="22" customHeight="true" outlineLevel="3">
@@ -3834,15 +3846,15 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="319" ht="22" customHeight="true" outlineLevel="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>373</v>
+        <v>77</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="true" outlineLevel="3">
@@ -3850,23 +3862,23 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>170</v>
+        <v>69</v>
       </c>
     </row>
     <row r="323" ht="22" customHeight="true" outlineLevel="3">
@@ -3874,7 +3886,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>179</v>
+        <v>25</v>
       </c>
     </row>
     <row r="324" ht="22" customHeight="true" outlineLevel="3">
@@ -3882,7 +3894,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="true" outlineLevel="3">
@@ -3890,7 +3902,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>29</v>
+        <v>113</v>
       </c>
     </row>
     <row r="326" ht="22" customHeight="true" outlineLevel="3">
@@ -3898,7 +3910,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>527</v>
+        <v>30</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="true" outlineLevel="3">
@@ -3906,7 +3918,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
     </row>
     <row r="328" ht="22" customHeight="true" outlineLevel="3">
@@ -3914,23 +3926,23 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="329" ht="11" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>281</v>
+        <v>142</v>
       </c>
     </row>
     <row r="331" ht="22" customHeight="true" outlineLevel="3">
@@ -3938,7 +3950,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="332" ht="22" customHeight="true" outlineLevel="3">
@@ -3946,7 +3958,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>13</v>
+        <v>431</v>
       </c>
     </row>
     <row r="333" ht="22" customHeight="true" outlineLevel="3">
@@ -3954,7 +3966,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>163</v>
+        <v>13</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="true" outlineLevel="3">
@@ -3962,7 +3974,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -3970,31 +3982,31 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="336" ht="22" customHeight="true" outlineLevel="3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>198</v>
+        <v>13</v>
       </c>
     </row>
     <row r="339" ht="22" customHeight="true" outlineLevel="3">
@@ -4002,15 +4014,15 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="340" ht="11" customHeight="true" outlineLevel="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="340" ht="22" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>307</v>
+        <v>9</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4018,15 +4030,15 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>268</v>
+        <v>106</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4034,7 +4046,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4042,15 +4054,15 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>397</v>
+        <v>192</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4058,7 +4070,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>239</v>
+        <v>307</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4066,7 +4078,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>226</v>
+        <v>33</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4074,7 +4086,7 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4082,7 +4094,7 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>789</v>
+        <v>339</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
@@ -4090,7 +4102,39 @@
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>645</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B351" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="C351" s="11" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C352" s="11" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B353" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C353" s="11" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B354" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C354" s="11" t="n">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.02.2026 7:55:12</t>
+    <t>Период: на 23.02.2026 11:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -179,6 +179,9 @@
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
@@ -245,45 +248,51 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 41г /180шт</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
@@ -359,6 +368,9 @@
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -446,6 +458,9 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -467,6 +482,9 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -527,21 +545,30 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -599,6 +626,9 @@
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>CoffeeLike КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
@@ -701,9 +731,15 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
+    <t>Chocolateria ВКФ 256г /8шт</t>
+  </si>
+  <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
@@ -818,21 +854,24 @@
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
     <t>До кави пряжене молоко ВКФ 185г /28шт /</t>
   </si>
   <si>
-    <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
@@ -866,6 +905,9 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White 1кг/5</t>
+  </si>
+  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -929,9 +971,6 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -968,33 +1007,48 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1016,6 +1070,9 @@
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -1049,19 +1106,31 @@
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
@@ -1325,7 +1394,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C354"/>
+  <dimension ref="C377"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1390,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1398,7 +1467,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>132811</v>
+        <v>299812</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1406,7 +1475,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>28389</v>
+        <v>59493</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1414,15 +1483,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>6300</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>1060</v>
+      <c r="C15" s="11" t="n">
+        <v>740</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1430,7 +1499,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>319</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1438,7 +1507,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>1367</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1454,7 +1523,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>616</v>
+        <v>977</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1462,7 +1531,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>709</v>
+        <v>805</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1478,7 +1547,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>83</v>
+        <v>797</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1486,7 +1555,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>307</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1494,15 +1563,15 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>694</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16" t="n">
-        <v>1093</v>
+      <c r="C25" s="11" t="n">
+        <v>819</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="2">
@@ -1510,7 +1579,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>9846</v>
+        <v>19205</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1518,15 +1587,15 @@
         <v>26</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>2776</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>541</v>
+      <c r="C28" s="16" t="n">
+        <v>5303</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1534,7 +1603,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>383</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1549,8 +1618,8 @@
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>41</v>
+      <c r="C31" s="16" t="n">
+        <v>3114</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1574,15 +1643,15 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>3308</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>212</v>
+      <c r="C35" s="16" t="n">
+        <v>1232</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1598,7 +1667,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>265</v>
+        <v>567</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1622,7 +1691,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>291</v>
+        <v>607</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1638,7 +1707,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>364</v>
+        <v>865</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="2">
@@ -1646,23 +1715,23 @@
         <v>42</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>4302</v>
+        <v>15697</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>56</v>
+      <c r="C44" s="16" t="n">
+        <v>1528</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>61</v>
+      <c r="C45" s="16" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1670,15 +1739,15 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>385</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>67</v>
+      <c r="C47" s="16" t="n">
+        <v>1199</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1686,7 +1755,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>360</v>
+        <v>956</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1694,7 +1763,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1702,7 +1771,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>326</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1710,7 +1779,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>847</v>
+        <v>832</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1718,7 +1787,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>102</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1726,23 +1795,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>624</v>
+        <v>584</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>46</v>
+      <c r="C54" s="16" t="n">
+        <v>1118</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>144</v>
+      <c r="C55" s="16" t="n">
+        <v>1120</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1750,7 +1819,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>32</v>
+        <v>953</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1758,23 +1827,23 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="58" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B58" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="12" t="n">
-        <v>7941</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B59" s="15" t="s">
+      <c r="C58" s="16" t="n">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B59" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>138</v>
+      <c r="C59" s="12" t="n">
+        <v>17972</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1782,7 +1851,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>948</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1790,7 +1859,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>322</v>
+        <v>877</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -1798,7 +1867,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>623</v>
+        <v>872</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1806,39 +1875,39 @@
         <v>62</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>1050</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="11" t="n">
-        <v>257</v>
+      <c r="C64" s="16" t="n">
+        <v>2001</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>2018</v>
+      <c r="C65" s="11" t="n">
+        <v>782</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>991</v>
+      <c r="C66" s="16" t="n">
+        <v>1782</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>10</v>
+      <c r="C67" s="16" t="n">
+        <v>1783</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -1846,7 +1915,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>126</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -1854,23 +1923,23 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>697</v>
+        <v>514</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>607</v>
+      <c r="C70" s="16" t="n">
+        <v>1402</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>57</v>
+      <c r="C71" s="16" t="n">
+        <v>5971</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -1878,31 +1947,31 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B73" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="12" t="n">
-        <v>104422</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B74" s="14" t="s">
+      <c r="C73" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B74" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>24247</v>
-      </c>
-    </row>
-    <row r="75" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B75" s="15" t="s">
+        <v>240319</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B75" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>120</v>
+      <c r="C75" s="12" t="n">
+        <v>89465</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="true" outlineLevel="3">
@@ -1910,7 +1979,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>1720</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="true" outlineLevel="3">
@@ -1918,63 +1987,63 @@
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>2798</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="3">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="true" outlineLevel="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>5960</v>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="true" outlineLevel="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C81" s="16" t="n">
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>74</v>
+      <c r="C83" s="16" t="n">
+        <v>4430</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>180</v>
+      <c r="C84" s="16" t="n">
+        <v>10800</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="true" outlineLevel="3">
@@ -1982,63 +2051,63 @@
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>2930</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>180</v>
+      <c r="C86" s="16" t="n">
+        <v>10800</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>5365</v>
+      <c r="C87" s="11" t="n">
+        <v>614</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B89" s="14" t="s">
+      <c r="C88" s="16" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="17" t="n">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C89" s="16" t="n">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C90" s="16" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B92" s="15" t="s">
+      <c r="C91" s="16" t="n">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B92" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>14</v>
+      <c r="C92" s="12" t="n">
+        <v>5770</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2046,7 +2115,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>115</v>
+        <v>764</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2054,7 +2123,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>94</v>
+        <v>525</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2062,15 +2131,15 @@
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>127</v>
+        <v>572</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>79</v>
+      <c r="C96" s="16" t="n">
+        <v>1474</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
@@ -2078,23 +2147,23 @@
         <v>96</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>127</v>
+        <v>379</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B99" s="14" t="s">
+      <c r="C98" s="16" t="n">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="12" t="n">
-        <v>41053</v>
+      <c r="C99" s="11" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2102,7 +2171,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>16</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
@@ -2110,23 +2179,23 @@
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B102" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B102" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>123</v>
+      <c r="C102" s="12" t="n">
+        <v>55216</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>4</v>
+      <c r="C103" s="16" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2134,7 +2203,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
@@ -2142,15 +2211,15 @@
         <v>104</v>
       </c>
       <c r="C105" s="16" t="n">
-        <v>13300</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="16" t="n">
-        <v>19643</v>
+      <c r="C106" s="11" t="n">
+        <v>574</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2158,7 +2227,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>25</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2166,31 +2235,31 @@
         <v>107</v>
       </c>
       <c r="C108" s="16" t="n">
-        <v>4550</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>38</v>
+      <c r="C109" s="16" t="n">
+        <v>16168</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>11</v>
+      <c r="C110" s="16" t="n">
+        <v>2275</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>36</v>
+      <c r="C111" s="16" t="n">
+        <v>9750</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2198,7 +2267,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2206,7 +2275,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>74</v>
+        <v>493</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2214,7 +2283,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>102</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2222,7 +2291,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>50</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2230,15 +2299,15 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" ht="22" customHeight="true" outlineLevel="3">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>48</v>
+        <v>348</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2246,7 +2315,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>207</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2254,7 +2323,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>288</v>
+        <v>428</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2262,15 +2331,15 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="true" outlineLevel="3">
       <c r="B121" s="15" t="s">
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>270</v>
+        <v>466</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2278,7 +2347,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>660</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2286,7 +2355,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>193</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2294,7 +2363,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>193</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2302,7 +2371,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>33</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2310,7 +2379,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>147</v>
+        <v>556</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2318,7 +2387,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2326,7 +2395,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>433</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2334,15 +2403,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B130" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="12" t="n">
-        <v>14878</v>
+      <c r="C130" s="11" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2350,7 +2419,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>193</v>
+        <v>119</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2358,7 +2427,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>81</v>
+        <v>340</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2366,15 +2435,15 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B134" s="15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B134" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>74</v>
+      <c r="C134" s="12" t="n">
+        <v>21033</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2382,7 +2451,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>90</v>
+        <v>182</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2390,7 +2459,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>104</v>
+        <v>54</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2398,7 +2467,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2406,7 +2475,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2414,7 +2483,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2422,7 +2491,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2430,7 +2499,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>799</v>
+        <v>76</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2438,7 +2507,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>212</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2446,7 +2515,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2454,7 +2523,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2462,7 +2531,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>60</v>
+        <v>639</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2470,7 +2539,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>135</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2478,7 +2547,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2486,7 +2555,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>8</v>
+        <v>757</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2494,7 +2563,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>80</v>
+        <v>715</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2502,7 +2571,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>428</v>
+        <v>219</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2510,7 +2579,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2518,7 +2587,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>192</v>
+        <v>848</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2526,7 +2595,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>355</v>
+        <v>300</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2534,7 +2603,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>28</v>
+        <v>994</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2542,31 +2611,31 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="true" outlineLevel="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="15" t="s">
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="157" ht="22" customHeight="true" outlineLevel="3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="158" ht="22" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>89</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2574,15 +2643,15 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>74</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="16" t="n">
-        <v>1626</v>
+      <c r="C160" s="11" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2590,7 +2659,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>280</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162" ht="22" customHeight="true" outlineLevel="3">
@@ -2598,7 +2667,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>110</v>
+        <v>871</v>
       </c>
     </row>
     <row r="163" ht="22" customHeight="true" outlineLevel="3">
@@ -2606,31 +2675,31 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="164" ht="11" customHeight="true" outlineLevel="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>51</v>
+        <v>510</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="16" t="n">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="166" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C165" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="11" t="n">
-        <v>315</v>
+      <c r="C166" s="16" t="n">
+        <v>1258</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2638,23 +2707,23 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="168" ht="11" customHeight="true" outlineLevel="3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="169" ht="11" customHeight="true" outlineLevel="3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2662,23 +2731,23 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>211</v>
+        <v>51</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="172" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C171" s="16" t="n">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="true" outlineLevel="3">
       <c r="B172" s="15" t="s">
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>71</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2686,7 +2755,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>38</v>
+        <v>134</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2694,7 +2763,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>186</v>
+        <v>228</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2702,7 +2771,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2710,7 +2779,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>27</v>
+        <v>161</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2718,7 +2787,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>174</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2726,7 +2795,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2734,15 +2803,15 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>251</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="16" t="n">
-        <v>3424</v>
+      <c r="C180" s="11" t="n">
+        <v>387</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2750,7 +2819,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>216</v>
+        <v>167</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2758,7 +2827,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>174</v>
+        <v>280</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2766,7 +2835,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2774,7 +2843,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>49</v>
+        <v>191</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2782,7 +2851,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>149</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2790,7 +2859,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>287</v>
+        <v>174</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2798,7 +2867,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2806,23 +2875,23 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>530</v>
+        <v>241</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="190" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B190" s="14" t="s">
+      <c r="C189" s="16" t="n">
+        <v>3296</v>
+      </c>
+    </row>
+    <row r="190" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="12" t="n">
-        <v>6449</v>
+      <c r="C190" s="11" t="n">
+        <v>201</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2830,7 +2899,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2838,7 +2907,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2846,7 +2915,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>570</v>
+        <v>485</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2854,7 +2923,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>32</v>
+        <v>141</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2862,7 +2931,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>101</v>
+        <v>282</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2870,7 +2939,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2878,7 +2947,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>124</v>
+        <v>529</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2886,15 +2955,15 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="199" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B199" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B199" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="11" t="n">
-        <v>105</v>
+      <c r="C199" s="12" t="n">
+        <v>13463</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -2902,7 +2971,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>50</v>
+        <v>164</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2910,7 +2979,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>125</v>
+        <v>43</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2918,7 +2987,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>203</v>
+        <v>371</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2926,7 +2995,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>123</v>
+        <v>630</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -2934,7 +3003,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>131</v>
+        <v>600</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -2942,7 +3011,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>277</v>
+        <v>777</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2950,7 +3019,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2958,7 +3027,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>185</v>
+        <v>116</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -2966,7 +3035,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>335</v>
+        <v>50</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -2974,7 +3043,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -2982,7 +3051,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -2990,7 +3059,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>501</v>
+        <v>433</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -2998,7 +3067,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>31</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3006,7 +3075,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>357</v>
+        <v>636</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3014,7 +3083,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3022,7 +3091,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>427</v>
+        <v>219</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3030,7 +3099,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>724</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3038,7 +3107,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>49</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3046,7 +3115,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>624</v>
+        <v>268</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3054,7 +3123,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3062,7 +3131,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>494</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3070,7 +3139,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>117</v>
+        <v>336</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3078,7 +3147,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>35</v>
+        <v>685</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3086,15 +3155,15 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="224" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B224" s="14" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="224" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B224" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="12" t="n">
-        <v>1189</v>
+      <c r="C224" s="11" t="n">
+        <v>725</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3102,7 +3171,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>280</v>
+        <v>862</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3110,7 +3179,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>28</v>
+        <v>560</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3118,7 +3187,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3126,15 +3195,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>88</v>
+        <v>436</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>34</v>
+      <c r="C229" s="16" t="n">
+        <v>1010</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3142,7 +3211,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>67</v>
+        <v>857</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3150,15 +3219,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>334</v>
+        <v>622</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>13</v>
+      <c r="C232" s="16" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3166,15 +3235,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B234" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B234" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>170</v>
+      <c r="C234" s="12" t="n">
+        <v>1674</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3182,7 +3251,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>6</v>
+        <v>248</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3190,7 +3259,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3198,15 +3267,15 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="238" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B238" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="12" t="n">
-        <v>5082</v>
+      <c r="C238" s="11" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3214,7 +3283,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3222,7 +3291,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3230,7 +3299,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3238,7 +3307,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>180</v>
+        <v>86</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3246,7 +3315,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>191</v>
+        <v>322</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3254,7 +3323,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3262,7 +3331,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>337</v>
+        <v>208</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3270,15 +3339,15 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="247" ht="22" customHeight="true" outlineLevel="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3286,7 +3355,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3294,79 +3363,79 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="250" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B250" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B250" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>191</v>
+      <c r="C250" s="12" t="n">
+        <v>24121</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>210</v>
+      <c r="C251" s="16" t="n">
+        <v>1094</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C252" s="16" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="254" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C253" s="16" t="n">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="255" ht="22" customHeight="true" outlineLevel="3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="256" ht="22" customHeight="true" outlineLevel="3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="257" ht="22" customHeight="true" outlineLevel="3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="258" ht="22" customHeight="true" outlineLevel="3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>18</v>
+        <v>514</v>
       </c>
     </row>
     <row r="259" ht="22" customHeight="true" outlineLevel="3">
@@ -3374,15 +3443,15 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="260" ht="22" customHeight="true" outlineLevel="3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>14</v>
+        <v>427</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3390,7 +3459,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>26</v>
+        <v>476</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3398,7 +3467,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>79</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3406,7 +3475,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>225</v>
+        <v>168</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3414,55 +3483,55 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="266" ht="11" customHeight="true" outlineLevel="3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="267" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="268" ht="11" customHeight="true" outlineLevel="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="268" ht="22" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="269" ht="11" customHeight="true" outlineLevel="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="270" ht="11" customHeight="true" outlineLevel="3">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>214</v>
+        <v>43</v>
       </c>
     </row>
     <row r="271" ht="22" customHeight="true" outlineLevel="3">
@@ -3470,15 +3539,15 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="272" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B272" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="272" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="12" t="n">
-        <v>6204</v>
+      <c r="C272" s="11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3486,7 +3555,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>155</v>
+        <v>98</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3494,31 +3563,31 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="275" ht="22" customHeight="true" outlineLevel="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="15" t="s">
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>9</v>
+        <v>208</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="16" t="n">
-        <v>1001</v>
+      <c r="C276" s="11" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="11" t="n">
-        <v>277</v>
+      <c r="C277" s="16" t="n">
+        <v>1993</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3526,7 +3595,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>9</v>
+        <v>798</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3534,23 +3603,23 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="C280" s="11" t="n">
-        <v>55</v>
+      <c r="C280" s="16" t="n">
+        <v>1019</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>93</v>
+      <c r="C281" s="16" t="n">
+        <v>1731</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3558,31 +3627,31 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>218</v>
+        <v>815</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>370</v>
+      <c r="C283" s="16" t="n">
+        <v>4832</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="11" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="285" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B285" s="15" t="s">
+      <c r="C284" s="16" t="n">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B285" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="11" t="n">
-        <v>265</v>
+      <c r="C285" s="12" t="n">
+        <v>10987</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3590,7 +3659,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>133</v>
+        <v>521</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3598,15 +3667,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>309</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3614,7 +3683,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>63</v>
+        <v>872</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3622,7 +3691,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>441</v>
+        <v>245</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3630,23 +3699,23 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="292" ht="22" customHeight="true" outlineLevel="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="293" ht="22" customHeight="true" outlineLevel="3">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>124</v>
+        <v>222</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3654,7 +3723,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -3662,15 +3731,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3678,15 +3747,15 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3694,15 +3763,15 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>56</v>
+        <v>234</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3710,15 +3779,15 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>52</v>
+        <v>301</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3726,7 +3795,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>173</v>
+        <v>288</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -3734,7 +3803,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>60</v>
+        <v>353</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3742,23 +3811,23 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="306" ht="11" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="306" ht="22" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="307" ht="22" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>276</v>
+        <v>113</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3766,7 +3835,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3774,15 +3843,15 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="310" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B310" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="17" t="n">
-        <v>147</v>
+      <c r="C310" s="11" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -3790,31 +3859,31 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B313" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="12" t="n">
-        <v>4316</v>
-      </c>
-    </row>
-    <row r="314" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C313" s="11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>16</v>
+        <v>182</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -3822,7 +3891,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>145</v>
+        <v>47</v>
       </c>
     </row>
     <row r="316" ht="22" customHeight="true" outlineLevel="3">
@@ -3830,23 +3899,23 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="317" ht="22" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C317" s="16" t="n">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>98</v>
+        <v>609</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -3854,15 +3923,15 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>2</v>
+        <v>311</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
@@ -3878,55 +3947,55 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="323" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B323" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B323" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C323" s="17" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="325" ht="22" customHeight="true" outlineLevel="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B326" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B326" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C326" s="12" t="n">
+        <v>18452</v>
+      </c>
+    </row>
+    <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="328" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="329" ht="22" customHeight="true" outlineLevel="3">
@@ -3934,7 +4003,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>15</v>
+        <v>670</v>
       </c>
     </row>
     <row r="330" ht="22" customHeight="true" outlineLevel="3">
@@ -3942,23 +4011,23 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="331" ht="22" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="332" ht="22" customHeight="true" outlineLevel="3">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>431</v>
+        <v>132</v>
       </c>
     </row>
     <row r="333" ht="22" customHeight="true" outlineLevel="3">
@@ -3966,7 +4035,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>13</v>
+        <v>934</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="true" outlineLevel="3">
@@ -3974,7 +4043,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -3982,7 +4051,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>177</v>
+        <v>156</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -3990,23 +4059,23 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="338" ht="22" customHeight="true" outlineLevel="3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="339" ht="22" customHeight="true" outlineLevel="3">
@@ -4014,7 +4083,7 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>43</v>
+        <v>576</v>
       </c>
     </row>
     <row r="340" ht="22" customHeight="true" outlineLevel="3">
@@ -4022,15 +4091,15 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="342" ht="22" customHeight="true" outlineLevel="3">
@@ -4038,23 +4107,23 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="345" ht="22" customHeight="true" outlineLevel="3">
@@ -4062,71 +4131,71 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="347" ht="22" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>158</v>
+        <v>6</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4134,7 +4203,191 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>392</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B355" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C355" s="11" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="356" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B356" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C356" s="11" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="357" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B357" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="C357" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B358" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="C358" s="11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B359" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="C359" s="11" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C360" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B361" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C361" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B362" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C362" s="11" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="363" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B363" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="C363" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B364" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C364" s="11" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B365" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C365" s="11" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B366" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C366" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B367" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C367" s="11" t="n">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B368" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C368" s="11" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B369" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="C369" s="11" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B370" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C370" s="11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B371" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C371" s="16" t="n">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B372" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C372" s="16" t="n">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B373" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C373" s="16" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B374" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C374" s="11" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B375" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C375" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B376" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C376" s="11" t="n">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B377" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C377" s="11" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="420">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.02.2026 11:15:12</t>
+    <t>Период: на 19.03.2026 20:05:29</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -83,18 +83,15 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт</t>
-  </si>
-  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Какао-порошок 22% УБ 60г /26шт</t>
-  </si>
-  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
+    <t>Какао-порошок УБ 80г /48шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -104,7 +101,10 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
-    <t>Ванільний цукор УБ 35г /36шт</t>
+    <t>Ванільний цукор УБ 10г /58шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Глазур декоративна біла УБ 75г /40шт</t>
   </si>
   <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
@@ -125,6 +125,15 @@
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №1 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №2 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №3 УБ 7г /55шт</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
@@ -152,10 +161,13 @@
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт</t>
+    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
@@ -170,6 +182,9 @@
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
@@ -179,6 +194,9 @@
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -188,6 +206,9 @@
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
+    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Часник гранульований сушений УБ 15г /42шт</t>
   </si>
   <si>
@@ -230,10 +251,13 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
@@ -248,16 +272,13 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 41г /180шт</t>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 39г /180шт</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 39г /180шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
@@ -266,6 +287,9 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
@@ -278,7 +302,7 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
@@ -287,6 +311,12 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -317,9 +347,6 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -413,6 +440,9 @@
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers молоко ВКФ 216г /16шт</t>
+  </si>
+  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -428,9 +458,6 @@
     <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
-    <t>Bonny-Fruit цитрусовий мікс ВКФ 200г /18шт /</t>
-  </si>
-  <si>
     <t>Bonny-Fruit ягідний мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
@@ -458,6 +485,9 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -467,33 +497,60 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -503,9 +560,6 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -515,84 +569,123 @@
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
+    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
+    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -635,6 +728,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -728,15 +824,18 @@
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 256г /8шт</t>
   </si>
   <si>
@@ -758,9 +857,6 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -803,12 +899,6 @@
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies арахіс ККФ 150г /16шт</t>
-  </si>
-  <si>
-    <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
-  </si>
-  <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
@@ -818,9 +908,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 420г /7шт</t>
   </si>
   <si>
@@ -833,9 +920,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -851,9 +935,15 @@
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -863,12 +953,18 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
     <t>До кави пряжене молоко ВКФ 185г /28шт /</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
@@ -905,9 +1001,6 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White 1кг/5</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -971,18 +1064,24 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
+    <t>Сливки-Ленивки ВКФ 1кг АКЦІЯ</t>
+  </si>
+  <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1001,33 +1100,39 @@
     <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
@@ -1037,16 +1142,19 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
@@ -1055,28 +1163,40 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -1094,42 +1214,36 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
@@ -1149,6 +1263,21 @@
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 40г /24шт</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 60г /20шт</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1375,6 +1504,12 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1394,7 +1529,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C377"/>
+  <dimension ref="C420"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1459,7 +1594,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1467,7 +1602,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>299812</v>
+        <v>181087</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1475,7 +1610,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>59493</v>
+        <v>35859</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1483,7 +1618,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>6619</v>
+        <v>6678</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1491,23 +1626,23 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>459</v>
+      <c r="C16" s="16" t="n">
+        <v>1696</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
       <c r="B17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="16" t="n">
-        <v>1184</v>
+      <c r="C17" s="11" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1523,7 +1658,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>977</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1531,7 +1666,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>805</v>
+        <v>977</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1547,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>797</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1555,31 +1690,31 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>141</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="25" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B25" s="15" t="s">
+      <c r="C24" s="16" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="25" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B25" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B26" s="14" t="s">
+      <c r="C25" s="12" t="n">
+        <v>15273</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>19205</v>
+      <c r="C26" s="16" t="n">
+        <v>1090</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1587,15 +1722,15 @@
         <v>26</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>2389</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>5303</v>
+      <c r="C28" s="11" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1603,31 +1738,31 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>317</v>
+        <v>556</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="16" t="n">
-        <v>1100</v>
+      <c r="C30" s="11" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>3114</v>
+      <c r="C31" s="11" t="n">
+        <v>595</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>48</v>
+      <c r="C32" s="16" t="n">
+        <v>1048</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1643,15 +1778,15 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>3146</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="16" t="n">
-        <v>1232</v>
+      <c r="C35" s="11" t="n">
+        <v>815</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1659,23 +1794,23 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>22</v>
+        <v>990</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>567</v>
+      <c r="C37" s="16" t="n">
+        <v>1222</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>334</v>
+      <c r="C38" s="16" t="n">
+        <v>4784</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1683,7 +1818,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1691,7 +1826,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>607</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1699,7 +1834,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>124</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -1707,47 +1842,47 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B43" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="12" t="n">
-        <v>15697</v>
+      <c r="C43" s="11" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="n">
-        <v>1528</v>
+      <c r="C44" s="11" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="16" t="n">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="46" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B46" s="15" t="s">
+      <c r="C45" s="11" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B46" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>240</v>
+      <c r="C46" s="12" t="n">
+        <v>5840</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="16" t="n">
-        <v>1199</v>
+      <c r="C47" s="11" t="n">
+        <v>363</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1755,7 +1890,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>956</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1763,7 +1898,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>341</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1771,7 +1906,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>222</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1779,7 +1914,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>832</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1787,7 +1922,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>578</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1795,23 +1930,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>584</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="16" t="n">
-        <v>1118</v>
+      <c r="C54" s="11" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="16" t="n">
-        <v>1120</v>
+      <c r="C55" s="11" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1819,7 +1954,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>953</v>
+        <v>592</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1827,23 +1962,23 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>31</v>
+        <v>911</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>4975</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B59" s="14" t="s">
+      <c r="C58" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="12" t="n">
-        <v>17972</v>
+      <c r="C59" s="11" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1851,7 +1986,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>320</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1859,7 +1994,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>877</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -1867,47 +2002,47 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>872</v>
+        <v>458</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="16" t="n">
-        <v>1305</v>
+      <c r="C63" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>2001</v>
+      <c r="C64" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="66" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B66" s="15" t="s">
+      <c r="C65" s="16" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B66" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>1782</v>
+      <c r="C66" s="12" t="n">
+        <v>8068</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>1783</v>
+      <c r="C67" s="11" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -1915,7 +2050,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>10</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -1923,23 +2058,23 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>514</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>1402</v>
+      <c r="C70" s="11" t="n">
+        <v>406</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>5971</v>
+      <c r="C71" s="11" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -1947,7 +2082,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>286</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -1955,87 +2090,87 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="74" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B74" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="12" t="n">
-        <v>240319</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B75" s="14" t="s">
+      <c r="C74" s="11" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="12" t="n">
-        <v>89465</v>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C75" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="16" t="n">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C76" s="11" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="true" outlineLevel="3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="16" t="n">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C78" s="11" t="n">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>85</v>
+      <c r="C79" s="16" t="n">
+        <v>3342</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>1800</v>
+      <c r="C80" s="11" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>4848</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B82" s="15" t="s">
+      <c r="C81" s="11" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B82" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B83" s="15" t="s">
+      <c r="C82" s="12" t="n">
+        <v>145228</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B83" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="16" t="n">
-        <v>4430</v>
+      <c r="C83" s="12" t="n">
+        <v>42330</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="true" outlineLevel="3">
@@ -2043,7 +2178,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="16" t="n">
-        <v>10800</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="true" outlineLevel="3">
@@ -2051,47 +2186,47 @@
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>3350</v>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="true" outlineLevel="3">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="16" t="n">
-        <v>10800</v>
+      <c r="C86" s="11" t="n">
+        <v>964</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C87" s="16" t="n">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C88" s="11" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
       <c r="C89" s="16" t="n">
-        <v>4425</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>10800</v>
+      <c r="C90" s="11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="true" outlineLevel="3">
@@ -2099,87 +2234,87 @@
         <v>90</v>
       </c>
       <c r="C91" s="16" t="n">
-        <v>2893</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B92" s="14" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="12" t="n">
-        <v>5770</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C92" s="16" t="n">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="11" t="n">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C93" s="16" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="11" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C94" s="16" t="n">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="16" t="n">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="16" t="n">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+        <v>5029</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C98" s="11" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C99" s="16" t="n">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="16" t="n">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>128</v>
+      <c r="C101" s="16" t="n">
+        <v>1003</v>
       </c>
     </row>
     <row r="102" ht="11" customHeight="true" outlineLevel="2">
@@ -2187,15 +2322,15 @@
         <v>101</v>
       </c>
       <c r="C102" s="12" t="n">
-        <v>55216</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="16" t="n">
-        <v>1020</v>
+      <c r="C103" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2203,15 +2338,15 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>1127</v>
+      <c r="C105" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
@@ -2219,7 +2354,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>574</v>
+        <v>693</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2227,39 +2362,39 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>545</v>
+        <v>208</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="16" t="n">
-        <v>17900</v>
+      <c r="C108" s="11" t="n">
+        <v>182</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="16" t="n">
-        <v>16168</v>
+      <c r="C109" s="11" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="16" t="n">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B111" s="15" t="s">
+      <c r="C110" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B111" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="16" t="n">
-        <v>9750</v>
+      <c r="C111" s="12" t="n">
+        <v>29896</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2267,7 +2402,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2275,7 +2410,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>493</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2283,7 +2418,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>439</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2291,7 +2426,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2299,47 +2434,47 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>478</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>348</v>
+      <c r="C117" s="16" t="n">
+        <v>9975</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="11" t="n">
-        <v>101</v>
+      <c r="C118" s="16" t="n">
+        <v>11297</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>428</v>
+      <c r="C119" s="16" t="n">
+        <v>1700</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C120" s="16" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="3">
       <c r="B121" s="15" t="s">
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>466</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2347,7 +2482,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2355,7 +2490,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>397</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2363,7 +2498,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2371,7 +2506,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>351</v>
+        <v>150</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2379,7 +2514,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>556</v>
+        <v>63</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2387,7 +2522,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>138</v>
+        <v>82</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2395,7 +2530,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2403,15 +2538,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2419,7 +2554,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2427,7 +2562,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>340</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2435,15 +2570,15 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B134" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="12" t="n">
-        <v>21033</v>
+      <c r="C134" s="11" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2451,7 +2586,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>182</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2459,7 +2594,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2467,7 +2602,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>40</v>
+        <v>111</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2475,7 +2610,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2483,7 +2618,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2491,7 +2626,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2499,7 +2634,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>76</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2507,7 +2642,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>75</v>
+        <v>478</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2515,15 +2650,15 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="144" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B144" s="15" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="144" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B144" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="11" t="n">
-        <v>68</v>
+      <c r="C144" s="12" t="n">
+        <v>18018</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2531,7 +2666,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>639</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2539,7 +2674,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>177</v>
+        <v>77</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2547,7 +2682,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2555,7 +2690,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>757</v>
+        <v>68</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2563,7 +2698,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>715</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2571,7 +2706,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>219</v>
+        <v>58</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2579,7 +2714,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2587,7 +2722,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>848</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2595,7 +2730,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>300</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2603,7 +2738,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>994</v>
+        <v>476</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2611,7 +2746,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2619,7 +2754,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>339</v>
+        <v>255</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2627,7 +2762,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2635,7 +2770,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>349</v>
+        <v>64</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2643,7 +2778,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2651,7 +2786,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2659,31 +2794,31 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="162" ht="22" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="163" ht="22" customHeight="true" outlineLevel="3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="164" ht="22" customHeight="true" outlineLevel="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>510</v>
+        <v>183</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2691,15 +2826,15 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>74</v>
+        <v>239</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="16" t="n">
-        <v>1258</v>
+      <c r="C166" s="11" t="n">
+        <v>368</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2707,23 +2842,23 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="168" ht="22" customHeight="true" outlineLevel="3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="169" ht="22" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2731,23 +2866,23 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>51</v>
+        <v>502</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="16" t="n">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="172" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C171" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="15" t="s">
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>276</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2755,7 +2890,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2763,7 +2898,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>228</v>
+        <v>128</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2771,15 +2906,15 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="176" ht="11" customHeight="true" outlineLevel="3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="true" outlineLevel="3">
       <c r="B176" s="15" t="s">
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>161</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2787,7 +2922,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>220</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2795,7 +2930,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>171</v>
+        <v>333</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2803,7 +2938,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2811,23 +2946,23 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="181" ht="11" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="182" ht="11" customHeight="true" outlineLevel="3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>280</v>
+        <v>138</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2835,7 +2970,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2843,15 +2978,15 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="185" ht="11" customHeight="true" outlineLevel="3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>279</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2859,15 +2994,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="187" ht="11" customHeight="true" outlineLevel="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2875,15 +3010,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>241</v>
+        <v>112</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="16" t="n">
-        <v>3296</v>
+      <c r="C189" s="11" t="n">
+        <v>427</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2891,7 +3026,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>201</v>
+        <v>247</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2899,7 +3034,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2907,7 +3042,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>36</v>
+        <v>142</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2915,7 +3050,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>485</v>
+        <v>179</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2923,7 +3058,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>141</v>
+        <v>314</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2931,7 +3066,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>282</v>
+        <v>100</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2939,7 +3074,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2947,7 +3082,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>529</v>
+        <v>91</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2955,23 +3090,23 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="199" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B199" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B199" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="12" t="n">
-        <v>13463</v>
-      </c>
-    </row>
-    <row r="200" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C199" s="11" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2979,7 +3114,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2987,7 +3122,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>371</v>
+        <v>112</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2995,7 +3130,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>630</v>
+        <v>63</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3003,7 +3138,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>600</v>
+        <v>37</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3011,7 +3146,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>777</v>
+        <v>199</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3019,7 +3154,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3027,7 +3162,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>116</v>
+        <v>418</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3035,7 +3170,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>50</v>
+        <v>384</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3043,7 +3178,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3051,7 +3186,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3059,7 +3194,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>433</v>
+        <v>131</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3067,7 +3202,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>196</v>
+        <v>271</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3075,15 +3210,15 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>636</v>
+        <v>154</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="11" t="n">
-        <v>86</v>
+      <c r="C214" s="16" t="n">
+        <v>1008</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3091,15 +3226,15 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>219</v>
+        <v>296</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>40</v>
+      <c r="C216" s="16" t="n">
+        <v>2908</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3107,7 +3242,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>177</v>
+        <v>275</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3115,7 +3250,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>268</v>
+        <v>183</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3123,7 +3258,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>81</v>
+        <v>184</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3131,7 +3266,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>471</v>
+        <v>662</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3139,7 +3274,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>336</v>
+        <v>135</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3147,7 +3282,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>685</v>
+        <v>293</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3155,7 +3290,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>254</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3163,7 +3298,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>725</v>
+        <v>195</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3171,7 +3306,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>862</v>
+        <v>111</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3179,7 +3314,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>560</v>
+        <v>263</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3187,7 +3322,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3195,23 +3330,23 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>436</v>
+        <v>253</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="230" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B230" s="15" t="s">
+      <c r="C229" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B230" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="11" t="n">
-        <v>857</v>
+      <c r="C230" s="12" t="n">
+        <v>9859</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3219,15 +3354,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>622</v>
+        <v>226</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="16" t="n">
-        <v>1332</v>
+      <c r="C232" s="11" t="n">
+        <v>231</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3235,15 +3370,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B234" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="12" t="n">
-        <v>1674</v>
+      <c r="C234" s="11" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3251,7 +3386,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>248</v>
+        <v>136</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3259,7 +3394,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>17</v>
+        <v>763</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3267,7 +3402,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3275,7 +3410,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>148</v>
+        <v>74</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3283,7 +3418,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3291,7 +3426,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>8</v>
+        <v>220</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3299,7 +3434,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3307,7 +3442,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3315,7 +3450,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>322</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3323,7 +3458,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3331,7 +3466,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>208</v>
+        <v>441</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3339,7 +3474,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>159</v>
+        <v>24</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3347,7 +3482,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3355,7 +3490,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3363,39 +3498,39 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="250" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B250" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="12" t="n">
-        <v>24121</v>
+      <c r="C250" s="11" t="n">
+        <v>499</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="16" t="n">
-        <v>1094</v>
+      <c r="C251" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="16" t="n">
-        <v>1030</v>
+      <c r="C252" s="11" t="n">
+        <v>433</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="16" t="n">
-        <v>1443</v>
+      <c r="C253" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3403,7 +3538,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>284</v>
+        <v>631</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3411,7 +3546,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>291</v>
+        <v>119</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3419,7 +3554,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>462</v>
+        <v>212</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3427,7 +3562,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>311</v>
+        <v>414</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3435,15 +3570,15 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="259" ht="22" customHeight="true" outlineLevel="3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3451,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>427</v>
+        <v>295</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3459,7 +3594,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>476</v>
+        <v>624</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3467,7 +3602,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3475,79 +3610,79 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
       <c r="B264" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="11" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="265" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C264" s="16" t="n">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="266" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B266" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B266" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="267" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C266" s="17" t="n">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="268" ht="22" customHeight="true" outlineLevel="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="269" ht="22" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="270" ht="22" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="271" ht="22" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="272" ht="22" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3555,7 +3690,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3563,7 +3698,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3571,7 +3706,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>208</v>
+        <v>53</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3579,15 +3714,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>118</v>
+        <v>248</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="16" t="n">
-        <v>1993</v>
+      <c r="C277" s="11" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3595,7 +3730,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>798</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3603,55 +3738,55 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>449</v>
+        <v>69</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="C280" s="16" t="n">
-        <v>1019</v>
+      <c r="C280" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="16" t="n">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="282" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B282" s="15" t="s">
+      <c r="C281" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B282" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="11" t="n">
-        <v>815</v>
+      <c r="C282" s="12" t="n">
+        <v>9574</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="16" t="n">
-        <v>4832</v>
+      <c r="C283" s="11" t="n">
+        <v>474</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="16" t="n">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="285" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B285" s="14" t="s">
+      <c r="C284" s="11" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="12" t="n">
-        <v>10987</v>
+      <c r="C285" s="11" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3659,7 +3794,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>521</v>
+        <v>129</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3667,15 +3802,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>9</v>
+        <v>184</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3683,7 +3818,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>872</v>
+        <v>26</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3691,15 +3826,15 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="291" ht="11" customHeight="true" outlineLevel="3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>310</v>
+        <v>56</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3707,7 +3842,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>826</v>
+        <v>63</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3715,7 +3850,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>222</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3723,55 +3858,55 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="296" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="297" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>234</v>
+        <v>106</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3779,7 +3914,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>321</v>
+        <v>71</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3787,7 +3922,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>301</v>
+        <v>73</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3795,7 +3930,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>288</v>
+        <v>116</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -3803,7 +3938,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>353</v>
+        <v>87</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3811,7 +3946,7 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>31</v>
+        <v>660</v>
       </c>
     </row>
     <row r="306" ht="22" customHeight="true" outlineLevel="3">
@@ -3819,15 +3954,15 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="307" ht="22" customHeight="true" outlineLevel="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="11" t="n">
-        <v>113</v>
+      <c r="C307" s="16" t="n">
+        <v>1897</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3835,7 +3970,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3843,15 +3978,15 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="true" outlineLevel="3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -3859,15 +3994,15 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="true" outlineLevel="3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -3875,15 +4010,15 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="314" ht="22" customHeight="true" outlineLevel="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>182</v>
+      <c r="C314" s="16" t="n">
+        <v>2002</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -3891,23 +4026,23 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="true" outlineLevel="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B317" s="15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B317" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="16" t="n">
-        <v>2111</v>
+      <c r="C317" s="12" t="n">
+        <v>10345</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -3915,7 +4050,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>609</v>
+        <v>646</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -3923,15 +4058,15 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>311</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
@@ -3939,7 +4074,7 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>25</v>
+        <v>748</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -3947,15 +4082,15 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B323" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="17" t="n">
-        <v>139</v>
+      <c r="C323" s="11" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -3963,7 +4098,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>78</v>
+        <v>982</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -3971,15 +4106,15 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B326" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="12" t="n">
-        <v>18452</v>
+      <c r="C326" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -3987,7 +4122,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>16</v>
+        <v>190</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -3995,23 +4130,23 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="330" ht="22" customHeight="true" outlineLevel="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>79</v>
+        <v>189</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4019,7 +4154,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>692</v>
+        <v>597</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4027,23 +4162,23 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="333" ht="22" customHeight="true" outlineLevel="3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="334" ht="22" customHeight="true" outlineLevel="3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>34</v>
+        <v>141</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4051,7 +4186,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4059,39 +4194,39 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="340" ht="22" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>782</v>
+        <v>18</v>
       </c>
     </row>
     <row r="341" ht="22" customHeight="true" outlineLevel="3">
@@ -4099,15 +4234,15 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="342" ht="22" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>384</v>
+        <v>47</v>
       </c>
     </row>
     <row r="343" ht="22" customHeight="true" outlineLevel="3">
@@ -4115,15 +4250,15 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="344" ht="22" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>203</v>
+        <v>52</v>
       </c>
     </row>
     <row r="345" ht="22" customHeight="true" outlineLevel="3">
@@ -4131,15 +4266,15 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="346" ht="22" customHeight="true" outlineLevel="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>597</v>
+        <v>33</v>
       </c>
     </row>
     <row r="347" ht="22" customHeight="true" outlineLevel="3">
@@ -4147,55 +4282,55 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="348" ht="22" customHeight="true" outlineLevel="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="351" ht="22" customHeight="true" outlineLevel="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="352" ht="22" customHeight="true" outlineLevel="3">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="353" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C352" s="16" t="n">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4203,7 +4338,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>174</v>
+        <v>493</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4211,39 +4346,39 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="356" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B356" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B356" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="357" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C356" s="17" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="358" ht="22" customHeight="true" outlineLevel="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="359" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B359" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B359" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="11" t="n">
-        <v>254</v>
+      <c r="C359" s="12" t="n">
+        <v>23118</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4251,15 +4386,15 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>5</v>
+        <v>414</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4267,7 +4402,7 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>949</v>
+        <v>91</v>
       </c>
     </row>
     <row r="363" ht="22" customHeight="true" outlineLevel="3">
@@ -4275,23 +4410,23 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="364" ht="33" customHeight="true" outlineLevel="3">
       <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>290</v>
+        <v>159</v>
       </c>
     </row>
     <row r="366" ht="22" customHeight="true" outlineLevel="3">
@@ -4299,7 +4434,7 @@
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>4</v>
+        <v>472</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4307,7 +4442,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>964</v>
+        <v>606</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4315,15 +4450,15 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="369" ht="22" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>884</v>
+        <v>49</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
@@ -4331,34 +4466,34 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>120</v>
+        <v>650</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C371" s="16" t="n">
-        <v>1059</v>
+      <c r="C371" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="C372" s="16" t="n">
-        <v>1656</v>
+      <c r="C372" s="11" t="n">
+        <v>208</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="16" t="n">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C373" s="11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
@@ -4366,28 +4501,372 @@
         <v>167</v>
       </c>
     </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+    <row r="375" ht="22" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="11" t="n">
-        <v>600</v>
+      <c r="C377" s="16" t="n">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B378" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C378" s="11" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B379" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C379" s="16" t="n">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B380" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C380" s="11" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B381" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C381" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B382" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C382" s="16" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="383" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B383" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C383" s="11" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="384" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B384" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C384" s="11" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="385" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B385" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C385" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B386" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C386" s="16" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B387" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C387" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B388" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C388" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B389" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C389" s="11" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B390" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C390" s="11" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="391" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B391" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C391" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B392" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="16" t="n">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B393" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C393" s="11" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B394" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C394" s="11" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B395" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="11" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="396" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B396" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C396" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B397" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C397" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B398" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C398" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="399" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B399" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="C399" s="11" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B400" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C400" s="11" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C401" s="11" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B402" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C402" s="11" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B403" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C403" s="11" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C404" s="11" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="11" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B406" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C406" s="11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B407" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C407" s="11" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="11" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="11" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="412" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="11" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="413" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="11" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B416" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="12" t="n">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B417" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="11" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B418" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="419" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B419" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="11" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B420" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceZP.xlsx
+++ b/client/public/Sorce/balanceZP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 19.03.2026 20:05:29</t>
+    <t>Период: на 05.04.2026 19:35:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -83,9 +83,15 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
@@ -98,24 +104,18 @@
     <t>Ванілін УБ 2г /98шт</t>
   </si>
   <si>
-    <t>Ванільний цукор УБ 10г /58шт</t>
-  </si>
-  <si>
-    <t>Ванільний цукор УБ 10г /58шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Глазур декоративна біла УБ 75г /40шт</t>
   </si>
   <si>
+    <t>Глазур декоративна біла УБ 75г /40шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
@@ -128,12 +128,21 @@
     <t>Посипка декоративна №1 УБ 7г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №1 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Посипка декоративна №2 УБ 7г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №2 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Посипка декоративна №3 УБ 7г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №3 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
@@ -167,18 +176,24 @@
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
+    <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
@@ -200,6 +215,9 @@
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
@@ -254,9 +272,6 @@
     <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -272,6 +287,9 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -284,7 +302,7 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
@@ -293,12 +311,18 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -311,12 +335,12 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -347,6 +371,9 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -356,9 +383,6 @@
     <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
-  </si>
-  <si>
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -383,21 +407,12 @@
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -413,36 +428,45 @@
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers горіх ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао-молоко ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ВКФ 216г /16шт</t>
+    <t>Wafers кокос та мигдаль ВКФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт</t>
+    <t>Wafers лимон ККФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -458,6 +482,9 @@
     <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
+    <t>Bonny-Fruit цитрусовий мікс ВКФ 200г /18шт /</t>
+  </si>
+  <si>
     <t>Bonny-Fruit ягідний мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
@@ -479,6 +506,9 @@
     <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -518,9 +548,6 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -533,21 +560,12 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
@@ -617,7 +635,7 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
@@ -626,9 +644,15 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Rabbits ВКФ 165г /14шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -644,24 +668,21 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -677,9 +698,6 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -740,9 +758,6 @@
     <t>Lollipops GUM Фруктовий мікс РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -770,9 +785,6 @@
     <t>Roshen Yogurtini РЦ 1кг /8шт</t>
   </si>
   <si>
-    <t>Toffelini з какао-начинкою ВКФ 1кг /6пак</t>
-  </si>
-  <si>
     <t>Yummi's РЦ 1кг /7пак</t>
   </si>
   <si>
@@ -812,6 +824,9 @@
     <t>Шалена бджілка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Шалена бджілка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
     <t>Шипучка РЦ 1кг /7пак</t>
   </si>
   <si>
@@ -836,6 +851,9 @@
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Chocolateria ВКФ 194г /8шт NEW</t>
+  </si>
+  <si>
     <t>Chocolateria ВКФ 256г /8шт</t>
   </si>
   <si>
@@ -899,6 +917,12 @@
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
+    <t>Lovita Classic Cookies арахіс ККФ 150г /16шт</t>
+  </si>
+  <si>
+    <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
+  </si>
+  <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
@@ -914,12 +938,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -947,9 +971,6 @@
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
-  </si>
-  <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -980,6 +1001,9 @@
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
   </si>
   <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
@@ -995,16 +1019,19 @@
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
-  </si>
-  <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
@@ -1034,12 +1061,6 @@
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
-    <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
-  </si>
-  <si>
-    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
-  </si>
-  <si>
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1082,6 +1103,9 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1097,9 +1121,6 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1127,9 +1148,6 @@
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
@@ -1229,24 +1247,48 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
@@ -1268,10 +1310,10 @@
     <t>ФІГУРКИ</t>
   </si>
   <si>
-    <t>Кролик Roshen весняний ВКФ 25г /35шт</t>
-  </si>
-  <si>
     <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Кролик Roshen весняний ВКФ 40г /24шт</t>
@@ -1529,7 +1571,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C420"/>
+  <dimension ref="C434"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1594,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>129</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1602,7 +1644,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>181087</v>
+        <v>156794</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1610,7 +1652,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>35859</v>
+        <v>44418</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1618,7 +1660,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>6678</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1626,15 +1668,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>1696</v>
+      <c r="C16" s="11" t="n">
+        <v>308</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1642,7 +1684,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>320</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1650,7 +1692,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>32</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1658,7 +1700,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>298</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1666,7 +1708,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>977</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1682,7 +1724,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>340</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1690,23 +1732,23 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>275</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="16" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="25" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B25" s="14" t="s">
+      <c r="C24" s="11" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="12" t="n">
-        <v>15273</v>
+      <c r="C25" s="11" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1714,15 +1756,15 @@
         <v>25</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B27" s="15" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B27" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="16" t="n">
-        <v>1188</v>
+      <c r="C27" s="12" t="n">
+        <v>19243</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1730,7 +1772,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>210</v>
+        <v>999</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1738,7 +1780,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>556</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1746,7 +1788,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>52</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1754,15 +1796,15 @@
         <v>30</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>595</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>1048</v>
+      <c r="C32" s="11" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1778,23 +1820,23 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>2015</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>815</v>
+      <c r="C35" s="16" t="n">
+        <v>1490</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>990</v>
+      <c r="C36" s="16" t="n">
+        <v>2778</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1802,7 +1844,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>1222</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1810,31 +1852,31 @@
         <v>37</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>4784</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>21</v>
+      <c r="C39" s="16" t="n">
+        <v>2350</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>64</v>
+      <c r="C40" s="16" t="n">
+        <v>1891</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>334</v>
+      <c r="C41" s="16" t="n">
+        <v>2050</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -1842,7 +1884,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1850,7 +1892,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1858,7 +1900,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>88</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1866,15 +1908,15 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B46" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="12" t="n">
-        <v>5840</v>
+      <c r="C46" s="11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1882,7 +1924,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>363</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1890,15 +1932,15 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B49" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B49" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>423</v>
+      <c r="C49" s="12" t="n">
+        <v>5456</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1906,7 +1948,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>46</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1914,7 +1956,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>7</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1922,7 +1964,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>276</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1930,7 +1972,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1938,7 +1980,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1946,7 +1988,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1954,7 +1996,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>592</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1962,7 +2004,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>911</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -1970,7 +2012,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1978,7 +2020,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>96</v>
+        <v>475</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1986,7 +2028,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>234</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1994,7 +2036,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>177</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2002,7 +2044,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>458</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2010,7 +2052,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>18</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2018,23 +2060,23 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="66" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B66" s="14" t="s">
+      <c r="C65" s="11" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="12" t="n">
-        <v>8068</v>
+      <c r="C66" s="11" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -2042,7 +2084,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>87</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2050,7 +2092,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>238</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2058,7 +2100,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2066,23 +2108,23 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>406</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="72" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B72" s="15" t="s">
+      <c r="C71" s="16" t="n">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="72" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B72" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>270</v>
+      <c r="C72" s="12" t="n">
+        <v>15665</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2090,7 +2132,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>398</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2098,7 +2140,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>456</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2106,7 +2148,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2114,7 +2156,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>441</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2122,7 +2164,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>331</v>
+        <v>889</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2130,15 +2172,15 @@
         <v>77</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>889</v>
+        <v>681</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>3342</v>
+      <c r="C79" s="11" t="n">
+        <v>771</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2146,7 +2188,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>319</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2154,39 +2196,39 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B82" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="12" t="n">
-        <v>145228</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B83" s="14" t="s">
+      <c r="C82" s="11" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="12" t="n">
-        <v>42330</v>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C83" s="16" t="n">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="16" t="n">
-        <v>2315</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C84" s="11" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>5518</v>
+        <v>10526</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2194,31 +2236,31 @@
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B87" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B87" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B88" s="15" t="s">
+      <c r="C87" s="12" t="n">
+        <v>112376</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B88" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C88" s="12" t="n">
+        <v>25516</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="16" t="n">
-        <v>1680</v>
+      <c r="C89" s="11" t="n">
+        <v>365</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="true" outlineLevel="3">
@@ -2226,7 +2268,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>360</v>
+        <v>900</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="true" outlineLevel="3">
@@ -2234,55 +2276,55 @@
         <v>90</v>
       </c>
       <c r="C91" s="16" t="n">
-        <v>2835</v>
-      </c>
-    </row>
-    <row r="92" ht="22" customHeight="true" outlineLevel="3">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="16" t="n">
-        <v>5100</v>
+      <c r="C92" s="11" t="n">
+        <v>394</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="16" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C93" s="11" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>2488</v>
+      <c r="C95" s="11" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="16" t="n">
-        <v>5029</v>
+      <c r="C96" s="11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>20</v>
+      <c r="C97" s="16" t="n">
+        <v>1575</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="true" outlineLevel="3">
@@ -2290,7 +2332,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
@@ -2298,7 +2340,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="16" t="n">
-        <v>2884</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
@@ -2306,95 +2348,95 @@
         <v>99</v>
       </c>
       <c r="C100" s="16" t="n">
-        <v>4277</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="16" t="n">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B102" s="14" t="s">
+      <c r="C101" s="11" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="12" t="n">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C102" s="16" t="n">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C104" s="16" t="n">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C106" s="16" t="n">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C108" s="16" t="n">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B110" s="15" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="110" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B110" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B111" s="14" t="s">
+      <c r="C110" s="12" t="n">
+        <v>3246</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="12" t="n">
-        <v>29896</v>
+      <c r="C111" s="11" t="n">
+        <v>397</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2402,7 +2444,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>92</v>
+        <v>505</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2410,7 +2452,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>24</v>
+        <v>778</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2418,7 +2460,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>204</v>
+        <v>475</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2426,7 +2468,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>86</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2434,39 +2476,39 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>136</v>
+        <v>311</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="16" t="n">
-        <v>9975</v>
+      <c r="C117" s="11" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="16" t="n">
-        <v>11297</v>
+      <c r="C118" s="11" t="n">
+        <v>245</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="16" t="n">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="120" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B120" s="15" t="s">
+      <c r="C119" s="11" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="120" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B120" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="16" t="n">
-        <v>2750</v>
+      <c r="C120" s="12" t="n">
+        <v>24697</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2474,7 +2516,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2482,7 +2524,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2490,7 +2532,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2498,39 +2540,39 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>150</v>
+      <c r="C125" s="16" t="n">
+        <v>6225</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="11" t="n">
-        <v>63</v>
+      <c r="C126" s="16" t="n">
+        <v>8219</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>82</v>
+      <c r="C127" s="16" t="n">
+        <v>1700</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="11" t="n">
-        <v>170</v>
+      <c r="C128" s="16" t="n">
+        <v>1550</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2538,15 +2580,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="130" ht="22" customHeight="true" outlineLevel="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>121</v>
+        <v>51</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2554,7 +2596,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>199</v>
+        <v>69</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2562,7 +2604,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>273</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2570,7 +2612,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>40</v>
+        <v>124</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2578,15 +2620,15 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="135" ht="11" customHeight="true" outlineLevel="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>657</v>
+        <v>64</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2594,7 +2636,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>51</v>
+        <v>268</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2602,7 +2644,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>111</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2610,7 +2652,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>10</v>
+        <v>768</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2618,7 +2660,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2626,7 +2668,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>4</v>
+        <v>766</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2634,7 +2676,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>319</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2642,7 +2684,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>478</v>
+        <v>39</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2650,15 +2692,15 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="144" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B144" s="14" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="144" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B144" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="12" t="n">
-        <v>18018</v>
+      <c r="C144" s="11" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2666,7 +2708,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>28</v>
+        <v>638</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2674,7 +2716,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>77</v>
+        <v>248</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2682,7 +2724,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>60</v>
+        <v>766</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2690,7 +2732,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>68</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2698,7 +2740,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>83</v>
+        <v>768</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2706,7 +2748,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>58</v>
+        <v>192</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2714,15 +2756,15 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B152" s="15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B152" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>5</v>
+      <c r="C152" s="12" t="n">
+        <v>13956</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2738,7 +2780,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>476</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2746,7 +2788,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>165</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2754,7 +2796,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>255</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2762,7 +2804,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2770,7 +2812,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2778,7 +2820,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>339</v>
+        <v>38</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2786,7 +2828,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>218</v>
+        <v>37</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2794,7 +2836,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>132</v>
+        <v>56</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2802,7 +2844,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>362</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2810,7 +2852,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2818,7 +2860,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>183</v>
+        <v>422</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2826,7 +2868,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>239</v>
+        <v>138</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2834,7 +2876,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>368</v>
+        <v>255</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2842,7 +2884,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>244</v>
+        <v>59</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2850,7 +2892,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>66</v>
+        <v>184</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2858,7 +2900,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2866,7 +2908,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>502</v>
+        <v>218</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2874,7 +2916,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2882,7 +2924,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>18</v>
+        <v>362</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2890,7 +2932,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2898,7 +2940,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>128</v>
+        <v>183</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2906,15 +2948,15 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="176" ht="22" customHeight="true" outlineLevel="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="15" t="s">
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>44</v>
+        <v>368</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2922,7 +2964,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2930,7 +2972,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>333</v>
+        <v>127</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2938,7 +2980,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2946,23 +2988,23 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="181" ht="22" customHeight="true" outlineLevel="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="182" ht="22" customHeight="true" outlineLevel="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>138</v>
+        <v>408</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2970,7 +3012,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2978,15 +3020,15 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="185" ht="22" customHeight="true" outlineLevel="3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2994,7 +3036,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187" ht="22" customHeight="true" outlineLevel="3">
@@ -3002,15 +3044,15 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="188" ht="11" customHeight="true" outlineLevel="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3018,7 +3060,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>427</v>
+        <v>25</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3026,15 +3068,15 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="191" ht="11" customHeight="true" outlineLevel="3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>169</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3042,15 +3084,15 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="193" ht="11" customHeight="true" outlineLevel="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>179</v>
+        <v>135</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3058,7 +3100,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>314</v>
+        <v>97</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3066,7 +3108,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>100</v>
+        <v>427</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3074,7 +3116,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>225</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3082,7 +3124,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3090,7 +3132,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3098,15 +3140,15 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="200" ht="22" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>44</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3114,7 +3156,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>68</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3122,7 +3164,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>112</v>
+        <v>225</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3130,7 +3172,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>63</v>
+        <v>173</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3138,7 +3180,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3146,7 +3188,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>199</v>
+        <v>244</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3154,7 +3196,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3162,7 +3204,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>418</v>
+        <v>57</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3170,7 +3212,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>384</v>
+        <v>112</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3178,7 +3220,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3186,7 +3228,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>211</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3194,7 +3236,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3202,7 +3244,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>271</v>
+        <v>145</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3210,15 +3252,15 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="16" t="n">
-        <v>1008</v>
+      <c r="C214" s="11" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3226,15 +3268,15 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>296</v>
+        <v>146</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="16" t="n">
-        <v>2908</v>
+      <c r="C216" s="11" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3242,7 +3284,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>275</v>
+        <v>131</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3250,7 +3292,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>183</v>
+        <v>131</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3258,7 +3300,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>184</v>
+        <v>34</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3266,7 +3308,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>662</v>
+        <v>152</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3274,7 +3316,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3282,15 +3324,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>293</v>
+        <v>76</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="11" t="n">
-        <v>2</v>
+      <c r="C223" s="16" t="n">
+        <v>2688</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3298,7 +3340,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>195</v>
+        <v>275</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3306,7 +3348,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>111</v>
+        <v>173</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3314,7 +3356,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>263</v>
+        <v>184</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3322,7 +3364,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>31</v>
+        <v>237</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3330,7 +3372,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>253</v>
+        <v>293</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3338,15 +3380,15 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="230" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B230" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="12" t="n">
-        <v>9859</v>
+      <c r="C230" s="11" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3354,7 +3396,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>226</v>
+        <v>89</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3362,7 +3404,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3370,7 +3412,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>222</v>
+        <v>14</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3378,7 +3420,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3386,15 +3428,15 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="236" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B236" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B236" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>763</v>
+      <c r="C236" s="12" t="n">
+        <v>5714</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3402,7 +3444,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3410,7 +3452,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>74</v>
+        <v>339</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3418,7 +3460,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>82</v>
+        <v>224</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3426,7 +3468,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>220</v>
+        <v>139</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3434,7 +3476,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3442,7 +3484,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>78</v>
+        <v>473</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3450,7 +3492,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>560</v>
+        <v>30</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3458,7 +3500,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3466,7 +3508,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>441</v>
+        <v>39</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3474,7 +3516,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3482,7 +3524,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3490,7 +3532,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>165</v>
+        <v>202</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3498,7 +3540,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>57</v>
+        <v>241</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3506,7 +3548,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>499</v>
+        <v>18</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3514,7 +3556,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3522,7 +3564,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>433</v>
+        <v>54</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3530,7 +3572,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3538,7 +3580,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>631</v>
+        <v>430</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3546,7 +3588,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>119</v>
+        <v>216</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3554,7 +3596,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>212</v>
+        <v>119</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3562,7 +3604,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3570,7 +3612,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>258</v>
+        <v>225</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3578,7 +3620,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>414</v>
+        <v>253</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3586,7 +3628,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>295</v>
+        <v>599</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3594,7 +3636,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>624</v>
+        <v>194</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3602,7 +3644,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3610,15 +3652,15 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>230</v>
+        <v>24</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
       <c r="B264" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="16" t="n">
-        <v>1792</v>
+      <c r="C264" s="11" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3626,15 +3668,15 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="266" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B266" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="17" t="n">
-        <v>678</v>
+      <c r="C266" s="11" t="n">
+        <v>383</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3642,7 +3684,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>62</v>
+        <v>176</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3650,7 +3692,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>1</v>
+        <v>335</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3658,7 +3700,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3666,15 +3708,15 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B271" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B271" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>25</v>
+      <c r="C271" s="17" t="n">
+        <v>531</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3682,7 +3724,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3690,7 +3732,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3698,7 +3740,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3706,7 +3748,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3714,7 +3756,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>248</v>
+        <v>25</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3722,7 +3764,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3738,7 +3780,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3746,7 +3788,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3754,15 +3796,15 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="282" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B282" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B282" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="12" t="n">
-        <v>9574</v>
+      <c r="C282" s="11" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3770,7 +3812,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>474</v>
+        <v>32</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3778,7 +3820,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>163</v>
+        <v>46</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3786,7 +3828,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3794,7 +3836,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3802,15 +3844,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B288" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B288" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="11" t="n">
-        <v>184</v>
+      <c r="C288" s="12" t="n">
+        <v>9087</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3818,7 +3860,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>26</v>
+        <v>428</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3826,15 +3868,15 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="291" ht="22" customHeight="true" outlineLevel="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>56</v>
+        <v>141</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3842,7 +3884,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3850,7 +3892,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3858,23 +3900,23 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="true" outlineLevel="3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>23</v>
+        <v>151</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="true" outlineLevel="3">
@@ -3882,31 +3924,31 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3914,7 +3956,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3922,31 +3964,31 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="303" ht="11" customHeight="true" outlineLevel="3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="305" ht="11" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>660</v>
+        <v>9</v>
       </c>
     </row>
     <row r="306" ht="22" customHeight="true" outlineLevel="3">
@@ -3954,23 +3996,23 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="307" ht="22" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="16" t="n">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="308" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C307" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" ht="22" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3978,7 +4020,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>918</v>
+        <v>26</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -3986,7 +4028,7 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -3994,7 +4036,7 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>299</v>
+        <v>71</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -4002,7 +4044,7 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -4010,23 +4052,23 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="314" ht="11" customHeight="true" outlineLevel="3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="16" t="n">
-        <v>2002</v>
+      <c r="C314" s="11" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="11" t="n">
-        <v>105</v>
+      <c r="C315" s="16" t="n">
+        <v>1479</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4034,15 +4076,15 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B317" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="12" t="n">
-        <v>10345</v>
+      <c r="C317" s="11" t="n">
+        <v>588</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4050,7 +4092,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>646</v>
+        <v>399</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4058,15 +4100,15 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>9</v>
+        <v>282</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
@@ -4074,7 +4116,7 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>748</v>
+        <v>118</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -4082,23 +4124,23 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>266</v>
+        <v>236</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B324" s="15" t="s">
+      <c r="C323" s="16" t="n">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B324" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="11" t="n">
-        <v>982</v>
+      <c r="C324" s="12" t="n">
+        <v>6802</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4106,7 +4148,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>57</v>
+        <v>398</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4114,23 +4156,23 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="327" ht="11" customHeight="true" outlineLevel="3">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="328" ht="11" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4138,7 +4180,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>105</v>
+        <v>301</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4146,7 +4188,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>189</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4154,7 +4196,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>597</v>
+        <v>154</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4162,7 +4204,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>263</v>
+        <v>321</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4170,7 +4212,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>492</v>
+        <v>103</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4178,7 +4220,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4186,7 +4228,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4194,23 +4236,23 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="338" ht="22" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>79</v>
+        <v>274</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
@@ -4218,7 +4260,7 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>11</v>
+        <v>322</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4226,15 +4268,15 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>41</v>
+        <v>179</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4242,15 +4284,15 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4258,23 +4300,23 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="345" ht="22" customHeight="true" outlineLevel="3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="347" ht="22" customHeight="true" outlineLevel="3">
@@ -4282,15 +4324,15 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4298,15 +4340,15 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4314,15 +4356,15 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="16" t="n">
-        <v>1757</v>
+      <c r="C352" s="11" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4330,15 +4372,15 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354" ht="22" customHeight="true" outlineLevel="3">
       <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>493</v>
+        <v>29</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4346,15 +4388,15 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B356" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="17" t="n">
-        <v>89</v>
+      <c r="C356" s="11" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4362,7 +4404,7 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>75</v>
+        <v>225</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4370,15 +4412,15 @@
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B359" s="14" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="12" t="n">
-        <v>23118</v>
+      <c r="C359" s="16" t="n">
+        <v>1034</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4386,7 +4428,7 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>32</v>
+        <v>151</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4394,7 +4436,7 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>414</v>
+        <v>393</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4402,47 +4444,47 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="363" ht="22" customHeight="true" outlineLevel="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="15" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="364" ht="33" customHeight="true" outlineLevel="3">
-      <c r="B364" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B364" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="11" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C364" s="17" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B367" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B367" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="C367" s="11" t="n">
-        <v>606</v>
+      <c r="C367" s="12" t="n">
+        <v>22738</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4450,15 +4492,15 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
@@ -4466,47 +4508,47 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="371" ht="33" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="374" ht="22" customHeight="true" outlineLevel="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="375" ht="22" customHeight="true" outlineLevel="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>518</v>
+        <v>670</v>
       </c>
     </row>
     <row r="376" ht="22" customHeight="true" outlineLevel="3">
@@ -4514,31 +4556,31 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="377" ht="22" customHeight="true" outlineLevel="3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="16" t="n">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C377" s="11" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="16" t="n">
-        <v>1572</v>
+      <c r="C379" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="380" ht="22" customHeight="true" outlineLevel="3">
@@ -4546,7 +4588,7 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
     </row>
     <row r="381" ht="22" customHeight="true" outlineLevel="3">
@@ -4554,23 +4596,23 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>18</v>
+        <v>167</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
       <c r="B382" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="16" t="n">
-        <v>1534</v>
+      <c r="C382" s="11" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="11" t="n">
-        <v>183</v>
+      <c r="C383" s="16" t="n">
+        <v>1174</v>
       </c>
     </row>
     <row r="384" ht="22" customHeight="true" outlineLevel="3">
@@ -4578,23 +4620,23 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>102</v>
+        <v>512</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="11" t="n">
-        <v>39</v>
+      <c r="C385" s="16" t="n">
+        <v>1137</v>
       </c>
     </row>
     <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="16" t="n">
-        <v>1450</v>
+      <c r="C386" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="387" ht="22" customHeight="true" outlineLevel="3">
@@ -4602,15 +4644,15 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="388" ht="22" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="11" t="n">
-        <v>7</v>
+      <c r="C388" s="16" t="n">
+        <v>1171</v>
       </c>
     </row>
     <row r="389" ht="22" customHeight="true" outlineLevel="3">
@@ -4618,7 +4660,7 @@
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>44</v>
+        <v>342</v>
       </c>
     </row>
     <row r="390" ht="22" customHeight="true" outlineLevel="3">
@@ -4626,7 +4668,7 @@
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4634,7 +4676,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4642,7 +4684,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="16" t="n">
-        <v>2681</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4650,23 +4692,23 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="394" ht="22" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
     </row>
     <row r="396" ht="22" customHeight="true" outlineLevel="3">
@@ -4674,7 +4716,7 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>52</v>
+        <v>123</v>
       </c>
     </row>
     <row r="397" ht="22" customHeight="true" outlineLevel="3">
@@ -4682,15 +4724,15 @@
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="398" ht="22" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="11" t="n">
-        <v>10</v>
+      <c r="C398" s="16" t="n">
+        <v>1154</v>
       </c>
     </row>
     <row r="399" ht="22" customHeight="true" outlineLevel="3">
@@ -4698,23 +4740,23 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="401" ht="22" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
@@ -4722,55 +4764,55 @@
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="404" ht="22" customHeight="true" outlineLevel="3">
       <c r="B404" s="15" t="s">
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
       <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="407" ht="22" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="15" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="409" ht="11" customHeight="true" outlineLevel="3">
@@ -4778,15 +4820,15 @@
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="410" ht="11" customHeight="true" outlineLevel="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C410" s="11" t="n">
-        <v>184</v>
+      <c r="C410" s="16" t="n">
+        <v>1045</v>
       </c>
     </row>
     <row r="411" ht="11" customHeight="true" outlineLevel="3">
@@ -4794,15 +4836,15 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="412" ht="11" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
       <c r="B412" s="15" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>299</v>
+        <v>748</v>
       </c>
     </row>
     <row r="413" ht="11" customHeight="true" outlineLevel="3">
@@ -4810,15 +4852,15 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="15" t="s">
         <v>413</v>
       </c>
       <c r="C414" s="11" t="n">
-        <v>211</v>
+        <v>874</v>
       </c>
     </row>
     <row r="415" ht="11" customHeight="true" outlineLevel="3">
@@ -4826,47 +4868,159 @@
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B416" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="C416" s="12" t="n">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B417" s="19" t="s">
+      <c r="C416" s="11" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B418" s="19" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="419" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="11" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="11" t="n">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="11" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="16" t="n">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="11" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="11" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B430" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="17" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="431" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B431" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="419" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B419" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="C419" s="11" t="n">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B420" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="C420" s="11" t="n">
-        <v>200</v>
+    <row r="432" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B432" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="433" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B433" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B434" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="11" t="n">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
